--- a/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
+++ b/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
@@ -38,9 +38,9 @@
     <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
     <numFmt numFmtId="169" formatCode="0.00;(0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.000%"/>
-    <numFmt numFmtId="171" formatCode="0.0000"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -151,22 +151,22 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -850,7 +850,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8.87% -&gt; 8.67% on the same easing calendar as the cost-of-debt path; the terminal value is</t>
+          <t>9.21% -&gt; 8.67% on the same easing calendar as the cost-of-debt path; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -1044,23 +1044,23 @@
         <v>1362.497</v>
       </c>
       <c r="E6" s="17">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="I6" s="17">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -1166,23 +1166,23 @@
       <c r="D15" s="26" t="n">
         <v>8408.904</v>
       </c>
-      <c r="E15" s="30">
-        <f>Assumptions!$C$66+'Income Statement'!E20-'Cash Flow'!B15</f>
-        <v/>
-      </c>
-      <c r="F15" s="30">
+      <c r="E15" s="31">
+        <f>Assumptions!$C$82+'Income Statement'!E20-'Cash Flow'!B15</f>
+        <v/>
+      </c>
+      <c r="F15" s="31">
         <f>E15+'Income Statement'!F20-'Cash Flow'!C15</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <f>F15+'Income Statement'!G20-'Cash Flow'!D15</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <f>G15+'Income Statement'!H20-'Cash Flow'!E15</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <f>H15+'Income Statement'!I20-'Cash Flow'!F15</f>
         <v/>
       </c>
@@ -1193,15 +1193,15 @@
           <t>Working capital (from the lines above)</t>
         </is>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <f>B8+B9-B13</f>
         <v/>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>C8+C9-C13</f>
         <v/>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>D8+D9-D13</f>
         <v/>
       </c>
@@ -1232,15 +1232,15 @@
           <t>Net debt (negative = net cash)</t>
         </is>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <f>B12-B10</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>C12-C10</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>D12-D10</f>
         <v/>
       </c>
@@ -1271,35 +1271,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="40">
         <f>B17/'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="40">
         <f>C17/'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="40">
         <f>D17/'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="40">
         <f>E17/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="40">
         <f>F17/'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="40">
         <f>G17/'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="40">
         <f>H17/'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I18" s="39">
+      <c r="I18" s="40">
         <f>I17/'Income Statement'!I9</f>
         <v/>
       </c>
@@ -1322,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1445,7 +1445,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>less capital expenditure</t>
+          <t>less owned capex + pre-delivery payments</t>
         </is>
       </c>
       <c r="B7" s="17">
@@ -1502,24 +1502,51 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B9" s="31">
-        <f>B5+B6-B7-B8</f>
-        <v/>
-      </c>
-      <c r="C9" s="31">
-        <f>C5+C6-C7-C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="31">
-        <f>D5+D6-D7-D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="31">
-        <f>E5+E6-E7-E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="31">
-        <f>F5+F6-F7-F8</f>
+      <c r="B9" s="32">
+        <f>B5+B6-B7-B8-B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="32">
+        <f>C5+C6-C7-C8-C10</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>D5+D6-D7-D8-D10</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>E5+E6-E7-E8-E10</f>
+        <v/>
+      </c>
+      <c r="F9" s="32">
+        <f>F5+F6-F7-F8-F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>less leased-fleet additions (gross)</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
+        <f>DCF!B45</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>DCF!C45</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>DCF!D45</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>DCF!E45</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>DCF!F45</f>
         <v/>
       </c>
     </row>
@@ -1561,23 +1588,23 @@
           <t>Opening net debt (negative = net cash)</t>
         </is>
       </c>
-      <c r="B12" s="30">
-        <f>Assumptions!$C$59-Assumptions!$C$60</f>
-        <v/>
-      </c>
-      <c r="C12" s="30">
+      <c r="B12" s="31">
+        <f>Assumptions!$C$75-Assumptions!$C$76</f>
+        <v/>
+      </c>
+      <c r="C12" s="31">
         <f>B16</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>C16</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>D16</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>E16</f>
         <v/>
       </c>
@@ -1585,81 +1612,81 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Finance income (deposit yield x cash and deposits)</t>
-        </is>
-      </c>
-      <c r="B13" s="33">
-        <f>Assumptions!B24*(MAX(-B12,0)+Assumptions!$C$59)</f>
-        <v/>
-      </c>
-      <c r="C13" s="33">
-        <f>Assumptions!C24*(MAX(-C12,0)+Assumptions!$C$59)</f>
-        <v/>
-      </c>
-      <c r="D13" s="33">
-        <f>Assumptions!D24*(MAX(-D12,0)+Assumptions!$C$59)</f>
-        <v/>
-      </c>
-      <c r="E13" s="33">
-        <f>Assumptions!E24*(MAX(-E12,0)+Assumptions!$C$59)</f>
-        <v/>
-      </c>
-      <c r="F13" s="33">
-        <f>Assumptions!F24*(MAX(-F12,0)+Assumptions!$C$59)</f>
+          <t>Finance income (deposit yield x opening cash and deposits)</t>
+        </is>
+      </c>
+      <c r="B13" s="36">
+        <f>Assumptions!B29*(B17-B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="36">
+        <f>Assumptions!C29*(C17-C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="36">
+        <f>Assumptions!D29*(D17-D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="36">
+        <f>Assumptions!E29*(E17-E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="36">
+        <f>Assumptions!F29*(F17-F12)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Finance costs (booked rate x gross debt)</t>
-        </is>
-      </c>
-      <c r="B14" s="33">
-        <f>Assumptions!B23*Assumptions!$C$59*0.8</f>
-        <v/>
-      </c>
-      <c r="C14" s="33">
-        <f>Assumptions!C23*Assumptions!$C$59*0.8</f>
-        <v/>
-      </c>
-      <c r="D14" s="33">
-        <f>Assumptions!D23*Assumptions!$C$59*0.8</f>
-        <v/>
-      </c>
-      <c r="E14" s="33">
-        <f>Assumptions!E23*Assumptions!$C$59*0.8</f>
-        <v/>
-      </c>
-      <c r="F14" s="33">
-        <f>Assumptions!F23*Assumptions!$C$59*0.8</f>
+          <t>Finance costs (booked rate x average gross debt)</t>
+        </is>
+      </c>
+      <c r="B14" s="36">
+        <f>Assumptions!B26*(B17+B18)/2</f>
+        <v/>
+      </c>
+      <c r="C14" s="36">
+        <f>Assumptions!C26*(C17+C18)/2</f>
+        <v/>
+      </c>
+      <c r="D14" s="36">
+        <f>Assumptions!D26*(D17+D18)/2</f>
+        <v/>
+      </c>
+      <c r="E14" s="36">
+        <f>Assumptions!E26*(E17+E18)/2</f>
+        <v/>
+      </c>
+      <c r="F14" s="36">
+        <f>Assumptions!F26*(F17+F18)/2</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="B15" s="30">
-        <f>Assumptions!B26*'Income Statement'!E20</f>
-        <v/>
-      </c>
-      <c r="C15" s="30">
-        <f>Assumptions!C26*'Income Statement'!F20</f>
-        <v/>
-      </c>
-      <c r="D15" s="30">
-        <f>Assumptions!D26*'Income Statement'!G20</f>
-        <v/>
-      </c>
-      <c r="E15" s="30">
-        <f>Assumptions!E26*'Income Statement'!H20</f>
-        <v/>
-      </c>
-      <c r="F15" s="30">
-        <f>Assumptions!F26*'Income Statement'!I20</f>
+          <t>Dividends paid (payout, floored at 30 fils)</t>
+        </is>
+      </c>
+      <c r="B15" s="31">
+        <f>MAX(Assumptions!B31*'Income Statement'!E20,Assumptions!$C$59)</f>
+        <v/>
+      </c>
+      <c r="C15" s="31">
+        <f>MAX(Assumptions!C31*'Income Statement'!F20,Assumptions!$C$59)</f>
+        <v/>
+      </c>
+      <c r="D15" s="31">
+        <f>MAX(Assumptions!D31*'Income Statement'!G20,Assumptions!$C$59)</f>
+        <v/>
+      </c>
+      <c r="E15" s="31">
+        <f>MAX(Assumptions!E31*'Income Statement'!H20,Assumptions!$C$59)</f>
+        <v/>
+      </c>
+      <c r="F15" s="31">
+        <f>MAX(Assumptions!F31*'Income Statement'!I20,Assumptions!$C$59)</f>
         <v/>
       </c>
     </row>
@@ -1669,110 +1696,164 @@
           <t>Closing net debt</t>
         </is>
       </c>
-      <c r="B16" s="31">
-        <f>B12-(B9+B13-B14*(1-Assumptions!$C$31))+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="31">
-        <f>C12-(C9+C13-C14*(1-Assumptions!$C$31))+C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="31">
-        <f>D12-(D9+D13-D14*(1-Assumptions!$C$31))+D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="31">
-        <f>E12-(E9+E13-E14*(1-Assumptions!$C$31))+E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="31">
-        <f>F12-(F9+F13-F14*(1-Assumptions!$C$31))+F15</f>
+      <c r="B16" s="32">
+        <f>B12-(B9+(B13-B14)*(1-Assumptions!$C$36))+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>C12-(C9+(C13-C14)*(1-Assumptions!$C$36))+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>D12-(D9+(D13-D14)*(1-Assumptions!$C$36))+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>E12-(E9+(E13-E14)*(1-Assumptions!$C$36))+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>F12-(F9+(F13-F14)*(1-Assumptions!$C$36))+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Opening gross debt (borrowings + leases)</t>
+        </is>
+      </c>
+      <c r="B17" s="17">
+        <f>Assumptions!$C$75</f>
+        <v/>
+      </c>
+      <c r="C17" s="31">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="D17" s="31">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="E17" s="31">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="F17" s="31">
+        <f>E18</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Closing gross debt (+ new leases + aircraft loans - amortisation)</t>
+        </is>
+      </c>
+      <c r="B18" s="31">
+        <f>B17+DCF!B45+Assumptions!B23*Assumptions!$C$58-Assumptions!B27</f>
+        <v/>
+      </c>
+      <c r="C18" s="31">
+        <f>C17+DCF!C45+Assumptions!C23*Assumptions!$C$58-Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>D17+DCF!D45+Assumptions!D23*Assumptions!$C$58-Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E18" s="31">
+        <f>E17+DCF!E45+Assumptions!E23*Assumptions!$C$58-Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F18" s="31">
+        <f>F17+DCF!F45+Assumptions!F23*Assumptions!$C$58-Assumptions!F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Audited history (AED mn)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Net cash from operating activities</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="n">
-        <v>2304.108</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>2278.691</v>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>2860.401</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Fleet capex incl. aircraft advances</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="n">
-        <v>378.035</v>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>579.654</v>
-      </c>
-      <c r="D20" s="26" t="n">
-        <v>2327.603</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Dividends paid to owners</t>
+          <t>Net cash from operating activities</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>700.005</v>
+        <v>2304.108</v>
       </c>
       <c r="C21" s="26" t="n">
-        <v>933.34</v>
+        <v>2278.691</v>
       </c>
       <c r="D21" s="26" t="n">
-        <v>1167.376</v>
+        <v>2860.401</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>Fleet capex incl. aircraft advances</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>378.035</v>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>579.654</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>2327.603</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid to owners</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>700.005</v>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>933.34</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>1167.376</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B24" s="26" t="n">
         <v>647.327</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C24" s="26" t="n">
         <v>648.588</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D24" s="26" t="n">
         <v>621.798</v>
       </c>
     </row>
@@ -2107,23 +2188,23 @@
         <v>0.3</v>
       </c>
       <c r="E11" s="10">
-        <f>'Cash Flow'!B15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!B15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>'Cash Flow'!C15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!C15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>'Cash Flow'!D15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!D15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="H11" s="10">
-        <f>'Cash Flow'!E15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!E15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="I11" s="10">
-        <f>'Cash Flow'!F15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!F15/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -2227,7 +2308,7 @@
         </is>
       </c>
       <c r="E15" s="11">
-        <f>'Income Statement'!E20/Assumptions!$C$66</f>
+        <f>'Income Statement'!E20/Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="F15" s="11">
@@ -2262,23 +2343,23 @@
       <c r="D16" s="23" t="n">
         <v>13.06</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="33">
         <f>Segments!B5</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="33">
         <f>Segments!C5</f>
         <v/>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="33">
         <f>Segments!D5</f>
         <v/>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="33">
         <f>Segments!E5</f>
         <v/>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="33">
         <f>Segments!F5</f>
         <v/>
       </c>
@@ -2289,35 +2370,35 @@
           <t>Revenue per passenger (AED, total revenue basis)</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="36">
         <f>B5/B16</f>
         <v/>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="36">
         <f>C5/C16</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="36">
         <f>D5/D16</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="36">
         <f>E5/E16</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="36">
         <f>F5/F16</f>
         <v/>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="36">
         <f>G5/G16</f>
         <v/>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="36">
         <f>H5/H16</f>
         <v/>
       </c>
-      <c r="I17" s="33">
+      <c r="I17" s="36">
         <f>I5/I16</f>
         <v/>
       </c>
@@ -2534,7 +2615,7 @@
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>Struck at AED 5.24 on 2026-08-07 with a 5.7% trailing dividend yield netted from the drift. How much to trust these bands: over the stock's full history the simulation's probability bands beat a naive random-walk benchmark by a small margin on a standard probabilistic accuracy score (+0.7%), and over the recent four-plus years the two are statistically indistinguishable — the bands are honest, not clairvoyant. Realised outcomes landed inside the 80% band 83% of the time and inside the 90% band 89% of the time, about as close to nominal as a small sample allows.</t>
+          <t>Struck at AED 5.24 on 2026-08-07 with a 5.7% trailing dividend yield netted from the drift. How much to trust these bands: over the stock's full history the simulation's probability bands beat a naive random-walk benchmark by a small margin on a standard probabilistic accuracy score (+0.7% over the full 58-window history, 2012-2026), and over the recent four-plus years the two are statistically indistinguishable — the bands are honest, not clairvoyant. Realised outcomes landed inside the 80% band 79% of the time and inside the 90% band 86% of the time over that same full history — ONE window set, quoted identically in the study.</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2629,19 +2710,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4.86000159272719</v>
+        <v>4.563727371978012</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>5.125639335220155</v>
+        <v>4.826833817314236</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>5.453202808218446</v>
+        <v>5.151250713834374</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5.868018473014169</v>
+        <v>5.562052885138246</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>6.411403485131497</v>
+        <v>6.100146969325265</v>
       </c>
     </row>
     <row r="7">
@@ -2651,19 +2732,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4.134192488387557</v>
+        <v>3.844894063371688</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4.293347755299112</v>
+        <v>4.002252033552121</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4.481883386446197</v>
+        <v>4.188636361804018</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4.709241080832226</v>
+        <v>4.413374983406841</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4.98939348367895</v>
+        <v>4.690272186155007</v>
       </c>
     </row>
     <row r="8">
@@ -2673,19 +2754,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3.611505598030214</v>
+        <v>3.328204707597294</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.711215481738839</v>
+        <v>3.426565626328664</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.539716388425919</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.959649620558999</v>
+        <v>3.671571273184506</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4.117858723019506</v>
+        <v>3.827559476465596</v>
       </c>
     </row>
     <row r="9">
@@ -2695,19 +2776,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.217308493774543</v>
+        <v>2.939350044427541</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.281345105144399</v>
+        <v>3.002332932445859</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3.353352830354851</v>
+        <v>3.073135682640569</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.43512490551771</v>
+        <v>3.153517504517958</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3.529036064109843</v>
+        <v>3.245808071052985</v>
       </c>
     </row>
     <row r="10">
@@ -2717,19 +2798,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>2.909533334125558</v>
+        <v>2.636446054689363</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2.951018541788566</v>
+        <v>2.677083058851147</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2.996762467409751</v>
+        <v>2.721871308489303</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.047598231558944</v>
+        <v>2.771622899645585</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3.104591421673036</v>
+        <v>2.827376528723581</v>
       </c>
     </row>
     <row r="12">
@@ -2774,111 +2855,111 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>5.615531082125334</v>
+        <v>5.304018537245045</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>4.611779535138628</v>
+        <v>4.309353735514492</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3.933938958261041</v>
+        <v>3.63883720038445</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3.445582025385977</v>
+        <v>3.156735978743524</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3.077095787725095</v>
+        <v>2.793793397486388</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>8.21%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5.533423661671399</v>
+        <v>5.226747607739238</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>4.546077717134472</v>
+        <v>4.248294800245155</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3.879313165736106</v>
+        <v>3.588702352857153</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3.398933742908868</v>
+        <v>3.114451765271498</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>3.03646490985513</v>
+        <v>2.757416260096355</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>9.21%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>5.453202808218446</v>
+        <v>5.151250713834374</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>4.481883386446197</v>
+        <v>4.188636361804018</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.539716388425919</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3.353352830354851</v>
+        <v>3.073135682640569</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>2.996762467409751</v>
+        <v>2.721871308489303</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>10.21%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5.374811450093459</v>
+        <v>5.077474294187578</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>4.419150986997378</v>
+        <v>4.13033617316109</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>3.773778639541364</v>
+        <v>3.491844679320727</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3.308807097825804</v>
+        <v>3.032758574919082</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2.957960488374762</v>
+        <v>2.687133500795821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>10.87%</t>
+          <t>11.21%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>5.298194679313306</v>
+        <v>5.005366813033706</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>4.357836688605953</v>
+        <v>4.073353583985758</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3.72279576705975</v>
+        <v>3.445053905711079</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3.26526557327047</v>
+        <v>2.993292386783587</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2.9200320583038</v>
+        <v>2.653178739906747</v>
       </c>
     </row>
     <row r="20">
@@ -2923,19 +3004,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>4.55525352719996</v>
+        <v>4.257253763870267</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>4.213710434605852</v>
+        <v>3.920913618442269</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.539716388425919</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3.55369331183149</v>
+        <v>3.272618534148231</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>3.25162256389066</v>
+        <v>2.976910757184894</v>
       </c>
     </row>
     <row r="24">
@@ -2980,19 +3061,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>5.089658942693668</v>
+        <v>4.772475002449729</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>4.457798965202891</v>
+        <v>4.14253923376319</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3.194079010221337</v>
+        <v>2.882667696390122</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2.56221903273056</v>
+        <v>2.252731927703584</v>
       </c>
     </row>
     <row r="28">
@@ -3037,19 +3118,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>3.148807583207949</v>
+        <v>2.837389090760229</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3.487373285460031</v>
+        <v>3.174996277918442</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>4.164504689964191</v>
+        <v>3.850210652234865</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>4.503070392216276</v>
+        <v>4.187817839393076</v>
       </c>
     </row>
     <row r="32">
@@ -3094,19 +3175,19 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>2.339775855100146</v>
+        <v>2.030923191697147</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>3.08285742140613</v>
+        <v>2.7717633283869</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>4.569020554018098</v>
+        <v>4.253443601766409</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>5.312102120324081</v>
+        <v>4.994283738456162</v>
       </c>
     </row>
     <row r="36">
@@ -3151,19 +3232,19 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>4.288271530765242</v>
+        <v>4.047106184932743</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>4.057105259238678</v>
+        <v>3.779854825004699</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3.479189580422266</v>
+        <v>3.111726425184587</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>3.132440173132419</v>
+        <v>2.71084938529252</v>
       </c>
     </row>
     <row r="40">
@@ -3208,19 +3289,19 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>4.087349221154775</v>
+        <v>3.766451552378421</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>4.259126488113735</v>
+        <v>3.933259599963986</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>4.387959438332954</v>
+        <v>4.05836563565316</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>4.602681022031653</v>
+        <v>4.266875695135115</v>
       </c>
     </row>
     <row r="44">
@@ -3265,19 +3346,177 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>3.657376569144967</v>
+        <v>3.34435094460545</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>3.741657778428539</v>
+        <v>3.428477204841052</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>3.825938987712114</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3.910220196995685</v>
+        <v>3.596729725312257</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>3.994501406279259</v>
+        <v>3.680855985547858</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Published scenario driver vectors — type these into the Scenario cells on Assumptions to reproduce each pasted output LIVE in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Passenger x</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Fare x</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Fuel path</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Capex x</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Rate shift</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Terminal g</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Output (AED/sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>High-fuel alternative</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>alternative (switch=1)</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="46" t="inlineStr">
+        <is>
+          <t>0bp</t>
+        </is>
+      </c>
+      <c r="G50" s="46" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>1.855923186986279</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>alternative (switch=1)</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F51" s="46" t="inlineStr">
+        <is>
+          <t>+100bp</t>
+        </is>
+      </c>
+      <c r="G51" s="46" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>0.4703575469948413</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Bull (JV capitalised)</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D52" s="46" t="inlineStr">
+        <is>
+          <t>base (switch=0)</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F52" s="46" t="inlineStr">
+        <is>
+          <t>-100bp</t>
+        </is>
+      </c>
+      <c r="G52" s="46" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>7.228322439161341</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>The bull additionally switches the SOTP Bridge to the JV-capitalised row. Every other figure in the workbook reprices live when the Scenario cells change.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3375,19 +3614,19 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>Assumptions!$C$48</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>'Cash Flow'!B15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!B15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>'Cash Flow'!D15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!D15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>'Cash Flow'!F15/Assumptions!$C$47</f>
+        <f>'Cash Flow'!F15/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -3398,19 +3637,19 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>Assumptions!$C$66/Assumptions!$C$47</f>
+        <f>Assumptions!$C$82/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>'Balance Sheet'!E15/Assumptions!$C$47</f>
+        <f>'Balance Sheet'!E15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>'Balance Sheet'!G15/Assumptions!$C$47</f>
+        <f>'Balance Sheet'!G15/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>'Balance Sheet'!I15/Assumptions!$C$47</f>
+        <f>'Balance Sheet'!I15/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -3421,15 +3660,15 @@
         </is>
       </c>
       <c r="C8" s="8">
-        <f>'Cash Flow'!B9/Assumptions!$C$47</f>
+        <f>'Cash Flow'!B9/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>'Cash Flow'!D9/Assumptions!$C$47</f>
+        <f>'Cash Flow'!D9/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>'Cash Flow'!F9/Assumptions!$C$47</f>
+        <f>'Cash Flow'!F9/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3679,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'SOTP Bridge'!C6/Assumptions!$C$47</f>
+        <f>'SOTP Bridge'!C6/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -3463,8 +3702,8 @@
           <t>Trailing price/earnings</t>
         </is>
       </c>
-      <c r="C12" s="39">
-        <f>Assumptions!$C$46/'Income Statement'!D21</f>
+      <c r="C12" s="40">
+        <f>Assumptions!$C$52/'Income Statement'!D21</f>
         <v/>
       </c>
     </row>
@@ -3474,8 +3713,8 @@
           <t>Forward price/earnings (FY2027E)</t>
         </is>
       </c>
-      <c r="C13" s="39">
-        <f>Assumptions!$C$46/'Income Statement'!F21</f>
+      <c r="C13" s="40">
+        <f>Assumptions!$C$52/'Income Statement'!F21</f>
         <v/>
       </c>
     </row>
@@ -3485,8 +3724,8 @@
           <t>Price / book (FY2025)</t>
         </is>
       </c>
-      <c r="C14" s="39">
-        <f>Assumptions!$C$46/((Assumptions!$C$66)/Assumptions!$C$47)</f>
+      <c r="C14" s="40">
+        <f>Assumptions!$C$52/((Assumptions!$C$82)/Assumptions!$C$53)</f>
         <v/>
       </c>
     </row>
@@ -3496,8 +3735,8 @@
           <t>EV / EBITDA (trailing, incl. fees)</t>
         </is>
       </c>
-      <c r="C15" s="39">
-        <f>(DCF!C14+Assumptions!$C$59-Assumptions!$C$60)/('Income Statement'!D9+'Income Statement'!D12)</f>
+      <c r="C15" s="40">
+        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
     </row>
@@ -3508,7 +3747,7 @@
         </is>
       </c>
       <c r="C16" s="11">
-        <f>Assumptions!$C$48/Assumptions!$C$46</f>
+        <f>Assumptions!$C$54/Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -3720,11 +3959,11 @@
         </is>
       </c>
       <c r="B12" s="47">
-        <f>Assumptions!$C$46/'Income Statement'!D21</f>
+        <f>Assumptions!$C$52/'Income Statement'!D21</f>
         <v/>
       </c>
       <c r="C12" s="47">
-        <f>(DCF!C14+Assumptions!$C$59-Assumptions!$C$60)/('Income Statement'!D9+'Income Statement'!D12)</f>
+        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
       <c r="D12" s="48" t="inlineStr">
@@ -3827,17 +4066,17 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.8120922184796022</v>
+        <v>0.4703575469948413</v>
       </c>
       <c r="C5" s="8">
         <f>'Fundamental Valuation'!C5</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7.532643851437822</v>
+        <v>7.228322439161341</v>
       </c>
       <c r="E5" s="9">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="F5" s="10">
@@ -3868,7 +4107,7 @@
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F6" s="10">
@@ -3899,7 +4138,7 @@
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F7" s="10">
@@ -3930,7 +4169,7 @@
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F8" s="10">
@@ -3945,11 +4184,11 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Weighted central</t>
+          <t>Weighted central (range weighted like the base)</t>
         </is>
       </c>
       <c r="B9" s="13">
-        <f>MIN(B5:B8)</f>
+        <f>B5*E5+B6*E6+B7*E7+B8*E8</f>
         <v/>
       </c>
       <c r="C9" s="13">
@@ -3957,7 +4196,7 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>MAX(D5:D8)</f>
+        <f>D5*E5+D6*E6+D7*E7+D8*E8</f>
         <v/>
       </c>
       <c r="E9" s="14">
@@ -3992,7 +4231,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>C9+Assumptions!$C$67*('SOTP Bridge'!C20-'Fundamental Valuation'!C5)</f>
+        <f>C9+Assumptions!$C$83*('SOTP Bridge'!C20-'Fundamental Valuation'!C5)</f>
         <v/>
       </c>
       <c r="G11" s="11">
@@ -4033,13 +4272,28 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.166584340889459</v>
+        <v>1.855923186986279</v>
       </c>
       <c r="G14" s="11">
         <f>C14/$C$16-1</f>
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Widest single-lens span (the DCF scenarios) — labelled, not the weighted range</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D15" s="10">
+        <f>MAX(D5:D8)</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
@@ -4048,7 +4302,7 @@
       </c>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="16">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D16" s="15" t="n"/>
@@ -4076,7 +4330,7 @@
         </is>
       </c>
       <c r="C19" s="17">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -4164,7 +4418,7 @@
         </is>
       </c>
       <c r="C27" s="9">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -4243,7 +4497,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>7.5x FY2027E EBITDA, discounted</t>
+          <t>6.5x FY2027E EBITDA, discounted</t>
         </is>
       </c>
       <c r="C6" s="8">
@@ -4329,7 +4583,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.166584340889459</v>
+        <v>1.855923186986279</v>
       </c>
     </row>
     <row r="15">
@@ -4339,7 +4593,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.8120922184796022</v>
+        <v>0.4703575469948413</v>
       </c>
     </row>
     <row r="16">
@@ -4349,7 +4603,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.532643851437822</v>
+        <v>7.228322439161341</v>
       </c>
     </row>
     <row r="18">
@@ -4368,49 +4622,55 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Expert 1 — earnings power at a justified multiple</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>4.153316563596437</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>3.125628125843413</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>5.181005001349461</v>
+          <t>Expert 1 — earnings power at a justified multiple (live formula)</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>13*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53)*DCF!C61-Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>10*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53)*DCF!C61-Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>16*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53)*DCF!C61-Assumptions!$C$54</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Expert 2 — owner cash earnings capitalised</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>3.4458209598253</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>2.652986809248068</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>4.372637418702393</v>
+          <t>Expert 2 — owner cash earnings capitalised (live formula)</t>
+        </is>
+      </c>
+      <c r="C20" s="10">
+        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$81))*(1+Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47)+0.5*(Assumptions!$C$76-Assumptions!$C$75))/Assumptions!$C$53*DCF!C61-Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="D20" s="10">
+        <f>((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$81))*1.015/(0.5*(DCF!C10+DCF!C21)-0.015)/Assumptions!$C$53*DCF!C61-Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$81))*1.035/(DCF!C21-0.035)+2*0.5*(Assumptions!$C$76-Assumptions!$C$75))/Assumptions!$C$53*DCF!C61-Assumptions!$C$54</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Expert 3 — cash returns vs the cost of capital</t>
+          <t>Expert 3 — cash returns vs the cost of capital (whole-model re-run; full chain in Appendix C)</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>3.509409047812734</v>
+        <v>3.461161670069188</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2.706872093860241</v>
+        <v>2.669746136632601</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>4.071429498433575</v>
+        <v>4.006923840645693</v>
       </c>
     </row>
     <row r="23">
@@ -4442,7 +4702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -4665,45 +4925,45 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fuel cost per passenger (AED) — base path</t>
+          <t>Effective jet fuel price (USD/bbl) — base path</t>
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>195</v>
+        <v>100.7</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>165</v>
+        <v>85.2</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>168.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>171.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>175.1</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Fuel cost per passenger (AED) — high-fuel alternative</t>
+          <t>Effective jet fuel price (USD/bbl) — high-fuel alternative</t>
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>210</v>
+        <v>108.4</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>205</v>
+        <v>105.8</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>206</v>
+        <v>106.4</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>208.1</v>
+        <v>107.5</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>210.1</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="14">
@@ -4907,560 +5167,780 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Marginal cost of debt path</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="D23" s="27" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="E23" s="27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>0.05</v>
+          <t>Owned aircraft additions (units)</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Deposit yield path</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="C24" s="27" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="D24" s="27" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>0.037</v>
+          <t>Leased aircraft additions (units)</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of joint-venture and associate profit</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C25" s="25" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D25" s="25" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E25" s="25" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F25" s="25" t="n">
-        <v>0.12</v>
+          <t>Consolidated fleet, year-end (aircraft)</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Dividend payout ratio</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F26" s="25" t="n">
-        <v>0.85</v>
+          <t>Booked finance-cost rate on the debt book</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="D26" s="27" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>0.037</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Debt amortisation (AED mn)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>520</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>540</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>560</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Scalar driver</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Marginal cost of debt path</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="D28" s="27" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Selling &amp; marketing / revenue</t>
-        </is>
+          <t>Deposit yield path</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="n">
+        <v>0.041</v>
       </c>
       <c r="C29" s="27" t="n">
-        <v>0.0146</v>
+        <v>0.038</v>
+      </c>
+      <c r="D29" s="27" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
-        </is>
+          <t>Growth in the share of joint-venture and associate profit</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>0.02</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>-0.64</v>
+        <v>0.18</v>
+      </c>
+      <c r="D30" s="25" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F30" s="25" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Tax rate</t>
-        </is>
+          <t>Dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>AED government bond yield (January-2031 tranche)</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="n">
-        <v>0.0448</v>
+        <v>0.9</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Sovereign default spread (netted out)</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="n">
-        <v>0.0042</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Scalar driver</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Beta (five-year weekly, vs the Dubai index)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>1.086</v>
+          <t>Selling &amp; marketing / revenue</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="n">
-        <v>0.0487</v>
+          <t>Working capital / revenue</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="C36" s="27" t="n">
-        <v>0.04</v>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>AED government bond yield (January-2031 tranche)</t>
         </is>
       </c>
       <c r="C37" s="27" t="n">
-        <v>0.0475</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Marginal cost of debt</t>
+          <t>Observed sovereign spread at the auction (netted out)</t>
         </is>
       </c>
       <c r="C38" s="27" t="n">
-        <v>0.055</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Rating-table sovereign spread (alternative netting, disclosed)</t>
         </is>
       </c>
       <c r="C39" s="27" t="n">
-        <v>0.05</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="n">
-        <v>0.1</v>
+          <t>Beta (five-year weekly, vs the Dubai index)</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>1.086</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C41" s="25" t="n">
-        <v>0.025</v>
+          <t>Equity risk premium</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="n">
+        <v>0.0487</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Joint-venture capitalisation multiple</t>
-        </is>
-      </c>
-      <c r="C42" s="28" t="n">
-        <v>15</v>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="n">
-        <v>7.5</v>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>0.0475</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="n">
-        <v>13</v>
+          <t>Marginal cost of debt</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C45" s="25" t="n">
-        <v>0.18</v>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Spot price (AED)</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>5.24</v>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="n">
-        <v>4666.7</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share (AED, approved 12 March 2026)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>0.3</v>
+          <t>Joint-venture capitalisation multiple</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Days from 31-Dec-2025 to the 7-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="n">
-        <v>219</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Leased-fleet asset additions net of their depreciation (AED mn / year)</t>
-        </is>
-      </c>
-      <c r="C50" s="26" t="n">
-        <v>300</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Cash administrative costs, FY2025 (AED mn, audited less its depreciation)</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="n">
-        <v>276.183</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Cargo revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="n">
-        <v>186.948</v>
+          <t>Spot price (AED)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>5.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Service revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="n">
-        <v>223.323</v>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="n">
+        <v>4666.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Hotel revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="n">
-        <v>59.842</v>
+          <t>FY2025 dividend per share (AED, approved 12 March 2026)</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Aircraft-lease revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="n">
-        <v>219.755</v>
+          <t>Days from 31-Dec-2025 to the 7-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Other income, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="n">
-        <v>197.132</v>
+          <t>Fuel intensity (AED per passenger per USD/bbl of effective jet price)</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>1.937</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Share of JV and associate profit, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="n">
-        <v>189.975</v>
+          <t>Right-of-use value per leased aircraft (AED mn)</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Working capital, FY2025 (AED mn, audited balance sheet)</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="n">
-        <v>-5186.834</v>
+          <t>Loan drawn per owned aircraft (AED mn)</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Gross debt, FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="n">
-        <v>2781.435</v>
+          <t>Dividend floor (AED mn = 30 fils on the full share count)</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Cash and fixed deposits, FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="n">
-        <v>5198.732</v>
+          <t>Minority interests at carrying value (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>1.287</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Fleet assets, FY2025 (PP&amp;E + right-of-use + aircraft advances, AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="n">
-        <v>8670.864</v>
+          <t>Scenario: passenger multiplier</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="n">
-        <v>1362.497</v>
+          <t>Scenario: fare multiplier</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>JV and associates at carrying value (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C63" s="24" t="n">
-        <v>363.386</v>
+          <t>Scenario: fuel multiplier</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Non-operating assets (investments + investment property + net investment in lease, AED mn)</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="n">
-        <v>1069.284</v>
+          <t>Scenario: capital-expenditure multiplier</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Minority share of profit</t>
-        </is>
-      </c>
-      <c r="C65" s="29" t="n">
-        <v>0.0001596330894835507</v>
+          <t>Scenario: cost-of-capital shift</t>
+        </is>
+      </c>
+      <c r="C65" s="27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to owners, FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C66" s="24" t="n">
-        <v>8408.904</v>
+          <t>Scenario: high-fuel switch (0 = base path, 1 = alternative)</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C67" s="25" t="n">
-        <v>0.45</v>
+          <t>Cash administrative costs, FY2025 (AED mn, audited less its depreciation)</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="n">
+        <v>276.183</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C68" s="25" t="n">
-        <v>0.2</v>
+          <t>Cargo revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="n">
+        <v>186.948</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C69" s="25" t="n">
-        <v>0.2</v>
+          <t>Service revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="n">
+        <v>223.323</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C70" s="25" t="n">
-        <v>0.15</v>
+          <t>Hotel revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="n">
+        <v>59.842</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Relative lens — bear multiple</t>
-        </is>
-      </c>
-      <c r="C71" s="28" t="n">
-        <v>6</v>
+          <t>Aircraft-lease revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="n">
+        <v>219.755</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Relative lens — bull multiple</t>
-        </is>
-      </c>
-      <c r="C72" s="28" t="n">
-        <v>9</v>
+          <t>Other income, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="n">
+        <v>197.132</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Normalised lens — bear P/E</t>
-        </is>
-      </c>
-      <c r="C73" s="28" t="n">
-        <v>10</v>
+          <t>Share of JV and associate profit, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="n">
+        <v>189.975</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
+          <t>Working capital, FY2025 (AED mn, audited balance sheet)</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="n">
+        <v>-5186.834</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Gross debt, FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="n">
+        <v>2781.435</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Cash and fixed deposits, FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="n">
+        <v>5198.732</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Fleet assets, FY2025 (PP&amp;E + right-of-use + aircraft advances, AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="n">
+        <v>8670.864</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="n">
+        <v>1362.497</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>JV and associates at carrying value (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="n">
+        <v>363.386</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Non-operating assets (investments + investment property + net investment in lease, AED mn)</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="n">
+        <v>1069.284</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Minority share of profit</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="n">
+        <v>0.0001596330894835507</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners, FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="n">
+        <v>8408.904</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Weight — book</t>
+        </is>
+      </c>
+      <c r="C86" s="25" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Relative lens — bear multiple</t>
+        </is>
+      </c>
+      <c r="C87" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Relative lens — bull multiple</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Normalised lens — bear P/E</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
           <t>Normalised lens — bull P/E</t>
         </is>
       </c>
-      <c r="C74" s="28" t="n">
+      <c r="C90" s="28" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5537,8 +6017,8 @@
           <t>plus net cash (cash + deposits - borrowings - leases)</t>
         </is>
       </c>
-      <c r="C6" s="30">
-        <f>Assumptions!$C$60-Assumptions!$C$59</f>
+      <c r="C6" s="31">
+        <f>Assumptions!$C$76-Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -5549,7 +6029,7 @@
         </is>
       </c>
       <c r="C7" s="17">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -5560,7 +6040,7 @@
         </is>
       </c>
       <c r="C8" s="17">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -5570,30 +6050,19 @@
           <t>Equity before minorities</t>
         </is>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Minority share of group profit</t>
-        </is>
-      </c>
-      <c r="C10" s="32">
-        <f>Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>less minorities</t>
+          <t>less minorities at audited carrying value</t>
         </is>
       </c>
       <c r="C11" s="33">
-        <f>C9*C10</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -5603,7 +6072,7 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>C9-C11</f>
         <v/>
       </c>
@@ -5615,18 +6084,18 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>C13/Assumptions!$C$47</f>
+        <f>C13/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>Per share at the 7-Aug-2026 anchor</t>
+          <t>Per share at the anchor — operating equity rolled at the cost of equity, cash and near-cash legs at the deposit yield</t>
         </is>
       </c>
       <c r="C15" s="21">
-        <f>C14*DCF!C61-Assumptions!$C$48</f>
+        <f>(C5*DCF!C61+(C6+C7+C8)*DCF!C63-C11)/Assumptions!$C$53-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -5649,8 +6118,8 @@
           <t>JV network capitalised (multiple x FY2025 profit share)</t>
         </is>
       </c>
-      <c r="C18" s="30">
-        <f>Assumptions!$C$42*Assumptions!$C$57</f>
+      <c r="C18" s="31">
+        <f>Assumptions!$C$48*Assumptions!$C$73</f>
         <v/>
       </c>
     </row>
@@ -5660,8 +6129,8 @@
           <t>Equity attributable on this framing</t>
         </is>
       </c>
-      <c r="C19" s="30">
-        <f>(C5+C6+C7+C18)*(1-C10)</f>
+      <c r="C19" s="31">
+        <f>C5+C6+C7+C18-C11</f>
         <v/>
       </c>
     </row>
@@ -5672,7 +6141,7 @@
         </is>
       </c>
       <c r="C20" s="21">
-        <f>(C19/Assumptions!$C$47)*DCF!C61-Assumptions!$C$48</f>
+        <f>(C5*DCF!C61+(C6+C7+C18)*DCF!C63-C11)/Assumptions!$C$53-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -5821,23 +6290,23 @@
         </is>
       </c>
       <c r="B5" s="35">
-        <f>Assumptions!B5</f>
+        <f>Assumptions!B5*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="C5" s="35">
-        <f>Assumptions!C5</f>
+        <f>Assumptions!C5*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="D5" s="35">
-        <f>Assumptions!D5</f>
+        <f>Assumptions!D5*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="E5" s="35">
-        <f>Assumptions!E5</f>
+        <f>Assumptions!E5*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>Assumptions!F5</f>
+        <f>Assumptions!F5*Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -5848,23 +6317,23 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <f>Assumptions!B6</f>
+        <f>Assumptions!B6*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>Assumptions!C6</f>
+        <f>Assumptions!C6*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>Assumptions!D6</f>
+        <f>Assumptions!D6*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>Assumptions!E6</f>
+        <f>Assumptions!E6*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="F6" s="36">
-        <f>Assumptions!F6</f>
+        <f>Assumptions!F6*Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
@@ -5874,23 +6343,23 @@
           <t>Passenger and baggage revenue</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>F5*F6</f>
         <v/>
       </c>
@@ -5901,23 +6370,23 @@
           <t>Ancillary rate (AED per passenger)</t>
         </is>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="37">
         <f>Assumptions!D7</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>Assumptions!E7</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="37">
         <f>Assumptions!F7</f>
         <v/>
       </c>
@@ -5928,23 +6397,23 @@
           <t>Ancillary revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>B5*B8</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>C5*C8</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>D5*D8</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>E5*E8</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>F5*F8</f>
         <v/>
       </c>
@@ -5955,23 +6424,23 @@
           <t>Cargo revenue</t>
         </is>
       </c>
-      <c r="B10" s="33">
-        <f>Assumptions!$C$52*(1+Assumptions!B8)</f>
-        <v/>
-      </c>
-      <c r="C10" s="33">
+      <c r="B10" s="36">
+        <f>Assumptions!$C$68*(1+Assumptions!B8)</f>
+        <v/>
+      </c>
+      <c r="C10" s="36">
         <f>B10*(1+Assumptions!C8)</f>
         <v/>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="36">
         <f>C10*(1+Assumptions!D8)</f>
         <v/>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="36">
         <f>D10*(1+Assumptions!E8)</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="36">
         <f>E10*(1+Assumptions!F8)</f>
         <v/>
       </c>
@@ -5982,23 +6451,23 @@
           <t>Service revenue</t>
         </is>
       </c>
-      <c r="B11" s="33">
-        <f>Assumptions!$C$53*(1+Assumptions!B9)</f>
-        <v/>
-      </c>
-      <c r="C11" s="33">
+      <c r="B11" s="36">
+        <f>Assumptions!$C$69*(1+Assumptions!B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="36">
         <f>B11*(1+Assumptions!C9)</f>
         <v/>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="36">
         <f>C11*(1+Assumptions!D9)</f>
         <v/>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="36">
         <f>D11*(1+Assumptions!E9)</f>
         <v/>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="36">
         <f>E11*(1+Assumptions!F9)</f>
         <v/>
       </c>
@@ -6009,23 +6478,23 @@
           <t>Hotel revenue</t>
         </is>
       </c>
-      <c r="B12" s="33">
-        <f>Assumptions!$C$54*(1+Assumptions!B10)</f>
-        <v/>
-      </c>
-      <c r="C12" s="33">
+      <c r="B12" s="36">
+        <f>Assumptions!$C$70*(1+Assumptions!B10)</f>
+        <v/>
+      </c>
+      <c r="C12" s="36">
         <f>B12*(1+Assumptions!C10)</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="36">
         <f>C12*(1+Assumptions!D10)</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="36">
         <f>D12*(1+Assumptions!E10)</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="36">
         <f>E12*(1+Assumptions!F10)</f>
         <v/>
       </c>
@@ -6036,23 +6505,23 @@
           <t>Aircraft-lease revenue (JV network)</t>
         </is>
       </c>
-      <c r="B13" s="33">
-        <f>Assumptions!$C$55*(1+Assumptions!B11)</f>
-        <v/>
-      </c>
-      <c r="C13" s="33">
+      <c r="B13" s="36">
+        <f>Assumptions!$C$71*(1+Assumptions!B11)</f>
+        <v/>
+      </c>
+      <c r="C13" s="36">
         <f>B13*(1+Assumptions!C11)</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="36">
         <f>C13*(1+Assumptions!D11)</f>
         <v/>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="36">
         <f>D13*(1+Assumptions!E11)</f>
         <v/>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="36">
         <f>E13*(1+Assumptions!F11)</f>
         <v/>
       </c>
@@ -6063,23 +6532,23 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>B7+B9+B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C7+C9+C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D7+D9+D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E7+E9+E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F7+F9+F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -6119,27 +6588,27 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Fuel (base path)</t>
+          <t>Fuel cost per passenger (intensity x effective jet price)</t>
         </is>
       </c>
       <c r="B17" s="36">
-        <f>Assumptions!B12</f>
+        <f>Assumptions!$C$56*(Assumptions!B12*(1-Assumptions!$C$66)+Assumptions!B13*Assumptions!$C$66)*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="C17" s="36">
-        <f>Assumptions!C12</f>
+        <f>Assumptions!$C$56*(Assumptions!C12*(1-Assumptions!$C$66)+Assumptions!C13*Assumptions!$C$66)*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="D17" s="36">
-        <f>Assumptions!D12</f>
+        <f>Assumptions!$C$56*(Assumptions!D12*(1-Assumptions!$C$66)+Assumptions!D13*Assumptions!$C$66)*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="E17" s="36">
-        <f>Assumptions!E12</f>
+        <f>Assumptions!$C$56*(Assumptions!E12*(1-Assumptions!$C$66)+Assumptions!E13*Assumptions!$C$66)*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>Assumptions!F12</f>
+        <f>Assumptions!$C$56*(Assumptions!F12*(1-Assumptions!$C$66)+Assumptions!F13*Assumptions!$C$66)*Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6149,23 +6618,23 @@
           <t>Staff</t>
         </is>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="37">
         <f>Assumptions!B14</f>
         <v/>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="37">
         <f>Assumptions!C14</f>
         <v/>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="37">
         <f>Assumptions!D14</f>
         <v/>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="37">
         <f>Assumptions!E14</f>
         <v/>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="37">
         <f>Assumptions!F14</f>
         <v/>
       </c>
@@ -6176,23 +6645,23 @@
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B19" s="36">
+      <c r="B19" s="37">
         <f>Assumptions!B15</f>
         <v/>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="37">
         <f>Assumptions!C15</f>
         <v/>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <f>Assumptions!D15</f>
         <v/>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <f>Assumptions!E15</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <f>Assumptions!F15</f>
         <v/>
       </c>
@@ -6203,23 +6672,23 @@
           <t>Landing &amp; overflying</t>
         </is>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="37">
         <f>Assumptions!B16</f>
         <v/>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="37">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="37">
         <f>Assumptions!D16</f>
         <v/>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="37">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="37">
         <f>Assumptions!F16</f>
         <v/>
       </c>
@@ -6230,23 +6699,23 @@
           <t>Handling</t>
         </is>
       </c>
-      <c r="B21" s="36">
+      <c r="B21" s="37">
         <f>Assumptions!B17</f>
         <v/>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="37">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="37">
         <f>Assumptions!D17</f>
         <v/>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="37">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="37">
         <f>Assumptions!F17</f>
         <v/>
       </c>
@@ -6257,23 +6726,23 @@
           <t>Other direct</t>
         </is>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="37">
         <f>Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="37">
         <f>Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="37">
         <f>Assumptions!D18</f>
         <v/>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="37">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="37">
         <f>Assumptions!F18</f>
         <v/>
       </c>
@@ -6311,23 +6780,23 @@
           <t>Direct cash operating costs (AED mn)</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>B5*B23</f>
         <v/>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>C5*C23</f>
         <v/>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>D5*D23</f>
         <v/>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <f>E5*E23</f>
         <v/>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <f>F5*F23</f>
         <v/>
       </c>
@@ -6338,23 +6807,23 @@
           <t>Administrative costs (cash)</t>
         </is>
       </c>
-      <c r="B25" s="33">
-        <f>Assumptions!$C$51*(1+Assumptions!B19)</f>
-        <v/>
-      </c>
-      <c r="C25" s="33">
+      <c r="B25" s="36">
+        <f>Assumptions!$C$67*(1+Assumptions!B19)</f>
+        <v/>
+      </c>
+      <c r="C25" s="36">
         <f>B25*(1+Assumptions!C19)</f>
         <v/>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="36">
         <f>C25*(1+Assumptions!D19)</f>
         <v/>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="36">
         <f>D25*(1+Assumptions!E19)</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="36">
         <f>E25*(1+Assumptions!F19)</f>
         <v/>
       </c>
@@ -6365,24 +6834,24 @@
           <t>Selling &amp; marketing</t>
         </is>
       </c>
-      <c r="B26" s="33">
-        <f>Assumptions!$C$29*B14</f>
-        <v/>
-      </c>
-      <c r="C26" s="33">
-        <f>Assumptions!$C$29*C14</f>
-        <v/>
-      </c>
-      <c r="D26" s="33">
-        <f>Assumptions!$C$29*D14</f>
-        <v/>
-      </c>
-      <c r="E26" s="33">
-        <f>Assumptions!$C$29*E14</f>
-        <v/>
-      </c>
-      <c r="F26" s="33">
-        <f>Assumptions!$C$29*F14</f>
+      <c r="B26" s="36">
+        <f>Assumptions!$C$34*B14</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>Assumptions!$C$34*C14</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>Assumptions!$C$34*D14</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>Assumptions!$C$34*E14</f>
+        <v/>
+      </c>
+      <c r="F26" s="36">
+        <f>Assumptions!$C$34*F14</f>
         <v/>
       </c>
     </row>
@@ -6392,23 +6861,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <f>B14-B24-B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>C14-C24-C25-C26</f>
         <v/>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <f>D14-D24-D25-D26</f>
         <v/>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <f>E14-E24-E25-E26</f>
         <v/>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <f>F14-F24-F25-F26</f>
         <v/>
       </c>
@@ -6419,23 +6888,23 @@
           <t>Other income (management fees from the JV network and misc.)</t>
         </is>
       </c>
-      <c r="B28" s="33">
-        <f>Assumptions!$C$56*(1+Assumptions!B20)</f>
-        <v/>
-      </c>
-      <c r="C28" s="33">
+      <c r="B28" s="36">
+        <f>Assumptions!$C$72*(1+Assumptions!B20)</f>
+        <v/>
+      </c>
+      <c r="C28" s="36">
         <f>B28*(1+Assumptions!C20)</f>
         <v/>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="36">
         <f>C28*(1+Assumptions!D20)</f>
         <v/>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="36">
         <f>D28*(1+Assumptions!E20)</f>
         <v/>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="36">
         <f>E28*(1+Assumptions!F20)</f>
         <v/>
       </c>
@@ -6446,23 +6915,23 @@
           <t>EBITDA including fees and other income</t>
         </is>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <f>C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="32">
         <f>D27+D28</f>
         <v/>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="32">
         <f>E27+E28</f>
         <v/>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="32">
         <f>F27+F28</f>
         <v/>
       </c>
@@ -6682,7 +7151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6723,99 +7192,99 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>FY2027E EBITDA incl. fees and other income (AED mn)</t>
+          <t>FY2027E EBITDA EXCLUDING fees/other income (AED mn) — peer basis</t>
         </is>
       </c>
       <c r="C5" s="17">
-        <f>Segments!C29</f>
+        <f>Segments!C27</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C6" s="37">
-        <f>Assumptions!$C$43</f>
+          <t>Justified EV/EBITDA (peer median, primary filings)</t>
+        </is>
+      </c>
+      <c r="C6" s="38">
+        <f>Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Enterprise value at end-FY2027</t>
-        </is>
-      </c>
-      <c r="C7" s="30">
-        <f>C5*C6</f>
+          <t>Fee/other-income stream valued separately (after-tax annuity)</t>
+        </is>
+      </c>
+      <c r="C7" s="31">
+        <f>Segments!C28*(1-Assumptions!$C$36)/(DCF!C24-Assumptions!$C$47)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Year-2 discount factor</t>
-        </is>
-      </c>
-      <c r="C8" s="38">
-        <f>DCF!C30</f>
+          <t>Enterprise value at end-FY2027</t>
+        </is>
+      </c>
+      <c r="C8" s="31">
+        <f>C5*C6+C7</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>PV of FY2026-27 free cash flow</t>
-        </is>
-      </c>
-      <c r="C9" s="17">
-        <f>DCF!B44+DCF!C44</f>
+          <t>Year-2 discount factor</t>
+        </is>
+      </c>
+      <c r="C9" s="39">
+        <f>DCF!C30</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Enterprise value at 31-Dec-2025</t>
-        </is>
-      </c>
-      <c r="C10" s="30">
-        <f>C7*C8+C9</f>
+          <t>PV of FY2026-27 free cash flow</t>
+        </is>
+      </c>
+      <c r="C10" s="17">
+        <f>DCF!B44+DCF!C44</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Implied value per share at the anchor</t>
+          <t>Implied value per share at the anchor (split roll)</t>
         </is>
       </c>
       <c r="C11" s="21">
-        <f>(C10+Assumptions!$C$60-Assumptions!$C$59+Assumptions!$C$64+Assumptions!$C$63)*(1-Assumptions!$C$65)/Assumptions!$C$47*DCF!C61-Assumptions!$C$48</f>
+        <f>((C5*C6+C7)*C9+C10)*DCF!C61/Assumptions!$C$53+((Assumptions!$C$76-Assumptions!$C$75+Assumptions!$C$80+Assumptions!$C$79)*DCF!C63-Assumptions!$C$60)/Assumptions!$C$53-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bear (6.0x)</t>
+          <t>Bear (5.0x)</t>
         </is>
       </c>
       <c r="C12" s="10">
-        <f>(C5*Assumptions!$C$71*C8+C9+Assumptions!$C$60-Assumptions!$C$59+Assumptions!$C$64+Assumptions!$C$63)*(1-Assumptions!$C$65)/Assumptions!$C$47*DCF!C61-Assumptions!$C$48</f>
+        <f>((C5*Assumptions!$C$87+C7)*C9+C10)*DCF!C61/Assumptions!$C$53+((Assumptions!$C$76-Assumptions!$C$75+Assumptions!$C$80+Assumptions!$C$79)*DCF!C63-Assumptions!$C$60)/Assumptions!$C$53-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Bull (9.0x)</t>
+          <t>Bull (8.0x)</t>
         </is>
       </c>
       <c r="C13" s="10">
-        <f>(C5*Assumptions!$C$72*C8+C9+Assumptions!$C$60-Assumptions!$C$59+Assumptions!$C$64+Assumptions!$C$63)*(1-Assumptions!$C$65)/Assumptions!$C$47*DCF!C61-Assumptions!$C$48</f>
+        <f>((C5*Assumptions!$C$88+C7)*C9+C10)*DCF!C61/Assumptions!$C$53+((Assumptions!$C$76-Assumptions!$C$75+Assumptions!$C$80+Assumptions!$C$79)*DCF!C63-Assumptions!$C$60)/Assumptions!$C$53-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -6829,11 +7298,11 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>EV / FY2025 EBITDA at spot</t>
-        </is>
-      </c>
-      <c r="C16" s="39">
-        <f>(DCF!C14+Assumptions!$C$59-Assumptions!$C$60)/'Income Statement'!D9</f>
+          <t>EV / FY2025 EBITDA at spot — EX fees (peer basis)</t>
+        </is>
+      </c>
+      <c r="C16" s="40">
+        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
@@ -6843,8 +7312,19 @@
           <t>Price / FY2025 earnings at spot</t>
         </is>
       </c>
-      <c r="C17" s="39">
-        <f>Assumptions!$C$46/'Income Statement'!D21</f>
+      <c r="C17" s="40">
+        <f>Assumptions!$C$52/'Income Statement'!D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>EV / FY2025 EBITDA at spot — INCLUDING fees (both bases published)</t>
+        </is>
+      </c>
+      <c r="C18" s="40">
+        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
     </row>
@@ -6889,7 +7369,7 @@
           <t>Normalised EBITDA incl. fees and other income</t>
         </is>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>C21*C22+Segments!B28</f>
         <v/>
       </c>
@@ -6911,7 +7391,7 @@
           <t>Normalised EBIT</t>
         </is>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <f>C23-C24</f>
         <v/>
       </c>
@@ -6922,7 +7402,7 @@
           <t>Net finance income (FY2026E)</t>
         </is>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="37">
         <f>'Cash Flow'!B13-'Cash Flow'!B14</f>
         <v/>
       </c>
@@ -6930,22 +7410,18 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Share of JV and associate profit (FY2026E)</t>
-        </is>
-      </c>
-      <c r="C27" s="36">
-        <f>'Income Statement'!E15</f>
-        <v/>
+          <t>JV share EXCLUDED from the multiplied base (enters at book below) — the base framing carries the JV at carrying value in every lens</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Normalised earnings per share</t>
-        </is>
-      </c>
-      <c r="C28" s="40">
-        <f>(C25+C26+C27)*(1-Assumptions!$C$31)*(1-Assumptions!$C$65)/Assumptions!$C$47</f>
+          <t>Normalised earnings per share (ex-JV)</t>
+        </is>
+      </c>
+      <c r="C28" s="41">
+        <f>(C25+C26)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -6956,7 +7432,7 @@
         </is>
       </c>
       <c r="C29" s="21">
-        <f>Assumptions!$C$44*C28*DCF!C61-Assumptions!$C$48</f>
+        <f>Assumptions!$C$50*C28*DCF!C61+Assumptions!$C$79/Assumptions!$C$53*DCF!C63-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -6967,7 +7443,7 @@
         </is>
       </c>
       <c r="C31" s="10">
-        <f>Assumptions!$C$73*C28*DCF!C61-Assumptions!$C$48</f>
+        <f>Assumptions!$C$89*C28*DCF!C61+Assumptions!$C$79/Assumptions!$C$53*DCF!C63-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -6978,7 +7454,7 @@
         </is>
       </c>
       <c r="C32" s="10">
-        <f>Assumptions!$C$74*C28*DCF!C61-Assumptions!$C$48</f>
+        <f>Assumptions!$C$90*C28*DCF!C61+Assumptions!$C$79/Assumptions!$C$53*DCF!C63-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7002,7 +7478,7 @@
         </is>
       </c>
       <c r="C36" s="10">
-        <f>Assumptions!$C$66/Assumptions!$C$47</f>
+        <f>Assumptions!$C$82/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -7013,7 +7489,7 @@
         </is>
       </c>
       <c r="C37" s="21">
-        <f>((Assumptions!$C$45-Assumptions!$C$41)/(DCF!C21-Assumptions!$C$41))*C36*DCF!C61-Assumptions!$C$48</f>
+        <f>((Assumptions!$C$51-Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47))*C36*DCF!C61-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7023,8 +7499,8 @@
           <t>Justified P/B multiple</t>
         </is>
       </c>
-      <c r="C38" s="39">
-        <f>(Assumptions!$C$45-Assumptions!$C$41)/(DCF!C21-Assumptions!$C$41)</f>
+      <c r="C38" s="40">
+        <f>(Assumptions!$C$51-Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47)</f>
         <v/>
       </c>
     </row>
@@ -7035,7 +7511,7 @@
         </is>
       </c>
       <c r="C39" s="10">
-        <f>((Assumptions!$C$45-0.02)/(0.5*(DCF!C10+DCF!C21)-0.015))*C36*DCF!C61-Assumptions!$C$48</f>
+        <f>((Assumptions!$C$51-0.02-0.015)/(0.5*(DCF!C10+DCF!C21)-0.015))*C36*DCF!C61-Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7046,8 +7522,15 @@
         </is>
       </c>
       <c r="C40" s="10">
-        <f>((Assumptions!$C$45+0.02-Assumptions!$C$41)/(DCF!C21-Assumptions!$C$41))*C36*DCF!C61-Assumptions!$C$48</f>
-        <v/>
+        <f>((Assumptions!$C$51+0.02-Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47))*C36*DCF!C61-Assumptions!$C$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>The bear leg holds the same Gordon identity as base and bull: (ROE_bear - g_bear)/(k_bear - g_bear).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7061,7 +7544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7109,18 +7592,18 @@
         </is>
       </c>
       <c r="C5" s="18">
-        <f>Assumptions!$C$32</f>
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>less sovereign default spread</t>
+          <t>less the observed auction spread over US Treasuries</t>
         </is>
       </c>
       <c r="C6" s="18">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -7130,7 +7613,7 @@
           <t>Net risk-free rate</t>
         </is>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="42">
         <f>C5-C6</f>
         <v/>
       </c>
@@ -7141,8 +7624,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C8" s="35">
-        <f>Assumptions!$C$34</f>
+      <c r="C8" s="33">
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -7153,7 +7636,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$41</f>
         <v/>
       </c>
     </row>
@@ -7163,7 +7646,7 @@
           <t>Cost of equity</t>
         </is>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="43">
         <f>C7+C8*C9</f>
         <v/>
       </c>
@@ -7175,7 +7658,7 @@
         </is>
       </c>
       <c r="C11" s="18">
-        <f>Assumptions!$C$38</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
@@ -7186,7 +7669,7 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>Assumptions!$C$31</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -7196,7 +7679,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="42">
         <f>C11*(1-C12)</f>
         <v/>
       </c>
@@ -7207,8 +7690,8 @@
           <t>Market capitalisation (AED mn)</t>
         </is>
       </c>
-      <c r="C14" s="30">
-        <f>Assumptions!$C$46*Assumptions!$C$47</f>
+      <c r="C14" s="31">
+        <f>Assumptions!$C$52*Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -7218,8 +7701,8 @@
           <t>Gross debt (audited)</t>
         </is>
       </c>
-      <c r="C15" s="36">
-        <f>Assumptions!$C$59</f>
+      <c r="C15" s="37">
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -7229,7 +7712,7 @@
           <t>Debt weight (gross)</t>
         </is>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="42">
         <f>C15/(C15+C14)</f>
         <v/>
       </c>
@@ -7240,8 +7723,8 @@
           <t>Cost of capital — explicit window</t>
         </is>
       </c>
-      <c r="C17" s="42">
-        <f>(1-C16)*C10+C16*C13</f>
+      <c r="C17" s="43">
+        <f>(1-C16)*C10+C16*C13+Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -7259,7 +7742,7 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>Assumptions!$C$36</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
@@ -7269,8 +7752,8 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C21" s="41">
-        <f>C20+Assumptions!$C$34*Assumptions!$C$37</f>
+      <c r="C21" s="42">
+        <f>C20+Assumptions!$C$40*Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -7280,8 +7763,8 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C22" s="41">
-        <f>Assumptions!$C$39*(1-C12)</f>
+      <c r="C22" s="42">
+        <f>Assumptions!$C$45*(1-C12)</f>
         <v/>
       </c>
     </row>
@@ -7292,7 +7775,7 @@
         </is>
       </c>
       <c r="C23" s="9">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -7302,8 +7785,8 @@
           <t>Cost of capital — terminal</t>
         </is>
       </c>
-      <c r="C24" s="42">
-        <f>(1-C23)*C21+C23*C22</f>
+      <c r="C24" s="43">
+        <f>(1-C23)*C21+C23*C22+Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -7346,23 +7829,23 @@
         </is>
       </c>
       <c r="B27" s="18">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B28</f>
         <v/>
       </c>
       <c r="C27" s="18">
-        <f>Assumptions!C23</f>
+        <f>Assumptions!C28</f>
         <v/>
       </c>
       <c r="D27" s="18">
-        <f>Assumptions!D23</f>
+        <f>Assumptions!D28</f>
         <v/>
       </c>
       <c r="E27" s="18">
-        <f>Assumptions!E23</f>
+        <f>Assumptions!E28</f>
         <v/>
       </c>
       <c r="F27" s="18">
-        <f>Assumptions!F23</f>
+        <f>Assumptions!F28</f>
         <v/>
       </c>
     </row>
@@ -7372,24 +7855,24 @@
           <t>Glide fraction (path progress)</t>
         </is>
       </c>
-      <c r="B28" s="43">
-        <f>(Assumptions!$B23-B27)/(Assumptions!B23-Assumptions!F23)</f>
-        <v/>
-      </c>
-      <c r="C28" s="43">
-        <f>(Assumptions!$B23-C27)/(Assumptions!B23-Assumptions!F23)</f>
-        <v/>
-      </c>
-      <c r="D28" s="43">
-        <f>(Assumptions!$B23-D27)/(Assumptions!B23-Assumptions!F23)</f>
-        <v/>
-      </c>
-      <c r="E28" s="43">
-        <f>(Assumptions!$B23-E27)/(Assumptions!B23-Assumptions!F23)</f>
-        <v/>
-      </c>
-      <c r="F28" s="43">
-        <f>(Assumptions!$B23-F27)/(Assumptions!B23-Assumptions!F23)</f>
+      <c r="B28" s="44">
+        <f>(Assumptions!$B28-B27)/(Assumptions!B28-Assumptions!F28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="44">
+        <f>(Assumptions!$B28-C27)/(Assumptions!B28-Assumptions!F28)</f>
+        <v/>
+      </c>
+      <c r="D28" s="44">
+        <f>(Assumptions!$B28-D27)/(Assumptions!B28-Assumptions!F28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="44">
+        <f>(Assumptions!$B28-E27)/(Assumptions!B28-Assumptions!F28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="44">
+        <f>(Assumptions!$B28-F27)/(Assumptions!B28-Assumptions!F28)</f>
         <v/>
       </c>
     </row>
@@ -7399,23 +7882,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B29" s="41">
+      <c r="B29" s="42">
         <f>$C$17-($C$17-$C$24)*B28</f>
         <v/>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="42">
         <f>$C$17-($C$17-$C$24)*C28</f>
         <v/>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="42">
         <f>$C$17-($C$17-$C$24)*D28</f>
         <v/>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="42">
         <f>$C$17-($C$17-$C$24)*E28</f>
         <v/>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="42">
         <f>$C$17-($C$17-$C$24)*F28</f>
         <v/>
       </c>
@@ -7426,23 +7909,23 @@
           <t>Cumulative discount factor</t>
         </is>
       </c>
-      <c r="B30" s="43">
+      <c r="B30" s="44">
         <f>1/(1+B29)</f>
         <v/>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="44">
         <f>B30/(1+C29)</f>
         <v/>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="44">
         <f>C30/(1+D29)</f>
         <v/>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="44">
         <f>D30/(1+E29)</f>
         <v/>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="44">
         <f>E30/(1+F29)</f>
         <v/>
       </c>
@@ -7566,23 +8049,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <f>C34-C35</f>
         <v/>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <f>D34-D35</f>
         <v/>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <f>E34-E35</f>
         <v/>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <f>F34-F35</f>
         <v/>
       </c>
@@ -7593,23 +8076,23 @@
           <t>NOPAT (EBIT x (1 - tax))</t>
         </is>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="31">
         <f>B36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <f>C36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <f>D36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <f>E36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <f>F36*(1-$C$12)</f>
         <v/>
       </c>
@@ -7620,23 +8103,23 @@
           <t>add back depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="31">
         <f>B35</f>
         <v/>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <f>C35</f>
         <v/>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <f>D35</f>
         <v/>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <f>E35</f>
         <v/>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <f>F35</f>
         <v/>
       </c>
@@ -7644,27 +8127,27 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>less capital expenditure</t>
-        </is>
-      </c>
-      <c r="B39" s="17">
-        <f>Assumptions!B22</f>
-        <v/>
-      </c>
-      <c r="C39" s="17">
-        <f>Assumptions!C22</f>
-        <v/>
-      </c>
-      <c r="D39" s="17">
-        <f>Assumptions!D22</f>
-        <v/>
-      </c>
-      <c r="E39" s="17">
-        <f>Assumptions!E22</f>
-        <v/>
-      </c>
-      <c r="F39" s="17">
-        <f>Assumptions!F22</f>
+          <t>less owned capex + pre-delivery payments</t>
+        </is>
+      </c>
+      <c r="B39" s="31">
+        <f>Assumptions!B22*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="C39" s="31">
+        <f>Assumptions!C22*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="D39" s="31">
+        <f>Assumptions!D22*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="E39" s="31">
+        <f>Assumptions!E22*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="F39" s="31">
+        <f>Assumptions!F22*Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -7674,24 +8157,24 @@
           <t>Working capital balance</t>
         </is>
       </c>
-      <c r="B40" s="30">
-        <f>Assumptions!$C$30*B33</f>
-        <v/>
-      </c>
-      <c r="C40" s="30">
-        <f>Assumptions!$C$30*C33</f>
-        <v/>
-      </c>
-      <c r="D40" s="30">
-        <f>Assumptions!$C$30*D33</f>
-        <v/>
-      </c>
-      <c r="E40" s="30">
-        <f>Assumptions!$C$30*E33</f>
-        <v/>
-      </c>
-      <c r="F40" s="30">
-        <f>Assumptions!$C$30*F33</f>
+      <c r="B40" s="31">
+        <f>Assumptions!$C$35*B33</f>
+        <v/>
+      </c>
+      <c r="C40" s="31">
+        <f>Assumptions!$C$35*C33</f>
+        <v/>
+      </c>
+      <c r="D40" s="31">
+        <f>Assumptions!$C$35*D33</f>
+        <v/>
+      </c>
+      <c r="E40" s="31">
+        <f>Assumptions!$C$35*E33</f>
+        <v/>
+      </c>
+      <c r="F40" s="31">
+        <f>Assumptions!$C$35*F33</f>
         <v/>
       </c>
     </row>
@@ -7701,23 +8184,23 @@
           <t>less change in working capital</t>
         </is>
       </c>
-      <c r="B41" s="30">
-        <f>B40-Assumptions!$C$58</f>
-        <v/>
-      </c>
-      <c r="C41" s="30">
+      <c r="B41" s="31">
+        <f>B40-Assumptions!$C$74</f>
+        <v/>
+      </c>
+      <c r="C41" s="31">
         <f>C40-B40</f>
         <v/>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="31">
         <f>D40-C40</f>
         <v/>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="31">
         <f>E40-D40</f>
         <v/>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <f>F40-E40</f>
         <v/>
       </c>
@@ -7728,24 +8211,24 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B42" s="31">
-        <f>B37+B38-B39-B41</f>
-        <v/>
-      </c>
-      <c r="C42" s="31">
-        <f>C37+C38-C39-C41</f>
-        <v/>
-      </c>
-      <c r="D42" s="31">
-        <f>D37+D38-D39-D41</f>
-        <v/>
-      </c>
-      <c r="E42" s="31">
-        <f>E37+E38-E39-E41</f>
-        <v/>
-      </c>
-      <c r="F42" s="31">
-        <f>F37+F38-F39-F41</f>
+      <c r="B42" s="32">
+        <f>B37+B38-B39-B41-B45</f>
+        <v/>
+      </c>
+      <c r="C42" s="32">
+        <f>C37+C38-C39-C41-C45</f>
+        <v/>
+      </c>
+      <c r="D42" s="32">
+        <f>D37+D38-D39-D41-D45</f>
+        <v/>
+      </c>
+      <c r="E42" s="32">
+        <f>E37+E38-E39-E41-E45</f>
+        <v/>
+      </c>
+      <c r="F42" s="32">
+        <f>F37+F38-F39-F41-F45</f>
         <v/>
       </c>
     </row>
@@ -7755,23 +8238,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B43" s="43">
+      <c r="B43" s="44">
         <f>B30</f>
         <v/>
       </c>
-      <c r="C43" s="43">
+      <c r="C43" s="44">
         <f>C30</f>
         <v/>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="44">
         <f>D30</f>
         <v/>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="44">
         <f>E30</f>
         <v/>
       </c>
-      <c r="F43" s="43">
+      <c r="F43" s="44">
         <f>F30</f>
         <v/>
       </c>
@@ -7782,24 +8265,51 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="32">
         <f>B42*B43</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <f>C42*C43</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <f>D42*D43</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <f>E42*E43</f>
         <v/>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <f>F42*F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>less leased-fleet additions (gross right-of-use value)</t>
+        </is>
+      </c>
+      <c r="B45" s="31">
+        <f>Assumptions!B24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="C45" s="31">
+        <f>Assumptions!C24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="D45" s="31">
+        <f>Assumptions!D24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="E45" s="31">
+        <f>Assumptions!E24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="F45" s="31">
+        <f>Assumptions!F24*Assumptions!$C$57*Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -7809,24 +8319,24 @@
           <t>Fleet assets roll-forward</t>
         </is>
       </c>
-      <c r="B46" s="30">
-        <f>Assumptions!$C$61+B39-B35+Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="C46" s="30">
-        <f>B46+C39-C35+Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="D46" s="30">
-        <f>C46+D39-D35+Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="E46" s="30">
-        <f>D46+E39-E35+Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="F46" s="30">
-        <f>E46+F39-F35+Assumptions!$C$50</f>
+      <c r="B46" s="31">
+        <f>Assumptions!$C$77+B39+B45-B35</f>
+        <v/>
+      </c>
+      <c r="C46" s="31">
+        <f>B46+C39+C45-C35</f>
+        <v/>
+      </c>
+      <c r="D46" s="31">
+        <f>C46+D39+D45-D35</f>
+        <v/>
+      </c>
+      <c r="E46" s="31">
+        <f>D46+E39+E45-E35</f>
+        <v/>
+      </c>
+      <c r="F46" s="31">
+        <f>E46+F39+F45-F35</f>
         <v/>
       </c>
     </row>
@@ -7836,24 +8346,24 @@
           <t>Invested capital (fleet + intangibles + working capital)</t>
         </is>
       </c>
-      <c r="B47" s="30">
-        <f>B46+Assumptions!$C$62+B40</f>
-        <v/>
-      </c>
-      <c r="C47" s="30">
-        <f>C46+Assumptions!$C$62+C40</f>
-        <v/>
-      </c>
-      <c r="D47" s="30">
-        <f>D46+Assumptions!$C$62+D40</f>
-        <v/>
-      </c>
-      <c r="E47" s="30">
-        <f>E46+Assumptions!$C$62+E40</f>
-        <v/>
-      </c>
-      <c r="F47" s="30">
-        <f>F46+Assumptions!$C$62+F40</f>
+      <c r="B47" s="31">
+        <f>B46+Assumptions!$C$78+B40</f>
+        <v/>
+      </c>
+      <c r="C47" s="31">
+        <f>C46+Assumptions!$C$78+C40</f>
+        <v/>
+      </c>
+      <c r="D47" s="31">
+        <f>D46+Assumptions!$C$78+D40</f>
+        <v/>
+      </c>
+      <c r="E47" s="31">
+        <f>E46+Assumptions!$C$78+E40</f>
+        <v/>
+      </c>
+      <c r="F47" s="31">
+        <f>F46+Assumptions!$C$78+F40</f>
         <v/>
       </c>
     </row>
@@ -7870,8 +8380,8 @@
           <t>Terminal NOPAT (FY2031E)</t>
         </is>
       </c>
-      <c r="C50" s="33">
-        <f>F37*(1+Assumptions!$C$41)</f>
+      <c r="C50" s="36">
+        <f>F37*(1+Assumptions!$C$47)</f>
         <v/>
       </c>
     </row>
@@ -7881,7 +8391,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C51" s="41">
+      <c r="C51" s="42">
         <f>C50/F47</f>
         <v/>
       </c>
@@ -7892,8 +8402,8 @@
           <t>Reinvestment rate = growth / return on capital</t>
         </is>
       </c>
-      <c r="C52" s="41">
-        <f>Assumptions!$C$41/C51</f>
+      <c r="C52" s="42">
+        <f>Assumptions!$C$47/C51</f>
         <v/>
       </c>
     </row>
@@ -7903,8 +8413,8 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C53" s="30">
-        <f>C50*(1-C52)/(C24-Assumptions!$C$41)</f>
+      <c r="C53" s="31">
+        <f>C50*(1-C52)/(C24-Assumptions!$C$47)</f>
         <v/>
       </c>
     </row>
@@ -7914,7 +8424,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="31">
         <f>C53*F30</f>
         <v/>
       </c>
@@ -7925,7 +8435,7 @@
           <t>PV of explicit years</t>
         </is>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="31">
         <f>SUM(B44:F44)</f>
         <v/>
       </c>
@@ -7936,7 +8446,7 @@
           <t>Enterprise value of the airline</t>
         </is>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <f>C54+C55</f>
         <v/>
       </c>
@@ -7947,7 +8457,7 @@
           <t>Terminal value share of enterprise value</t>
         </is>
       </c>
-      <c r="C57" s="44">
+      <c r="C57" s="45">
         <f>C54/C56</f>
         <v/>
       </c>
@@ -7970,7 +8480,7 @@
         </is>
       </c>
       <c r="C60" s="10">
-        <f>C59/Assumptions!$C$47</f>
+        <f>C59/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -7980,19 +8490,41 @@
           <t>Anchor accretion factor (at the cost of equity)</t>
         </is>
       </c>
-      <c r="C61" s="43">
-        <f>(1+C10)^(Assumptions!$C$49/365)</f>
+      <c r="C61" s="44">
+        <f>(1+C10)^(Assumptions!$C$55/365)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>Fair value per share at the 7-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C62" s="21">
-        <f>C60*C61-Assumptions!$C$48</f>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Per share, whole equity rolled at Ke (single-rate view)</t>
+        </is>
+      </c>
+      <c r="C62" s="10">
+        <f>C60*C61-Assumptions!$C$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Cash-leg accretion factor (deposit yield)</t>
+        </is>
+      </c>
+      <c r="C63" s="44">
+        <f>(1+Assumptions!B29)^(Assumptions!$C$55/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>Fair value per share at the anchor (split roll — the published figure)</t>
+        </is>
+      </c>
+      <c r="C64" s="19">
+        <f>'SOTP Bridge'!C15</f>
         <v/>
       </c>
     </row>
@@ -8175,23 +8707,23 @@
       <c r="D7" s="24" t="n">
         <v>276.1830000000001</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="37">
         <f>Segments!B25</f>
         <v/>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="37">
         <f>Segments!C25</f>
         <v/>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="37">
         <f>Segments!D25</f>
         <v/>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="37">
         <f>Segments!E25</f>
         <v/>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="37">
         <f>Segments!F25</f>
         <v/>
       </c>
@@ -8211,23 +8743,23 @@
       <c r="D8" s="24" t="n">
         <v>113.605</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>Segments!B26</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="37">
         <f>Segments!C26</f>
         <v/>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="37">
         <f>Segments!D26</f>
         <v/>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="37">
         <f>Segments!E26</f>
         <v/>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="37">
         <f>Segments!F26</f>
         <v/>
       </c>
@@ -8238,35 +8770,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>B5-B6-B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>C5-C6-C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>D5-D6-D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>E5-E6-E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>F5-F6-F7-F8</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="32">
         <f>G5-G6-G7-G8</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>H5-H6-H7-H8</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="32">
         <f>I5-I6-I7-I8</f>
         <v/>
       </c>
@@ -8313,35 +8845,35 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>B9-B10</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>C9-C10</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>D9-D10</f>
         <v/>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>E9-E10</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>F9-F10</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>G9-G10</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>H9-H10</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="32">
         <f>I9-I10</f>
         <v/>
       </c>
@@ -8361,23 +8893,23 @@
       <c r="D12" s="24" t="n">
         <v>197.132</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="37">
         <f>Segments!B28</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="37">
         <f>Segments!C28</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="37">
         <f>Segments!D28</f>
         <v/>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="37">
         <f>Segments!E28</f>
         <v/>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="37">
         <f>Segments!F28</f>
         <v/>
       </c>
@@ -8397,23 +8929,23 @@
       <c r="D13" s="24" t="n">
         <v>240.774</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="37">
         <f>'Cash Flow'!B13</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="37">
         <f>'Cash Flow'!C13</f>
         <v/>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>'Cash Flow'!D13</f>
         <v/>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="37">
         <f>'Cash Flow'!E13</f>
         <v/>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="37">
         <f>'Cash Flow'!F13</f>
         <v/>
       </c>
@@ -8433,23 +8965,23 @@
       <c r="D14" s="24" t="n">
         <v>66.672</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="37">
         <f>'Cash Flow'!B14</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>'Cash Flow'!C14</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="37">
         <f>'Cash Flow'!D14</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="37">
         <f>'Cash Flow'!E14</f>
         <v/>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="37">
         <f>'Cash Flow'!F14</f>
         <v/>
       </c>
@@ -8469,63 +9001,63 @@
       <c r="D15" s="24" t="n">
         <v>189.975</v>
       </c>
-      <c r="E15" s="33">
-        <f>Assumptions!$C$57*(1+Assumptions!B25)</f>
-        <v/>
-      </c>
-      <c r="F15" s="33">
-        <f>E15*(1+Assumptions!C25)</f>
-        <v/>
-      </c>
-      <c r="G15" s="33">
-        <f>F15*(1+Assumptions!D25)</f>
-        <v/>
-      </c>
-      <c r="H15" s="33">
-        <f>G15*(1+Assumptions!E25)</f>
-        <v/>
-      </c>
-      <c r="I15" s="33">
-        <f>H15*(1+Assumptions!F25)</f>
+      <c r="E15" s="36">
+        <f>Assumptions!$C$73*(1+Assumptions!B30)</f>
+        <v/>
+      </c>
+      <c r="F15" s="36">
+        <f>E15*(1+Assumptions!C30)</f>
+        <v/>
+      </c>
+      <c r="G15" s="36">
+        <f>F15*(1+Assumptions!D30)</f>
+        <v/>
+      </c>
+      <c r="H15" s="36">
+        <f>G15*(1+Assumptions!E30)</f>
+        <v/>
+      </c>
+      <c r="I15" s="36">
+        <f>H15*(1+Assumptions!F30)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>Profit before tax</t>
-        </is>
-      </c>
-      <c r="B16" s="31">
+          <t>Profit before tax (before the JV share, forecast)</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
         <f>B11+B12+B13-B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>C11+C12+C13-C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>D11+D12+D13-D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="31">
-        <f>E11+E12+E13-E14+E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="31">
-        <f>F11+F12+F13-F14+F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="31">
-        <f>G11+G12+G13-G14+G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="31">
-        <f>H11+H12+H13-H14+H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="31">
-        <f>I11+I12+I13-I14+I15</f>
+      <c r="E16" s="32">
+        <f>E11+E12+E13-E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>F11+F12+F13-F14</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>G11+G12+G13-G14</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>H11+H12+H13-H14</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>I11+I12+I13-I14</f>
         <v/>
       </c>
     </row>
@@ -8544,24 +9076,24 @@
       <c r="D17" s="24" t="n">
         <v>202.054</v>
       </c>
-      <c r="E17" s="33">
-        <f>E16*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="F17" s="33">
-        <f>F16*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="G17" s="33">
-        <f>G16*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="H17" s="33">
-        <f>H16*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="I17" s="33">
-        <f>I16*Assumptions!$C$31</f>
+      <c r="E17" s="36">
+        <f>E16*Assumptions!$C$36</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>F16*Assumptions!$C$36</f>
+        <v/>
+      </c>
+      <c r="G17" s="36">
+        <f>G16*Assumptions!$C$36</f>
+        <v/>
+      </c>
+      <c r="H17" s="36">
+        <f>H16*Assumptions!$C$36</f>
+        <v/>
+      </c>
+      <c r="I17" s="36">
+        <f>I16*Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -8571,36 +9103,36 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <f>B16-B17</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>C16-C17</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <f>D16-D17</f>
         <v/>
       </c>
-      <c r="E18" s="31">
-        <f>E16-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="31">
-        <f>F16-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="31">
-        <f>G16-G17</f>
-        <v/>
-      </c>
-      <c r="H18" s="31">
-        <f>H16-H17</f>
-        <v/>
-      </c>
-      <c r="I18" s="31">
-        <f>I16-I17</f>
+      <c r="E18" s="32">
+        <f>E16-E17+E15</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>F16-F17+F15</f>
+        <v/>
+      </c>
+      <c r="G18" s="32">
+        <f>G16-G17+G15</f>
+        <v/>
+      </c>
+      <c r="H18" s="32">
+        <f>H16-H17+H15</f>
+        <v/>
+      </c>
+      <c r="I18" s="32">
+        <f>I16-I17+I15</f>
         <v/>
       </c>
     </row>
@@ -8610,36 +9142,36 @@
           <t>Minorities</t>
         </is>
       </c>
-      <c r="B19" s="45">
+      <c r="B19" s="35">
         <f>B18-B20</f>
         <v/>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="35">
         <f>C18-C20</f>
         <v/>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="35">
         <f>D18-D20</f>
         <v/>
       </c>
-      <c r="E19" s="45">
-        <f>E18*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="F19" s="45">
-        <f>F18*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="G19" s="45">
-        <f>G18*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="H19" s="45">
-        <f>H18*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="I19" s="45">
-        <f>I18*Assumptions!$C$65</f>
+      <c r="E19" s="35">
+        <f>E18*Assumptions!$C$81</f>
+        <v/>
+      </c>
+      <c r="F19" s="35">
+        <f>F18*Assumptions!$C$81</f>
+        <v/>
+      </c>
+      <c r="G19" s="35">
+        <f>G18*Assumptions!$C$81</f>
+        <v/>
+      </c>
+      <c r="H19" s="35">
+        <f>H18*Assumptions!$C$81</f>
+        <v/>
+      </c>
+      <c r="I19" s="35">
+        <f>I18*Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -8658,23 +9190,23 @@
       <c r="D20" s="26" t="n">
         <v>1628.475</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <f>E18-E19</f>
         <v/>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>F18-F19</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>G18-G19</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="32">
         <f>H18-H19</f>
         <v/>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="32">
         <f>I18-I19</f>
         <v/>
       </c>
@@ -8686,35 +9218,35 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>B20/Assumptions!$C$47</f>
+        <f>B20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>C20/Assumptions!$C$47</f>
+        <f>C20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>D20/Assumptions!$C$47</f>
+        <f>D20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>E20/Assumptions!$C$47</f>
+        <f>E20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>F20/Assumptions!$C$47</f>
+        <f>F20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>G20/Assumptions!$C$47</f>
+        <f>G20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="H21" s="10">
-        <f>H20/Assumptions!$C$47</f>
+        <f>H20/Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="I21" s="10">
-        <f>I20/Assumptions!$C$47</f>
+        <f>I20/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>

--- a/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
+++ b/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -750,157 +750,202 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Two judgements are shown both ways, never averaged. The fuel path: the base case follows the official</t>
+          <t>The beta is switchable, and both regressions are in the sheet. The adopted beta is this stock's own</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>US energy-agency curve (relief from 2027); the alternative holds the airline-association high-fuel</t>
+          <t>five-year weekly regression against the Dubai market index — the exchange every filing says the shares</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>assumption. And the joint-venture network (Abu Dhabi, Egypt, Pakistan, Morocco, the new Saudi venture):</t>
+          <t>are listed on, and the index the company's own annual report benchmarks itself against. The same</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>the base carries it at its audited balance-sheet value of AED 363mn; the alternative capitalises its</t>
+          <t>regression run against the Abu Dhabi market index is carried beside it as a cross-check: it is a lower</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>profit share at a growth multiple. Both appear on the Summary and the SOTP Bridge.</t>
+          <t>beta, but it explains only a third as much of the share's weekly movement, which is why it is published</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>rather than adopted. Set the benchmark switch on Assumptions to 1 and the whole workbook reprices on it.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>outputs shown as ranges.</t>
+          <t>Two judgements are shown both ways, never averaged. The fuel path: the base case follows the official</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>US energy-agency curve (relief from 2027); the alternative holds the airline-association high-fuel</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
+          <t>assumption. And the joint-venture network (Abu Dhabi, Egypt, Pakistan, Morocco, the new Saudi venture):</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>financial statements, read from the company's investor-relations page; FY2024 comparatives are as</t>
+          <t>the base carries it at its audited balance-sheet value of AED 363mn; the alternative capitalises its</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>restated in the FY2025 filing. The interim quarter is the reviewed Q1-2026 filing. Passengers, load</t>
+          <t>profit share at a growth multiple. Both appear on the Summary and the SOTP Bridge.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>factor and fleet come from the company's own results presentations. Every input is listed with source</t>
-        </is>
-      </c>
+      <c r="A44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>and date in the companion bibliography document.</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>outputs shown as ranges.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
-        </is>
-      </c>
+      <c r="A47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>9.21% -&gt; 8.67% on the same easing calendar as the cost-of-debt path; the terminal value is</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of</t>
+          <t>financial statements, read from the company's investor-relations page; FY2024 comparatives are as</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>time: values are struck at 31-Dec-2025 and rolled to the 7-Aug-2026 anchor at the cost of equity, net of</t>
+          <t>restated in the FY2025 filing. The interim quarter is the reviewed Q1-2026 filing. Passengers, load</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>the AED 0.30 dividend paid inside the window.</t>
+          <t>factor and fleet come from the company's own results presentations. Every input is listed with source</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>and date in the companion bibliography document.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Currency. AED million unless stated. Spot AED 5.24 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
-        </is>
-      </c>
+      <c r="A53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>9.21% -&gt; 8.67% on the same easing calendar as the cost-of-debt path; the terminal value is</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>time: values are struck at 31-Dec-2025 and rolled to the 7-Aug-2026 anchor at the cost of equity, net of</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>the AED 0.30 dividend paid inside the window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Currency. AED million unless stated. Spot AED 5.24 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -1044,23 +1089,23 @@
         <v>1362.497</v>
       </c>
       <c r="E6" s="17">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="I6" s="17">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1212,7 @@
         <v>8408.904</v>
       </c>
       <c r="E15" s="31">
-        <f>Assumptions!$C$82+'Income Statement'!E20-'Cash Flow'!B15</f>
+        <f>Assumptions!$C$84+'Income Statement'!E20-'Cash Flow'!B15</f>
         <v/>
       </c>
       <c r="F15" s="31">
@@ -1589,7 +1634,7 @@
         </is>
       </c>
       <c r="B12" s="31">
-        <f>Assumptions!$C$75-Assumptions!$C$76</f>
+        <f>Assumptions!$C$77-Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="C12" s="31">
@@ -1670,23 +1715,23 @@
         </is>
       </c>
       <c r="B15" s="31">
-        <f>MAX(Assumptions!B31*'Income Statement'!E20,Assumptions!$C$59)</f>
+        <f>MAX(Assumptions!B31*'Income Statement'!E20,Assumptions!$C$60)</f>
         <v/>
       </c>
       <c r="C15" s="31">
-        <f>MAX(Assumptions!C31*'Income Statement'!F20,Assumptions!$C$59)</f>
+        <f>MAX(Assumptions!C31*'Income Statement'!F20,Assumptions!$C$60)</f>
         <v/>
       </c>
       <c r="D15" s="31">
-        <f>MAX(Assumptions!D31*'Income Statement'!G20,Assumptions!$C$59)</f>
+        <f>MAX(Assumptions!D31*'Income Statement'!G20,Assumptions!$C$60)</f>
         <v/>
       </c>
       <c r="E15" s="31">
-        <f>MAX(Assumptions!E31*'Income Statement'!H20,Assumptions!$C$59)</f>
+        <f>MAX(Assumptions!E31*'Income Statement'!H20,Assumptions!$C$60)</f>
         <v/>
       </c>
       <c r="F15" s="31">
-        <f>MAX(Assumptions!F31*'Income Statement'!I20,Assumptions!$C$59)</f>
+        <f>MAX(Assumptions!F31*'Income Statement'!I20,Assumptions!$C$60)</f>
         <v/>
       </c>
     </row>
@@ -1724,7 +1769,7 @@
         </is>
       </c>
       <c r="B17" s="17">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="C17" s="31">
@@ -1751,23 +1796,23 @@
         </is>
       </c>
       <c r="B18" s="31">
-        <f>B17+DCF!B45+Assumptions!B23*Assumptions!$C$58-Assumptions!B27</f>
+        <f>B17+DCF!B45+Assumptions!B23*Assumptions!$C$59-Assumptions!B27</f>
         <v/>
       </c>
       <c r="C18" s="31">
-        <f>C17+DCF!C45+Assumptions!C23*Assumptions!$C$58-Assumptions!C27</f>
+        <f>C17+DCF!C45+Assumptions!C23*Assumptions!$C$59-Assumptions!C27</f>
         <v/>
       </c>
       <c r="D18" s="31">
-        <f>D17+DCF!D45+Assumptions!D23*Assumptions!$C$58-Assumptions!D27</f>
+        <f>D17+DCF!D45+Assumptions!D23*Assumptions!$C$59-Assumptions!D27</f>
         <v/>
       </c>
       <c r="E18" s="31">
-        <f>E17+DCF!E45+Assumptions!E23*Assumptions!$C$58-Assumptions!E27</f>
+        <f>E17+DCF!E45+Assumptions!E23*Assumptions!$C$59-Assumptions!E27</f>
         <v/>
       </c>
       <c r="F18" s="31">
-        <f>F17+DCF!F45+Assumptions!F23*Assumptions!$C$58-Assumptions!F27</f>
+        <f>F17+DCF!F45+Assumptions!F23*Assumptions!$C$59-Assumptions!F27</f>
         <v/>
       </c>
     </row>
@@ -2188,23 +2233,23 @@
         <v>0.3</v>
       </c>
       <c r="E11" s="10">
-        <f>'Cash Flow'!B15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!B15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>'Cash Flow'!C15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!C15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>'Cash Flow'!D15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!D15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="H11" s="10">
-        <f>'Cash Flow'!E15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!E15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="I11" s="10">
-        <f>'Cash Flow'!F15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!F15/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +2353,7 @@
         </is>
       </c>
       <c r="E15" s="11">
-        <f>'Income Statement'!E20/Assumptions!$C$82</f>
+        <f>'Income Statement'!E20/Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F15" s="11">
@@ -2710,19 +2755,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4.563727371978012</v>
+        <v>4.536614448628748</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4.826833817314236</v>
+        <v>4.799720893964969</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>5.151250713834374</v>
+        <v>5.124137790485109</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5.562052885138246</v>
+        <v>5.534939961788981</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>6.100146969325265</v>
+        <v>6.073034045976001</v>
       </c>
     </row>
     <row r="7">
@@ -2732,19 +2777,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3.844894063371688</v>
+        <v>3.817781140022422</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4.002252033552121</v>
+        <v>3.975139110202857</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4.188636361804018</v>
+        <v>4.161523438454752</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4.413374983406841</v>
+        <v>4.386262060057576</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4.690272186155007</v>
+        <v>4.663159262805743</v>
       </c>
     </row>
     <row r="8">
@@ -2754,19 +2799,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3.328204707597294</v>
+        <v>3.301091784248027</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.426565626328664</v>
+        <v>3.399452702979399</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.539716388425919</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.671571273184506</v>
+        <v>3.644458349835241</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3.827559476465596</v>
+        <v>3.800446553116331</v>
       </c>
     </row>
     <row r="9">
@@ -2776,19 +2821,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.939350044427541</v>
+        <v>2.912237121078276</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.002332932445859</v>
+        <v>2.975220009096594</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3.073135682640569</v>
+        <v>3.046022759291303</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.153517504517958</v>
+        <v>3.126404581168692</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3.245808071052985</v>
+        <v>3.218695147703719</v>
       </c>
     </row>
     <row r="10">
@@ -2798,19 +2843,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>2.636446054689363</v>
+        <v>2.609333131340096</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2.677083058851147</v>
+        <v>2.649970135501881</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2.721871308489303</v>
+        <v>2.694758385140037</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2.771622899645585</v>
+        <v>2.744509976296319</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2.827376528723581</v>
+        <v>2.800263605374315</v>
       </c>
     </row>
     <row r="12">
@@ -2859,19 +2904,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>5.304018537245045</v>
+        <v>5.219033032295411</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>4.309353735514492</v>
+        <v>4.236532865742789</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3.63883720038445</v>
+        <v>3.57421667008031</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3.156735978743524</v>
+        <v>3.098011490472734</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>2.793793397486388</v>
+        <v>2.739507654895397</v>
       </c>
     </row>
     <row r="15">
@@ -2881,19 +2926,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5.226747607739238</v>
+        <v>5.17122927576858</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>4.248294800245155</v>
+        <v>4.198747379854847</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3.588702352857153</v>
+        <v>3.543180030205084</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3.114451765271498</v>
+        <v>3.071823509971186</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2.757416260096355</v>
+        <v>2.716966778688986</v>
       </c>
     </row>
     <row r="16">
@@ -2903,19 +2948,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>5.151250713834374</v>
+        <v>5.124137790485109</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>4.188636361804018</v>
+        <v>4.161523438454752</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3.539716388425919</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3.073135682640569</v>
+        <v>3.046022759291303</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>2.721871308489303</v>
+        <v>2.694758385140037</v>
       </c>
     </row>
     <row r="17">
@@ -2925,19 +2970,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5.077474294187578</v>
+        <v>5.077744450590231</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>4.13033617316109</v>
+        <v>4.124849931651495</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>3.491844679320727</v>
+        <v>3.482477893864546</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3.032758574919082</v>
+        <v>3.020601613210619</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2.687133500795821</v>
+        <v>2.672875942130129</v>
       </c>
     </row>
     <row r="18">
@@ -2947,25 +2992,25 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>5.005366813033706</v>
+        <v>5.032035476189662</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>4.073353583985758</v>
+        <v>4.088716021054054</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3.445053905711079</v>
+        <v>3.452794457175206</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2.993292386783587</v>
+        <v>2.995552632055155</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2.653178739906747</v>
+        <v>2.651313076159818</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Beta (leftmost column = the alternative-benchmark regression, published not adopted)</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3018,7 @@
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3004,19 +3049,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>4.257253763870267</v>
+        <v>4.345327726159549</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3.920913618442269</v>
+        <v>3.881657483484181</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>3.539716388425919</v>
+        <v>3.512603465076654</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3.272618534148231</v>
+        <v>3.253695840672244</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>2.976910757184894</v>
+        <v>2.966665579760465</v>
       </c>
     </row>
     <row r="24">
@@ -3475,7 +3520,7 @@
         </is>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.4703575469948413</v>
+        <v>0.4699048508822166</v>
       </c>
     </row>
     <row r="52">
@@ -3509,7 +3554,7 @@
         </is>
       </c>
       <c r="H52" s="7" t="n">
-        <v>7.228322439161341</v>
+        <v>7.190867623684912</v>
       </c>
     </row>
     <row r="53">
@@ -3614,19 +3659,19 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>Assumptions!$C$54</f>
+        <f>Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>'Cash Flow'!B15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!B15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>'Cash Flow'!D15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!D15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>'Cash Flow'!F15/Assumptions!$C$53</f>
+        <f>'Cash Flow'!F15/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -3637,19 +3682,19 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>Assumptions!$C$82/Assumptions!$C$53</f>
+        <f>Assumptions!$C$84/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>'Balance Sheet'!E15/Assumptions!$C$53</f>
+        <f>'Balance Sheet'!E15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>'Balance Sheet'!G15/Assumptions!$C$53</f>
+        <f>'Balance Sheet'!G15/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>'Balance Sheet'!I15/Assumptions!$C$53</f>
+        <f>'Balance Sheet'!I15/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -3660,15 +3705,15 @@
         </is>
       </c>
       <c r="C8" s="8">
-        <f>'Cash Flow'!B9/Assumptions!$C$53</f>
+        <f>'Cash Flow'!B9/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>'Cash Flow'!D9/Assumptions!$C$53</f>
+        <f>'Cash Flow'!D9/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>'Cash Flow'!F9/Assumptions!$C$53</f>
+        <f>'Cash Flow'!F9/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -3679,7 +3724,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'SOTP Bridge'!C6/Assumptions!$C$53</f>
+        <f>'SOTP Bridge'!C6/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -3703,7 +3748,7 @@
         </is>
       </c>
       <c r="C12" s="40">
-        <f>Assumptions!$C$52/'Income Statement'!D21</f>
+        <f>Assumptions!$C$53/'Income Statement'!D21</f>
         <v/>
       </c>
     </row>
@@ -3714,7 +3759,7 @@
         </is>
       </c>
       <c r="C13" s="40">
-        <f>Assumptions!$C$52/'Income Statement'!F21</f>
+        <f>Assumptions!$C$53/'Income Statement'!F21</f>
         <v/>
       </c>
     </row>
@@ -3725,7 +3770,7 @@
         </is>
       </c>
       <c r="C14" s="40">
-        <f>Assumptions!$C$52/((Assumptions!$C$82)/Assumptions!$C$53)</f>
+        <f>Assumptions!$C$53/((Assumptions!$C$84)/Assumptions!$C$54)</f>
         <v/>
       </c>
     </row>
@@ -3736,7 +3781,7 @@
         </is>
       </c>
       <c r="C15" s="40">
-        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/('Income Statement'!D9+'Income Statement'!D12)</f>
+        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
     </row>
@@ -3747,7 +3792,7 @@
         </is>
       </c>
       <c r="C16" s="11">
-        <f>Assumptions!$C$54/Assumptions!$C$52</f>
+        <f>Assumptions!$C$55/Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -3959,11 +4004,11 @@
         </is>
       </c>
       <c r="B12" s="47">
-        <f>Assumptions!$C$52/'Income Statement'!D21</f>
+        <f>Assumptions!$C$53/'Income Statement'!D21</f>
         <v/>
       </c>
       <c r="C12" s="47">
-        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/('Income Statement'!D9+'Income Statement'!D12)</f>
+        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
       <c r="D12" s="48" t="inlineStr">
@@ -4066,17 +4111,17 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.4703575469948413</v>
+        <v>0.4699048508822166</v>
       </c>
       <c r="C5" s="8">
         <f>'Fundamental Valuation'!C5</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7.228322439161341</v>
+        <v>7.190867623684912</v>
       </c>
       <c r="E5" s="9">
-        <f>Assumptions!$C$83</f>
+        <f>Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F5" s="10">
@@ -4107,7 +4152,7 @@
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F6" s="10">
@@ -4138,7 +4183,7 @@
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="F7" s="10">
@@ -4169,7 +4214,7 @@
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$88</f>
         <v/>
       </c>
       <c r="F8" s="10">
@@ -4231,7 +4276,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>C9+Assumptions!$C$83*('SOTP Bridge'!C20-'Fundamental Valuation'!C5)</f>
+        <f>C9+Assumptions!$C$85*('SOTP Bridge'!C20-'Fundamental Valuation'!C5)</f>
         <v/>
       </c>
       <c r="G11" s="11">
@@ -4302,7 +4347,7 @@
       </c>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="16">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="D16" s="15" t="n"/>
@@ -4330,7 +4375,7 @@
         </is>
       </c>
       <c r="C19" s="17">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -4418,7 +4463,7 @@
         </is>
       </c>
       <c r="C27" s="9">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -4593,7 +4638,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.4703575469948413</v>
+        <v>0.4699048508822166</v>
       </c>
     </row>
     <row r="16">
@@ -4603,7 +4648,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.228322439161341</v>
+        <v>7.190867623684912</v>
       </c>
     </row>
     <row r="18">
@@ -4626,15 +4671,15 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>13*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53)*DCF!C61-Assumptions!$C$54</f>
+        <f>13*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54)*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>10*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53)*DCF!C61-Assumptions!$C$54</f>
+        <f>10*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54)*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>16*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53)*DCF!C61-Assumptions!$C$54</f>
+        <f>16*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54)*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -4645,15 +4690,15 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$81))*(1+Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47)+0.5*(Assumptions!$C$76-Assumptions!$C$75))/Assumptions!$C$53*DCF!C61-Assumptions!$C$54</f>
+        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$83))*(1+Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48)+0.5*(Assumptions!$C$78-Assumptions!$C$77))/Assumptions!$C$54*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$81))*1.015/(0.5*(DCF!C10+DCF!C21)-0.015)/Assumptions!$C$53*DCF!C61-Assumptions!$C$54</f>
+        <f>((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$83))*1.015/(0.5*(DCF!C10+DCF!C21)-0.015)/Assumptions!$C$54*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$81))*1.035/(DCF!C21-0.035)+2*0.5*(Assumptions!$C$76-Assumptions!$C$75))/Assumptions!$C$53*DCF!C61-Assumptions!$C$54</f>
+        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$83))*1.035/(DCF!C21-0.035)+2*0.5*(Assumptions!$C$78-Assumptions!$C$77))/Assumptions!$C$54*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -4702,7 +4747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -5437,7 +5482,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Beta (five-year weekly, vs the Dubai index)</t>
+          <t>Beta — adopted (own stock, five-year weekly vs the Dubai market index)</t>
         </is>
       </c>
       <c r="C40" s="23" t="n">
@@ -5447,217 +5492,217 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="n">
-        <v>0.0487</v>
+          <t>Beta — alternative benchmark (same regression vs the Abu Dhabi market index)</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="C42" s="27" t="n">
-        <v>0.04</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="C43" s="27" t="n">
-        <v>0.0475</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Marginal cost of debt</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="C44" s="27" t="n">
-        <v>0.055</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Marginal cost of debt</t>
         </is>
       </c>
       <c r="C45" s="27" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="n">
-        <v>0.1</v>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Joint-venture capitalisation multiple</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="n">
-        <v>15</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
+          <t>Joint-venture capitalisation multiple</t>
         </is>
       </c>
       <c r="C49" s="28" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
+          <t>Justified EV/EBITDA</t>
         </is>
       </c>
       <c r="C50" s="28" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="n">
-        <v>0.18</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Spot price (AED)</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>5.24</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="n">
-        <v>4666.7</v>
+          <t>Spot price (AED)</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>5.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share (AED, approved 12 March 2026)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>0.3</v>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="n">
+        <v>4666.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Days from 31-Dec-2025 to the 7-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="n">
-        <v>219</v>
+          <t>FY2025 dividend per share (AED, approved 12 March 2026)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Fuel intensity (AED per passenger per USD/bbl of effective jet price)</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="n">
-        <v>1.937</v>
+          <t>Days from 31-Dec-2025 to the 7-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use value per leased aircraft (AED mn)</t>
-        </is>
-      </c>
-      <c r="C57" s="26" t="n">
-        <v>175</v>
+          <t>Fuel intensity (AED per passenger per USD/bbl of effective jet price)</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="n">
+        <v>1.937</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Loan drawn per owned aircraft (AED mn)</t>
+          <t>Right-of-use value per leased aircraft (AED mn)</t>
         </is>
       </c>
       <c r="C58" s="26" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Dividend floor (AED mn = 30 fils on the full share count)</t>
+          <t>Loan drawn per owned aircraft (AED mn)</t>
         </is>
       </c>
       <c r="C59" s="26" t="n">
-        <v>1400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Minority interests at carrying value (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="n">
-        <v>1.287</v>
+          <t>Dividend floor (AED mn = 30 fils on the full share count)</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Scenario: passenger multiplier</t>
+          <t>Minority interests at carrying value (AED mn, audited)</t>
         </is>
       </c>
       <c r="C61" s="23" t="n">
-        <v>1</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Scenario: fare multiplier</t>
+          <t>Scenario: passenger multiplier</t>
         </is>
       </c>
       <c r="C62" s="23" t="n">
@@ -5667,7 +5712,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Scenario: fuel multiplier</t>
+          <t>Scenario: fare multiplier</t>
         </is>
       </c>
       <c r="C63" s="23" t="n">
@@ -5677,7 +5722,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Scenario: capital-expenditure multiplier</t>
+          <t>Scenario: fuel multiplier</t>
         </is>
       </c>
       <c r="C64" s="23" t="n">
@@ -5687,260 +5732,280 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Scenario: cost-of-capital shift</t>
-        </is>
-      </c>
-      <c r="C65" s="27" t="n">
-        <v>0</v>
+          <t>Scenario: capital-expenditure multiplier</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Scenario: high-fuel switch (0 = base path, 1 = alternative)</t>
-        </is>
-      </c>
-      <c r="C66" s="23" t="n">
+          <t>Scenario: cost-of-capital shift</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Cash administrative costs, FY2025 (AED mn, audited less its depreciation)</t>
-        </is>
-      </c>
-      <c r="C67" s="24" t="n">
-        <v>276.183</v>
+          <t>Scenario: high-fuel switch (0 = base path, 1 = alternative)</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Cargo revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="n">
-        <v>186.948</v>
+          <t>Scenario: beta benchmark switch (0 = adopted index, 1 = alternative index)</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Service revenue, FY2025 (AED mn, disclosed)</t>
+          <t>Cash administrative costs, FY2025 (AED mn, audited less its depreciation)</t>
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>223.323</v>
+        <v>276.183</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>Hotel revenue, FY2025 (AED mn, disclosed)</t>
+          <t>Cargo revenue, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>59.842</v>
+        <v>186.948</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Aircraft-lease revenue, FY2025 (AED mn, disclosed)</t>
+          <t>Service revenue, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C71" s="24" t="n">
-        <v>219.755</v>
+        <v>223.323</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Other income, FY2025 (AED mn, disclosed)</t>
+          <t>Hotel revenue, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C72" s="24" t="n">
-        <v>197.132</v>
+        <v>59.842</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Share of JV and associate profit, FY2025 (AED mn, disclosed)</t>
+          <t>Aircraft-lease revenue, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C73" s="24" t="n">
-        <v>189.975</v>
+        <v>219.755</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Working capital, FY2025 (AED mn, audited balance sheet)</t>
+          <t>Other income, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C74" s="24" t="n">
-        <v>-5186.834</v>
+        <v>197.132</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Gross debt, FY2025 (AED mn, audited)</t>
+          <t>Share of JV and associate profit, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C75" s="24" t="n">
-        <v>2781.435</v>
+        <v>189.975</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Cash and fixed deposits, FY2025 (AED mn, audited)</t>
+          <t>Working capital, FY2025 (AED mn, audited balance sheet)</t>
         </is>
       </c>
       <c r="C76" s="24" t="n">
-        <v>5198.732</v>
+        <v>-5186.834</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Fleet assets, FY2025 (PP&amp;E + right-of-use + aircraft advances, AED mn, audited)</t>
+          <t>Gross debt, FY2025 (AED mn, audited)</t>
         </is>
       </c>
       <c r="C77" s="24" t="n">
-        <v>8670.864</v>
+        <v>2781.435</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets (AED mn, audited)</t>
+          <t>Cash and fixed deposits, FY2025 (AED mn, audited)</t>
         </is>
       </c>
       <c r="C78" s="24" t="n">
-        <v>1362.497</v>
+        <v>5198.732</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>JV and associates at carrying value (AED mn, audited)</t>
+          <t>Fleet assets, FY2025 (PP&amp;E + right-of-use + aircraft advances, AED mn, audited)</t>
         </is>
       </c>
       <c r="C79" s="24" t="n">
-        <v>363.386</v>
+        <v>8670.864</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Non-operating assets (investments + investment property + net investment in lease, AED mn)</t>
+          <t>Intangible assets (AED mn, audited)</t>
         </is>
       </c>
       <c r="C80" s="24" t="n">
-        <v>1069.284</v>
+        <v>1362.497</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Minority share of profit</t>
-        </is>
-      </c>
-      <c r="C81" s="30" t="n">
-        <v>0.0001596330894835507</v>
+          <t>JV and associates at carrying value (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="n">
+        <v>363.386</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to owners, FY2025 (AED mn, audited)</t>
+          <t>Non-operating assets (investments + investment property + net investment in lease, AED mn)</t>
         </is>
       </c>
       <c r="C82" s="24" t="n">
-        <v>8408.904</v>
+        <v>1069.284</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C83" s="25" t="n">
-        <v>0.45</v>
+          <t>Minority share of profit</t>
+        </is>
+      </c>
+      <c r="C83" s="30" t="n">
+        <v>0.0001596330894835507</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C84" s="25" t="n">
-        <v>0.2</v>
+          <t>Equity attributable to owners, FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="n">
+        <v>8408.904</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
+          <t>Weight — relative</t>
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Relative lens — bear multiple</t>
-        </is>
-      </c>
-      <c r="C87" s="28" t="n">
-        <v>5</v>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Relative lens — bull multiple</t>
-        </is>
-      </c>
-      <c r="C88" s="28" t="n">
-        <v>8</v>
+          <t>Weight — book</t>
+        </is>
+      </c>
+      <c r="C88" s="25" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Normalised lens — bear P/E</t>
+          <t>Relative lens — bear multiple</t>
         </is>
       </c>
       <c r="C89" s="28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
+          <t>Relative lens — bull multiple</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Normalised lens — bear P/E</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
           <t>Normalised lens — bull P/E</t>
         </is>
       </c>
-      <c r="C90" s="28" t="n">
+      <c r="C92" s="28" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6018,7 +6083,7 @@
         </is>
       </c>
       <c r="C6" s="31">
-        <f>Assumptions!$C$76-Assumptions!$C$75</f>
+        <f>Assumptions!$C$78-Assumptions!$C$77</f>
         <v/>
       </c>
     </row>
@@ -6029,7 +6094,7 @@
         </is>
       </c>
       <c r="C7" s="17">
-        <f>Assumptions!$C$80</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -6040,7 +6105,7 @@
         </is>
       </c>
       <c r="C8" s="17">
-        <f>Assumptions!$C$79</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -6062,7 +6127,7 @@
         </is>
       </c>
       <c r="C11" s="33">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -6084,7 +6149,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>C13/Assumptions!$C$53</f>
+        <f>C13/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -6095,7 +6160,7 @@
         </is>
       </c>
       <c r="C15" s="21">
-        <f>(C5*DCF!C61+(C6+C7+C8)*DCF!C63-C11)/Assumptions!$C$53-Assumptions!$C$54</f>
+        <f>(C5*DCF!C61+(C6+C7+C8)*DCF!C63-C11)/Assumptions!$C$54-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -6119,7 +6184,7 @@
         </is>
       </c>
       <c r="C18" s="31">
-        <f>Assumptions!$C$48*Assumptions!$C$73</f>
+        <f>Assumptions!$C$49*Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -6141,7 +6206,7 @@
         </is>
       </c>
       <c r="C20" s="21">
-        <f>(C5*DCF!C61+(C6+C7+C18)*DCF!C63-C11)/Assumptions!$C$53-Assumptions!$C$54</f>
+        <f>(C5*DCF!C61+(C6+C7+C18)*DCF!C63-C11)/Assumptions!$C$54-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -6290,23 +6355,23 @@
         </is>
       </c>
       <c r="B5" s="35">
-        <f>Assumptions!B5*Assumptions!$C$61</f>
+        <f>Assumptions!B5*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="C5" s="35">
-        <f>Assumptions!C5*Assumptions!$C$61</f>
+        <f>Assumptions!C5*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="D5" s="35">
-        <f>Assumptions!D5*Assumptions!$C$61</f>
+        <f>Assumptions!D5*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="E5" s="35">
-        <f>Assumptions!E5*Assumptions!$C$61</f>
+        <f>Assumptions!E5*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>Assumptions!F5*Assumptions!$C$61</f>
+        <f>Assumptions!F5*Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
@@ -6317,23 +6382,23 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <f>Assumptions!B6*Assumptions!$C$62</f>
+        <f>Assumptions!B6*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>Assumptions!C6*Assumptions!$C$62</f>
+        <f>Assumptions!C6*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>Assumptions!D6*Assumptions!$C$62</f>
+        <f>Assumptions!D6*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>Assumptions!E6*Assumptions!$C$62</f>
+        <f>Assumptions!E6*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F6" s="36">
-        <f>Assumptions!F6*Assumptions!$C$62</f>
+        <f>Assumptions!F6*Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6425,7 +6490,7 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <f>Assumptions!$C$68*(1+Assumptions!B8)</f>
+        <f>Assumptions!$C$70*(1+Assumptions!B8)</f>
         <v/>
       </c>
       <c r="C10" s="36">
@@ -6452,7 +6517,7 @@
         </is>
       </c>
       <c r="B11" s="36">
-        <f>Assumptions!$C$69*(1+Assumptions!B9)</f>
+        <f>Assumptions!$C$71*(1+Assumptions!B9)</f>
         <v/>
       </c>
       <c r="C11" s="36">
@@ -6479,7 +6544,7 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <f>Assumptions!$C$70*(1+Assumptions!B10)</f>
+        <f>Assumptions!$C$72*(1+Assumptions!B10)</f>
         <v/>
       </c>
       <c r="C12" s="36">
@@ -6506,7 +6571,7 @@
         </is>
       </c>
       <c r="B13" s="36">
-        <f>Assumptions!$C$71*(1+Assumptions!B11)</f>
+        <f>Assumptions!$C$73*(1+Assumptions!B11)</f>
         <v/>
       </c>
       <c r="C13" s="36">
@@ -6592,23 +6657,23 @@
         </is>
       </c>
       <c r="B17" s="36">
-        <f>Assumptions!$C$56*(Assumptions!B12*(1-Assumptions!$C$66)+Assumptions!B13*Assumptions!$C$66)*Assumptions!$C$63</f>
+        <f>Assumptions!$C$57*(Assumptions!B12*(1-Assumptions!$C$67)+Assumptions!B13*Assumptions!$C$67)*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="C17" s="36">
-        <f>Assumptions!$C$56*(Assumptions!C12*(1-Assumptions!$C$66)+Assumptions!C13*Assumptions!$C$66)*Assumptions!$C$63</f>
+        <f>Assumptions!$C$57*(Assumptions!C12*(1-Assumptions!$C$67)+Assumptions!C13*Assumptions!$C$67)*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="D17" s="36">
-        <f>Assumptions!$C$56*(Assumptions!D12*(1-Assumptions!$C$66)+Assumptions!D13*Assumptions!$C$66)*Assumptions!$C$63</f>
+        <f>Assumptions!$C$57*(Assumptions!D12*(1-Assumptions!$C$67)+Assumptions!D13*Assumptions!$C$67)*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="E17" s="36">
-        <f>Assumptions!$C$56*(Assumptions!E12*(1-Assumptions!$C$66)+Assumptions!E13*Assumptions!$C$66)*Assumptions!$C$63</f>
+        <f>Assumptions!$C$57*(Assumptions!E12*(1-Assumptions!$C$67)+Assumptions!E13*Assumptions!$C$67)*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>Assumptions!$C$56*(Assumptions!F12*(1-Assumptions!$C$66)+Assumptions!F13*Assumptions!$C$66)*Assumptions!$C$63</f>
+        <f>Assumptions!$C$57*(Assumptions!F12*(1-Assumptions!$C$67)+Assumptions!F13*Assumptions!$C$67)*Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -6808,7 +6873,7 @@
         </is>
       </c>
       <c r="B25" s="36">
-        <f>Assumptions!$C$67*(1+Assumptions!B19)</f>
+        <f>Assumptions!$C$69*(1+Assumptions!B19)</f>
         <v/>
       </c>
       <c r="C25" s="36">
@@ -6889,7 +6954,7 @@
         </is>
       </c>
       <c r="B28" s="36">
-        <f>Assumptions!$C$72*(1+Assumptions!B20)</f>
+        <f>Assumptions!$C$74*(1+Assumptions!B20)</f>
         <v/>
       </c>
       <c r="C28" s="36">
@@ -7207,7 +7272,7 @@
         </is>
       </c>
       <c r="C6" s="38">
-        <f>Assumptions!$C$49</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
     </row>
@@ -7218,7 +7283,7 @@
         </is>
       </c>
       <c r="C7" s="31">
-        <f>Segments!C28*(1-Assumptions!$C$36)/(DCF!C24-Assumptions!$C$47)</f>
+        <f>Segments!C28*(1-Assumptions!$C$36)/(DCF!C24-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
@@ -7262,7 +7327,7 @@
         </is>
       </c>
       <c r="C11" s="21">
-        <f>((C5*C6+C7)*C9+C10)*DCF!C61/Assumptions!$C$53+((Assumptions!$C$76-Assumptions!$C$75+Assumptions!$C$80+Assumptions!$C$79)*DCF!C63-Assumptions!$C$60)/Assumptions!$C$53-Assumptions!$C$54</f>
+        <f>((C5*C6+C7)*C9+C10)*DCF!C61/Assumptions!$C$54+((Assumptions!$C$78-Assumptions!$C$77+Assumptions!$C$82+Assumptions!$C$81)*DCF!C63-Assumptions!$C$61)/Assumptions!$C$54-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7273,7 +7338,7 @@
         </is>
       </c>
       <c r="C12" s="10">
-        <f>((C5*Assumptions!$C$87+C7)*C9+C10)*DCF!C61/Assumptions!$C$53+((Assumptions!$C$76-Assumptions!$C$75+Assumptions!$C$80+Assumptions!$C$79)*DCF!C63-Assumptions!$C$60)/Assumptions!$C$53-Assumptions!$C$54</f>
+        <f>((C5*Assumptions!$C$89+C7)*C9+C10)*DCF!C61/Assumptions!$C$54+((Assumptions!$C$78-Assumptions!$C$77+Assumptions!$C$82+Assumptions!$C$81)*DCF!C63-Assumptions!$C$61)/Assumptions!$C$54-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7284,7 +7349,7 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>((C5*Assumptions!$C$88+C7)*C9+C10)*DCF!C61/Assumptions!$C$53+((Assumptions!$C$76-Assumptions!$C$75+Assumptions!$C$80+Assumptions!$C$79)*DCF!C63-Assumptions!$C$60)/Assumptions!$C$53-Assumptions!$C$54</f>
+        <f>((C5*Assumptions!$C$90+C7)*C9+C10)*DCF!C61/Assumptions!$C$54+((Assumptions!$C$78-Assumptions!$C$77+Assumptions!$C$82+Assumptions!$C$81)*DCF!C63-Assumptions!$C$61)/Assumptions!$C$54-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7302,7 +7367,7 @@
         </is>
       </c>
       <c r="C16" s="40">
-        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/'Income Statement'!D9</f>
+        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
@@ -7313,7 +7378,7 @@
         </is>
       </c>
       <c r="C17" s="40">
-        <f>Assumptions!$C$52/'Income Statement'!D21</f>
+        <f>Assumptions!$C$53/'Income Statement'!D21</f>
         <v/>
       </c>
     </row>
@@ -7324,7 +7389,7 @@
         </is>
       </c>
       <c r="C18" s="40">
-        <f>(DCF!C14+Assumptions!$C$75-Assumptions!$C$76)/('Income Statement'!D9+'Income Statement'!D12)</f>
+        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
     </row>
@@ -7421,7 +7486,7 @@
         </is>
       </c>
       <c r="C28" s="41">
-        <f>(C25+C26)*(1-Assumptions!$C$36)*(1-Assumptions!$C$81)/Assumptions!$C$53</f>
+        <f>(C25+C26)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7432,7 +7497,7 @@
         </is>
       </c>
       <c r="C29" s="21">
-        <f>Assumptions!$C$50*C28*DCF!C61+Assumptions!$C$79/Assumptions!$C$53*DCF!C63-Assumptions!$C$54</f>
+        <f>Assumptions!$C$51*C28*DCF!C61+Assumptions!$C$81/Assumptions!$C$54*DCF!C63-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7443,7 +7508,7 @@
         </is>
       </c>
       <c r="C31" s="10">
-        <f>Assumptions!$C$89*C28*DCF!C61+Assumptions!$C$79/Assumptions!$C$53*DCF!C63-Assumptions!$C$54</f>
+        <f>Assumptions!$C$91*C28*DCF!C61+Assumptions!$C$81/Assumptions!$C$54*DCF!C63-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7454,7 +7519,7 @@
         </is>
       </c>
       <c r="C32" s="10">
-        <f>Assumptions!$C$90*C28*DCF!C61+Assumptions!$C$79/Assumptions!$C$53*DCF!C63-Assumptions!$C$54</f>
+        <f>Assumptions!$C$92*C28*DCF!C61+Assumptions!$C$81/Assumptions!$C$54*DCF!C63-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7478,7 +7543,7 @@
         </is>
       </c>
       <c r="C36" s="10">
-        <f>Assumptions!$C$82/Assumptions!$C$53</f>
+        <f>Assumptions!$C$84/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7489,7 +7554,7 @@
         </is>
       </c>
       <c r="C37" s="21">
-        <f>((Assumptions!$C$51-Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47))*C36*DCF!C61-Assumptions!$C$54</f>
+        <f>((Assumptions!$C$52-Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48))*C36*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7500,7 +7565,7 @@
         </is>
       </c>
       <c r="C38" s="40">
-        <f>(Assumptions!$C$51-Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47)</f>
+        <f>(Assumptions!$C$52-Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
@@ -7511,7 +7576,7 @@
         </is>
       </c>
       <c r="C39" s="10">
-        <f>((Assumptions!$C$51-0.02-0.015)/(0.5*(DCF!C10+DCF!C21)-0.015))*C36*DCF!C61-Assumptions!$C$54</f>
+        <f>((Assumptions!$C$52-0.02-0.015)/(0.5*(DCF!C10+DCF!C21)-0.015))*C36*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7522,7 +7587,7 @@
         </is>
       </c>
       <c r="C40" s="10">
-        <f>((Assumptions!$C$51+0.02-Assumptions!$C$47)/(DCF!C21-Assumptions!$C$47))*C36*DCF!C61-Assumptions!$C$54</f>
+        <f>((Assumptions!$C$52+0.02-Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48))*C36*DCF!C61-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -7621,11 +7686,11 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C8" s="33">
-        <f>Assumptions!$C$40</f>
+          <t>Beta (switchable: adopted index / alternative benchmark)</t>
+        </is>
+      </c>
+      <c r="C8" s="35">
+        <f>Assumptions!$C$40*(1-Assumptions!$C$68)+Assumptions!$C$41*Assumptions!$C$68</f>
         <v/>
       </c>
     </row>
@@ -7636,7 +7701,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
@@ -7658,7 +7723,7 @@
         </is>
       </c>
       <c r="C11" s="18">
-        <f>Assumptions!$C$44</f>
+        <f>Assumptions!$C$45</f>
         <v/>
       </c>
     </row>
@@ -7691,7 +7756,7 @@
         </is>
       </c>
       <c r="C14" s="31">
-        <f>Assumptions!$C$52*Assumptions!$C$53</f>
+        <f>Assumptions!$C$53*Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7702,7 +7767,7 @@
         </is>
       </c>
       <c r="C15" s="37">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
     </row>
@@ -7724,7 +7789,7 @@
         </is>
       </c>
       <c r="C17" s="43">
-        <f>(1-C16)*C10+C16*C13+Assumptions!$C$65</f>
+        <f>(1-C16)*C10+C16*C13+Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -7742,7 +7807,7 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -7753,7 +7818,7 @@
         </is>
       </c>
       <c r="C21" s="42">
-        <f>C20+Assumptions!$C$40*Assumptions!$C$43</f>
+        <f>C20+C8*Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
@@ -7764,7 +7829,7 @@
         </is>
       </c>
       <c r="C22" s="42">
-        <f>Assumptions!$C$45*(1-C12)</f>
+        <f>Assumptions!$C$46*(1-C12)</f>
         <v/>
       </c>
     </row>
@@ -7775,7 +7840,7 @@
         </is>
       </c>
       <c r="C23" s="9">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -7786,7 +7851,7 @@
         </is>
       </c>
       <c r="C24" s="43">
-        <f>(1-C23)*C21+C23*C22+Assumptions!$C$65</f>
+        <f>(1-C23)*C21+C23*C22+Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -8131,23 +8196,23 @@
         </is>
       </c>
       <c r="B39" s="31">
-        <f>Assumptions!B22*Assumptions!$C$64</f>
+        <f>Assumptions!B22*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="C39" s="31">
-        <f>Assumptions!C22*Assumptions!$C$64</f>
+        <f>Assumptions!C22*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="D39" s="31">
-        <f>Assumptions!D22*Assumptions!$C$64</f>
+        <f>Assumptions!D22*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="E39" s="31">
-        <f>Assumptions!E22*Assumptions!$C$64</f>
+        <f>Assumptions!E22*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="F39" s="31">
-        <f>Assumptions!F22*Assumptions!$C$64</f>
+        <f>Assumptions!F22*Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -8185,7 +8250,7 @@
         </is>
       </c>
       <c r="B41" s="31">
-        <f>B40-Assumptions!$C$74</f>
+        <f>B40-Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="C41" s="31">
@@ -8293,23 +8358,23 @@
         </is>
       </c>
       <c r="B45" s="31">
-        <f>Assumptions!B24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <f>Assumptions!B24*Assumptions!$C$58*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="C45" s="31">
-        <f>Assumptions!C24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <f>Assumptions!C24*Assumptions!$C$58*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="D45" s="31">
-        <f>Assumptions!D24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <f>Assumptions!D24*Assumptions!$C$58*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="E45" s="31">
-        <f>Assumptions!E24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <f>Assumptions!E24*Assumptions!$C$58*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="F45" s="31">
-        <f>Assumptions!F24*Assumptions!$C$57*Assumptions!$C$64</f>
+        <f>Assumptions!F24*Assumptions!$C$58*Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -8320,7 +8385,7 @@
         </is>
       </c>
       <c r="B46" s="31">
-        <f>Assumptions!$C$77+B39+B45-B35</f>
+        <f>Assumptions!$C$79+B39+B45-B35</f>
         <v/>
       </c>
       <c r="C46" s="31">
@@ -8347,23 +8412,23 @@
         </is>
       </c>
       <c r="B47" s="31">
-        <f>B46+Assumptions!$C$78+B40</f>
+        <f>B46+Assumptions!$C$80+B40</f>
         <v/>
       </c>
       <c r="C47" s="31">
-        <f>C46+Assumptions!$C$78+C40</f>
+        <f>C46+Assumptions!$C$80+C40</f>
         <v/>
       </c>
       <c r="D47" s="31">
-        <f>D46+Assumptions!$C$78+D40</f>
+        <f>D46+Assumptions!$C$80+D40</f>
         <v/>
       </c>
       <c r="E47" s="31">
-        <f>E46+Assumptions!$C$78+E40</f>
+        <f>E46+Assumptions!$C$80+E40</f>
         <v/>
       </c>
       <c r="F47" s="31">
-        <f>F46+Assumptions!$C$78+F40</f>
+        <f>F46+Assumptions!$C$80+F40</f>
         <v/>
       </c>
     </row>
@@ -8381,7 +8446,7 @@
         </is>
       </c>
       <c r="C50" s="36">
-        <f>F37*(1+Assumptions!$C$47)</f>
+        <f>F37*(1+Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
@@ -8403,7 +8468,7 @@
         </is>
       </c>
       <c r="C52" s="42">
-        <f>Assumptions!$C$47/C51</f>
+        <f>Assumptions!$C$48/C51</f>
         <v/>
       </c>
     </row>
@@ -8414,7 +8479,7 @@
         </is>
       </c>
       <c r="C53" s="31">
-        <f>C50*(1-C52)/(C24-Assumptions!$C$47)</f>
+        <f>C50*(1-C52)/(C24-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
@@ -8480,7 +8545,7 @@
         </is>
       </c>
       <c r="C60" s="10">
-        <f>C59/Assumptions!$C$53</f>
+        <f>C59/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -8491,7 +8556,7 @@
         </is>
       </c>
       <c r="C61" s="44">
-        <f>(1+C10)^(Assumptions!$C$55/365)</f>
+        <f>(1+C10)^(Assumptions!$C$56/365)</f>
         <v/>
       </c>
     </row>
@@ -8502,7 +8567,7 @@
         </is>
       </c>
       <c r="C62" s="10">
-        <f>C60*C61-Assumptions!$C$54</f>
+        <f>C60*C61-Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -8513,7 +8578,7 @@
         </is>
       </c>
       <c r="C63" s="44">
-        <f>(1+Assumptions!B29)^(Assumptions!$C$55/365)</f>
+        <f>(1+Assumptions!B29)^(Assumptions!$C$56/365)</f>
         <v/>
       </c>
     </row>
@@ -9002,7 +9067,7 @@
         <v>189.975</v>
       </c>
       <c r="E15" s="36">
-        <f>Assumptions!$C$73*(1+Assumptions!B30)</f>
+        <f>Assumptions!$C$75*(1+Assumptions!B30)</f>
         <v/>
       </c>
       <c r="F15" s="36">
@@ -9155,23 +9220,23 @@
         <v/>
       </c>
       <c r="E19" s="35">
-        <f>E18*Assumptions!$C$81</f>
+        <f>E18*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="F19" s="35">
-        <f>F18*Assumptions!$C$81</f>
+        <f>F18*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="G19" s="35">
-        <f>G18*Assumptions!$C$81</f>
+        <f>G18*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="H19" s="35">
-        <f>H18*Assumptions!$C$81</f>
+        <f>H18*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="I19" s="35">
-        <f>I18*Assumptions!$C$81</f>
+        <f>I18*Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -9218,35 +9283,35 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>B20/Assumptions!$C$53</f>
+        <f>B20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>C20/Assumptions!$C$53</f>
+        <f>C20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>D20/Assumptions!$C$53</f>
+        <f>D20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>E20/Assumptions!$C$53</f>
+        <f>E20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>F20/Assumptions!$C$53</f>
+        <f>F20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>G20/Assumptions!$C$53</f>
+        <f>G20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="H21" s="10">
-        <f>H20/Assumptions!$C$53</f>
+        <f>H20/Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="I21" s="10">
-        <f>I20/Assumptions!$C$53</f>
+        <f>I20/Assumptions!$C$54</f>
         <v/>
       </c>
     </row>

--- a/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
+++ b/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,22 +128,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,13 +164,15 @@
     <xf numFmtId="172" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -902,7 +905,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8.01% -&gt; 7.50% on the same easing calendar as the cost-of-debt path; the terminal value is</t>
+          <t>8.00% -&gt; 7.50% on the same easing calendar as the cost-of-debt path; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -933,7 +936,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Currency. AED million unless stated. Spot AED 5.24 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+          <t>Currency. AED million unless stated. Spot AED 4.97 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1059,32 @@
           <t>Fleet assets (PP&amp;E + right-of-use + aircraft advances)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="27" t="n">
         <v>6415.231</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>6708.975</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="27" t="n">
         <v>8670.864</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>DCF!B46</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>DCF!C46</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>DCF!D46</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>DCF!E46</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>DCF!F46</f>
         <v/>
       </c>
@@ -1092,27 +1095,27 @@
           <t>Intangible assets</t>
         </is>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>1362.497</v>
       </c>
-      <c r="E6" s="17">
-        <f>Assumptions!$C$80</f>
-        <v/>
-      </c>
-      <c r="F6" s="17">
-        <f>Assumptions!$C$80</f>
-        <v/>
-      </c>
-      <c r="G6" s="17">
-        <f>Assumptions!$C$80</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
-        <f>Assumptions!$C$80</f>
-        <v/>
-      </c>
-      <c r="I6" s="17">
-        <f>Assumptions!$C$80</f>
+      <c r="E6" s="18">
+        <f>Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
+        <f>Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="I6" s="18">
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -1129,13 +1132,13 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <v>48.719</v>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="27" t="n">
         <v>53.456</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="27" t="n">
         <v>97.042</v>
       </c>
     </row>
@@ -1145,13 +1148,13 @@
           <t>Trade and other receivables (current)</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="27" t="n">
         <v>858.576</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="27" t="n">
         <v>824.296</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="27" t="n">
         <v>896.388</v>
       </c>
     </row>
@@ -1161,13 +1164,13 @@
           <t>Cash and fixed deposits</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="27" t="n">
         <v>5246.377</v>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="27" t="n">
         <v>5319.517</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="27" t="n">
         <v>5198.732</v>
       </c>
     </row>
@@ -1177,13 +1180,13 @@
           <t>Borrowings + lease liabilities</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="27" t="n">
         <v>2278.957</v>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="27" t="n">
         <v>2101.441</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="27" t="n">
         <v>2781.435</v>
       </c>
     </row>
@@ -1193,13 +1196,13 @@
           <t>Payables, deferred income, provisions (operating)</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <v>4825.511</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <v>5085.291999999999</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="27" t="n">
         <v>6180.264</v>
       </c>
     </row>
@@ -1209,32 +1212,32 @@
           <t>Equity attributable to owners</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>7534.006</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>7950.33</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <v>8408.904</v>
       </c>
-      <c r="E15" s="31">
-        <f>Assumptions!$C$84+'Income Statement'!E20-'Cash Flow'!B15</f>
-        <v/>
-      </c>
-      <c r="F15" s="31">
+      <c r="E15" s="32">
+        <f>Assumptions!$C$87+'Income Statement'!E20-'Cash Flow'!B15</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
         <f>E15+'Income Statement'!F20-'Cash Flow'!C15</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>F15+'Income Statement'!G20-'Cash Flow'!D15</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>G15+'Income Statement'!H20-'Cash Flow'!E15</f>
         <v/>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="32">
         <f>H15+'Income Statement'!I20-'Cash Flow'!F15</f>
         <v/>
       </c>
@@ -1245,35 +1248,35 @@
           <t>Working capital (from the lines above)</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="32">
         <f>B8+B9-B13</f>
         <v/>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>C8+C9-C13</f>
         <v/>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>D8+D9-D13</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="18">
         <f>DCF!B40</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="18">
         <f>DCF!C40</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="18">
         <f>DCF!D40</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="18">
         <f>DCF!E40</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="18">
         <f>DCF!F40</f>
         <v/>
       </c>
@@ -1284,35 +1287,35 @@
           <t>Net debt (negative = net cash)</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>B12-B10</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C12-C10</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D12-D10</f>
         <v/>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="18">
         <f>'Cash Flow'!B16</f>
         <v/>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="18">
         <f>'Cash Flow'!C16</f>
         <v/>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="18">
         <f>'Cash Flow'!D16</f>
         <v/>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="18">
         <f>'Cash Flow'!E16</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="18">
         <f>'Cash Flow'!F16</f>
         <v/>
       </c>
@@ -1323,41 +1326,41 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="41">
         <f>B17/'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="41">
         <f>C17/'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="41">
         <f>D17/'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="41">
         <f>E17/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="41">
         <f>F17/'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="41">
         <f>G17/'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="41">
         <f>H17/'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="41">
         <f>I17/'Income Statement'!I9</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>The forecast rolls fleet assets (capex less depreciation plus leased-fleet additions), working capital (ratio x revenue), net debt (opening less retained cash generation plus dividends) and equity (profit less dividends). Deferred income, maintenance provisions and staff benefits are inside working capital — never double-counted against net debt.</t>
         </is>
@@ -1446,23 +1449,23 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <f>DCF!B37</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>DCF!C37</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>DCF!D37</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>DCF!E37</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>DCF!F37</f>
         <v/>
       </c>
@@ -1473,23 +1476,23 @@
           <t>add depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <f>DCF!B38</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <f>DCF!C38</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>DCF!D38</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>DCF!E38</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>DCF!F38</f>
         <v/>
       </c>
@@ -1500,23 +1503,23 @@
           <t>less owned capex + pre-delivery payments</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <f>DCF!B39</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>DCF!C39</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>DCF!D39</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>DCF!E39</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>DCF!F39</f>
         <v/>
       </c>
@@ -1527,50 +1530,50 @@
           <t>less change in working capital</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <f>DCF!B41</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>DCF!C41</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>DCF!D41</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>DCF!E41</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>DCF!F41</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>B5+B6-B7-B8-B10</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>C5+C6-C7-C8-C10</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>D5+D6-D7-D8-D10</f>
         <v/>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>E5+E6-E7-E8-E10</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>F5+F6-F7-F8-F10</f>
         <v/>
       </c>
@@ -1581,23 +1584,23 @@
           <t>less leased-fleet additions (gross)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <f>DCF!B45</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>DCF!C45</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <f>DCF!D45</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="18">
         <f>DCF!E45</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>DCF!F45</f>
         <v/>
       </c>
@@ -1640,23 +1643,23 @@
           <t>Opening net debt (negative = net cash)</t>
         </is>
       </c>
-      <c r="B12" s="31">
-        <f>Assumptions!$C$77-Assumptions!$C$78</f>
-        <v/>
-      </c>
-      <c r="C12" s="31">
+      <c r="B12" s="32">
+        <f>Assumptions!$C$80-Assumptions!$C$81</f>
+        <v/>
+      </c>
+      <c r="C12" s="32">
         <f>B16</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>C16</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>D16</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>E16</f>
         <v/>
       </c>
@@ -1667,23 +1670,23 @@
           <t>Finance income (deposit yield x opening cash and deposits)</t>
         </is>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>Assumptions!B29*(B17-B12)</f>
         <v/>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>Assumptions!C29*(C17-C12)</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="37">
         <f>Assumptions!D29*(D17-D12)</f>
         <v/>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="37">
         <f>Assumptions!E29*(E17-E12)</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="37">
         <f>Assumptions!F29*(F17-F12)</f>
         <v/>
       </c>
@@ -1694,23 +1697,23 @@
           <t>Finance costs (booked rate x average gross debt)</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>Assumptions!B26*(B17+B18)/2</f>
         <v/>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>Assumptions!C26*(C17+C18)/2</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="37">
         <f>Assumptions!D26*(D17+D18)/2</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="37">
         <f>Assumptions!E26*(E17+E18)/2</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>Assumptions!F26*(F17+F18)/2</f>
         <v/>
       </c>
@@ -1721,24 +1724,24 @@
           <t>Dividends paid (payout, floored at 30 fils)</t>
         </is>
       </c>
-      <c r="B15" s="31">
-        <f>MAX(Assumptions!B31*'Income Statement'!E20,Assumptions!$C$60)</f>
-        <v/>
-      </c>
-      <c r="C15" s="31">
-        <f>MAX(Assumptions!C31*'Income Statement'!F20,Assumptions!$C$60)</f>
-        <v/>
-      </c>
-      <c r="D15" s="31">
-        <f>MAX(Assumptions!D31*'Income Statement'!G20,Assumptions!$C$60)</f>
-        <v/>
-      </c>
-      <c r="E15" s="31">
-        <f>MAX(Assumptions!E31*'Income Statement'!H20,Assumptions!$C$60)</f>
-        <v/>
-      </c>
-      <c r="F15" s="31">
-        <f>MAX(Assumptions!F31*'Income Statement'!I20,Assumptions!$C$60)</f>
+      <c r="B15" s="32">
+        <f>MAX(Assumptions!B31*'Income Statement'!E20,Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="C15" s="32">
+        <f>MAX(Assumptions!C31*'Income Statement'!F20,Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="D15" s="32">
+        <f>MAX(Assumptions!D31*'Income Statement'!G20,Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>MAX(Assumptions!E31*'Income Statement'!H20,Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>MAX(Assumptions!F31*'Income Statement'!I20,Assumptions!$C$63)</f>
         <v/>
       </c>
     </row>
@@ -1748,23 +1751,23 @@
           <t>Closing net debt</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="33">
         <f>B12-(B9+(B13-B14)*(1-Assumptions!$C$36))+B15</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>C12-(C9+(C13-C14)*(1-Assumptions!$C$36))+C15</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="33">
         <f>D12-(D9+(D13-D14)*(1-Assumptions!$C$36))+D15</f>
         <v/>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="33">
         <f>E12-(E9+(E13-E14)*(1-Assumptions!$C$36))+E15</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="33">
         <f>F12-(F9+(F13-F14)*(1-Assumptions!$C$36))+F15</f>
         <v/>
       </c>
@@ -1775,23 +1778,23 @@
           <t>Opening gross debt (borrowings + leases)</t>
         </is>
       </c>
-      <c r="B17" s="17">
-        <f>Assumptions!$C$77</f>
-        <v/>
-      </c>
-      <c r="C17" s="31">
+      <c r="B17" s="18">
+        <f>Assumptions!$C$80</f>
+        <v/>
+      </c>
+      <c r="C17" s="32">
         <f>B18</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>C18</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>D18</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>E18</f>
         <v/>
       </c>
@@ -1802,24 +1805,24 @@
           <t>Closing gross debt (+ new leases + aircraft loans - amortisation)</t>
         </is>
       </c>
-      <c r="B18" s="31">
-        <f>B17+DCF!B45+Assumptions!B23*Assumptions!$C$59-Assumptions!B27</f>
-        <v/>
-      </c>
-      <c r="C18" s="31">
-        <f>C17+DCF!C45+Assumptions!C23*Assumptions!$C$59-Assumptions!C27</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>D17+DCF!D45+Assumptions!D23*Assumptions!$C$59-Assumptions!D27</f>
-        <v/>
-      </c>
-      <c r="E18" s="31">
-        <f>E17+DCF!E45+Assumptions!E23*Assumptions!$C$59-Assumptions!E27</f>
-        <v/>
-      </c>
-      <c r="F18" s="31">
-        <f>F17+DCF!F45+Assumptions!F23*Assumptions!$C$59-Assumptions!F27</f>
+      <c r="B18" s="32">
+        <f>B17+DCF!B45+Assumptions!B23*Assumptions!$C$62-Assumptions!B27</f>
+        <v/>
+      </c>
+      <c r="C18" s="32">
+        <f>C17+DCF!C45+Assumptions!C23*Assumptions!$C$62-Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D18" s="32">
+        <f>D17+DCF!D45+Assumptions!D23*Assumptions!$C$62-Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>E17+DCF!E45+Assumptions!E23*Assumptions!$C$62-Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>F17+DCF!F45+Assumptions!F23*Assumptions!$C$62-Assumptions!F27</f>
         <v/>
       </c>
     </row>
@@ -1851,13 +1854,13 @@
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>2304.108</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>2278.691</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <v>2860.401</v>
       </c>
     </row>
@@ -1867,13 +1870,13 @@
           <t>Fleet capex incl. aircraft advances</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>378.035</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>579.654</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="27" t="n">
         <v>2327.603</v>
       </c>
     </row>
@@ -1883,13 +1886,13 @@
           <t>Dividends paid to owners</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>700.005</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>933.34</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="27" t="n">
         <v>1167.376</v>
       </c>
     </row>
@@ -1899,13 +1902,13 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>647.327</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>648.588</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="27" t="n">
         <v>621.798</v>
       </c>
     </row>
@@ -2000,35 +2003,35 @@
           <t>Revenue (AED mn)</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <f>'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
@@ -2039,31 +2042,31 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="9">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <f>I5/H5-1</f>
         <v/>
       </c>
@@ -2074,35 +2077,35 @@
           <t>EBITDA (AED mn)</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <f>'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="18">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="18">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="18">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
@@ -2113,35 +2116,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="16">
         <f>'Income Statement'!B22</f>
         <v/>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="16">
         <f>'Income Statement'!C22</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="16">
         <f>'Income Statement'!D22</f>
         <v/>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="16">
         <f>'Income Statement'!E22</f>
         <v/>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="16">
         <f>'Income Statement'!F22</f>
         <v/>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="16">
         <f>'Income Statement'!G22</f>
         <v/>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="16">
         <f>'Income Statement'!H22</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="16">
         <f>'Income Statement'!I22</f>
         <v/>
       </c>
@@ -2152,35 +2155,35 @@
           <t>Attributable profit (AED mn)</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="18">
         <f>'Income Statement'!B20</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <f>'Income Statement'!C20</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="18">
         <f>'Income Statement'!F20</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="18">
         <f>'Income Statement'!G20</f>
         <v/>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="18">
         <f>'Income Statement'!H20</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="18">
         <f>'Income Statement'!I20</f>
         <v/>
       </c>
@@ -2239,24 +2242,24 @@
       <c r="D11" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="E11" s="10">
-        <f>'Cash Flow'!B15/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
-        <f>'Cash Flow'!C15/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="G11" s="10">
-        <f>'Cash Flow'!D15/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="H11" s="10">
-        <f>'Cash Flow'!E15/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="I11" s="10">
-        <f>'Cash Flow'!F15/Assumptions!$C$54</f>
+      <c r="E11" s="15">
+        <f>'Cash Flow'!B15/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="F11" s="15">
+        <f>'Cash Flow'!C15/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="G11" s="15">
+        <f>'Cash Flow'!D15/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="H11" s="15">
+        <f>'Cash Flow'!E15/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="I11" s="15">
+        <f>'Cash Flow'!F15/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -2266,35 +2269,35 @@
           <t>Net debt (AED mn, negative = net cash)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <f>'Balance Sheet'!B17</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <f>'Balance Sheet'!C17</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>'Balance Sheet'!D17</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <f>'Balance Sheet'!E17</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>'Balance Sheet'!F17</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="18">
         <f>'Balance Sheet'!G17</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="18">
         <f>'Balance Sheet'!H17</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="18">
         <f>'Balance Sheet'!I17</f>
         <v/>
       </c>
@@ -2305,23 +2308,23 @@
           <t>Invested capital (AED mn)</t>
         </is>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="18">
         <f>DCF!B47</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="18">
         <f>DCF!C47</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="18">
         <f>DCF!D47</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="18">
         <f>DCF!E47</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>DCF!F47</f>
         <v/>
       </c>
@@ -2332,23 +2335,23 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <f>DCF!B37/DCF!B47</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <f>DCF!C37/DCF!C47</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <f>DCF!D37/DCF!D47</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="9">
         <f>DCF!E37/DCF!E47</f>
         <v/>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <f>DCF!F37/DCF!F47</f>
         <v/>
       </c>
@@ -2359,23 +2362,23 @@
           <t>Return on equity (attributable, opening equity)</t>
         </is>
       </c>
-      <c r="E15" s="11">
-        <f>'Income Statement'!E20/Assumptions!$C$84</f>
-        <v/>
-      </c>
-      <c r="F15" s="11">
+      <c r="E15" s="9">
+        <f>'Income Statement'!E20/Assumptions!$C$87</f>
+        <v/>
+      </c>
+      <c r="F15" s="9">
         <f>'Income Statement'!F20/'Balance Sheet'!E15</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="9">
         <f>'Income Statement'!G20/'Balance Sheet'!F15</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="9">
         <f>'Income Statement'!H20/'Balance Sheet'!G15</f>
         <v/>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <f>'Income Statement'!I20/'Balance Sheet'!H15</f>
         <v/>
       </c>
@@ -2386,32 +2389,32 @@
           <t>Passengers (millions)</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>10.11</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>11.22</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>13.06</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>Segments!B5</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>Segments!C5</f>
         <v/>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="34">
         <f>Segments!D5</f>
         <v/>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="34">
         <f>Segments!E5</f>
         <v/>
       </c>
-      <c r="I16" s="33">
+      <c r="I16" s="34">
         <f>Segments!F5</f>
         <v/>
       </c>
@@ -2422,35 +2425,35 @@
           <t>Revenue per passenger (AED, total revenue basis)</t>
         </is>
       </c>
-      <c r="B17" s="36">
+      <c r="B17" s="37">
         <f>B5/B16</f>
         <v/>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="37">
         <f>C5/C16</f>
         <v/>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="37">
         <f>D5/D16</f>
         <v/>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="37">
         <f>E5/E16</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="37">
         <f>F5/F16</f>
         <v/>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="37">
         <f>G5/G16</f>
         <v/>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="37">
         <f>H5/H16</f>
         <v/>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="37">
         <f>I5/I16</f>
         <v/>
       </c>
@@ -2523,12 +2526,12 @@
           <t>Check date</t>
         </is>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
@@ -2605,10 +2608,10 @@
           <t>Probability of finishing above spot</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <v>0.49236</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>0.48994</v>
       </c>
     </row>
@@ -2618,10 +2621,10 @@
           <t>Probability of +10% or better at the check date</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="26" t="n">
         <v>0.14406</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="26" t="n">
         <v>0.25934</v>
       </c>
     </row>
@@ -2631,10 +2634,10 @@
           <t>Probability of -10% or worse at the check date</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <v>0.1286</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <v>0.25472</v>
       </c>
     </row>
@@ -2644,10 +2647,10 @@
           <t>Probability of TOUCHING +10% at any point</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <v>0.24206</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <v>0.48584</v>
       </c>
     </row>
@@ -2657,15 +2660,15 @@
           <t>Probability of TOUCHING -10% at any point</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <v>0.21184</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="26" t="n">
         <v>0.46226</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Struck at AED 5.24 on 2026-08-07 with a 5.7% trailing dividend yield netted from the drift. How much to trust these bands: over the stock's full history the simulation's probability bands beat a naive random-walk benchmark by a small margin on a standard probabilistic accuracy score (+0.7% over the full 58-window history, 2012-2026), and over the recent four-plus years the two are statistically indistinguishable — the bands are honest, not clairvoyant. Realised outcomes landed inside the 80% band 79% of the time and inside the 90% band 86% of the time over that same full history — ONE window set, quoted identically in the study.</t>
         </is>
@@ -2717,7 +2720,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Fair value per share: terminal cost of capital x terminal growth</t>
         </is>
@@ -2762,19 +2765,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5.905341140512895</v>
+        <v>6.613931971702153</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>6.441330940908468</v>
+        <v>7.22938797416904</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>7.153548771890394</v>
+        <v>8.047303999567715</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>8.147888174250852</v>
+        <v>9.189336112633173</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>9.619869598220205</v>
+        <v>10.88022997212353</v>
       </c>
     </row>
     <row r="7">
@@ -2784,19 +2787,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4.740158047465474</v>
+        <v>5.290650036151688</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5.032830501747734</v>
+        <v>5.628038240398886</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5.396807511432933</v>
+        <v>6.047709804384486</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5.862680511210436</v>
+        <v>6.584966343990367</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6.481460409580206</v>
+        <v>7.298672947301888</v>
       </c>
     </row>
     <row r="8">
@@ -2806,19 +2809,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3.965616670730551</v>
+        <v>4.411265519707568</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4.138882120605236</v>
+        <v>4.611970399626963</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851184061604538</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4.596022640590439</v>
+        <v>5.14175332927026</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4.90757571791659</v>
+        <v>5.502954385226047</v>
       </c>
     </row>
     <row r="9">
@@ -2828,19 +2831,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.414133146576976</v>
+        <v>3.785338160707695</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.521787854080209</v>
+        <v>3.910801948149978</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3.646184424595686</v>
+        <v>4.055845559017758</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.791891894478479</v>
+        <v>4.225812539903896</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3.965308268061985</v>
+        <v>4.428185438899458</v>
       </c>
     </row>
     <row r="10">
@@ -2850,23 +2853,23 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>3.001957904477179</v>
+        <v>3.317696432266285</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>3.070688107460237</v>
+        <v>3.398430090879895</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>3.148234173998356</v>
+        <v>3.489585452220582</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.236631692862467</v>
+        <v>3.593568894394453</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3.338595201098579</v>
+        <v>3.713589416492556</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Fair value per share: explicit x terminal cost of capital</t>
         </is>
@@ -2907,115 +2910,115 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>7.291199444745393</v>
+        <v>8.190595518800578</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5.497924252463902</v>
+        <v>6.152900095652542</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4.424589896535458</v>
+        <v>4.933557898331902</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3.71092502710528</v>
+        <v>4.12305166807534</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3.202640094455821</v>
+        <v>3.545995708484645</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>7.01%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>7.221852734350766</v>
+        <v>8.118262350506111</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>5.446983907888723</v>
+        <v>6.099847501414335</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4.384660179713804</v>
+        <v>4.89203512682659</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3.678311435635568</v>
+        <v>4.089186917413269</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>3.175233199630876</v>
+        <v>3.517578411938233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>7.153548771890394</v>
+        <v>8.046922852356397</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>5.396807511432933</v>
+        <v>6.047521370368907</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3.646184424595686</v>
+        <v>4.055782974525162</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3.148234173998356</v>
+        <v>3.489546608836069</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>9.01%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7.086266699473785</v>
+        <v>7.976559329993601</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>5.347379819429001</v>
+        <v>5.995908808691096</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4.306580646974706</v>
+        <v>4.810679901554656</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3.614534331340568</v>
+        <v>4.022831713053255</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>3.12163493696854</v>
+        <v>3.461893522369199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>10.01%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>7.019986173584717</v>
+        <v>7.907154453209897</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>5.298685963285037</v>
+        <v>5.944997186851519</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>4.268407345143883</v>
+        <v>4.770827598168174</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3.583351729934966</v>
+        <v>3.990325171911993</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3.095427605481774</v>
+        <v>3.434612513025957</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Beta (rightmost column = the Dubai-index cross-check, published not used)</t>
         </is>
@@ -3056,23 +3059,23 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>5.321684379458937</v>
+        <v>5.957451797954994</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>4.811843514618002</v>
+        <v>5.379702321466985</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3.881657483484181</v>
+        <v>4.325720187878041</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>3.512603465076654</v>
+        <v>3.907604314511882</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Fuel cost per passenger (multiplier on the base path)</t>
         </is>
@@ -3113,23 +3116,23 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>5.896497102667804</v>
+        <v>6.443342919647113</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>5.120912414413675</v>
+        <v>5.647211028302799</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3.569743037905427</v>
+        <v>4.054947245614179</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2.794158349651298</v>
+        <v>3.258815354269865</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>Passenger volumes (multiplier)</t>
         </is>
@@ -3170,23 +3173,23 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>3.539464264428549</v>
+        <v>4.024478047929036</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3.942395995294049</v>
+        <v>4.437801581315985</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>4.748259457025044</v>
+        <v>5.264316942610993</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>5.151191187890542</v>
+        <v>5.677520149872032</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Fare per passenger (multiplier)</t>
         </is>
@@ -3227,23 +3230,23 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>2.533114157171959</v>
+        <v>2.991805901498502</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>3.439220941665754</v>
+        <v>3.921439448943881</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>5.251434510653346</v>
+        <v>5.780724545348389</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>6.15754129514714</v>
+        <v>6.710375291402692</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Fleet capex (multiplier)</t>
         </is>
@@ -3284,23 +3287,23 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>4.929586331256607</v>
+        <v>5.363960992397897</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>4.637457028708077</v>
+        <v>5.107520064678192</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3.907133772336755</v>
+        <v>4.466417745378932</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>3.468939818513962</v>
+        <v>4.081756353799374</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>JV network value in the bridge (AED mn)</t>
         </is>
@@ -3341,23 +3344,23 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>4.599175813461317</v>
+        <v>5.105682872488786</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>4.765983861046881</v>
+        <v>5.272987469829767</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>4.891089896736054</v>
+        <v>5.398465917835503</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>5.09959995621801</v>
+        <v>5.607596664511728</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>Working capital / revenue</t>
         </is>
@@ -3398,23 +3401,23 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>4.164118914218613</v>
+        <v>4.666619172766612</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>4.254723320189081</v>
+        <v>4.758849154862552</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>4.345327726159549</v>
+        <v>4.851079136958488</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>4.435932132130015</v>
+        <v>4.943309119054425</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>4.526536538100481</v>
+        <v>5.035539101150361</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Published scenario driver vectors — type these into the Scenario cells on Assumptions to reproduce each pasted output LIVE in this workbook</t>
         </is>
@@ -3468,32 +3471,32 @@
           <t>High-fuel alternative</t>
         </is>
       </c>
-      <c r="B50" s="23" t="n">
+      <c r="B50" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="23" t="n">
+      <c r="C50" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="46" t="inlineStr">
+      <c r="D50" s="48" t="inlineStr">
         <is>
           <t>alternative (switch=1)</t>
         </is>
       </c>
-      <c r="E50" s="23" t="n">
+      <c r="E50" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="46" t="inlineStr">
+      <c r="F50" s="48" t="inlineStr">
         <is>
           <t>0bp</t>
         </is>
       </c>
-      <c r="G50" s="46" t="inlineStr">
+      <c r="G50" s="48" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
       <c r="H50" s="7" t="n">
-        <v>2.299371516993448</v>
+        <v>2.750417615655593</v>
       </c>
     </row>
     <row r="51">
@@ -3502,32 +3505,32 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n">
+      <c r="B51" s="24" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="C51" s="23" t="n">
+      <c r="C51" s="24" t="n">
         <v>0.97</v>
       </c>
-      <c r="D51" s="46" t="inlineStr">
+      <c r="D51" s="48" t="inlineStr">
         <is>
           <t>alternative (switch=1)</t>
         </is>
       </c>
-      <c r="E51" s="23" t="n">
+      <c r="E51" s="24" t="n">
         <v>1.15</v>
       </c>
-      <c r="F51" s="46" t="inlineStr">
+      <c r="F51" s="48" t="inlineStr">
         <is>
           <t>+100bp</t>
         </is>
       </c>
-      <c r="G51" s="46" t="inlineStr">
+      <c r="G51" s="48" t="inlineStr">
         <is>
           <t>1.5%</t>
         </is>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.61686433528253</v>
+        <v>1.121883543030733</v>
       </c>
     </row>
     <row r="52">
@@ -3536,32 +3539,32 @@
           <t>Bull (JV capitalised)</t>
         </is>
       </c>
-      <c r="B52" s="23" t="n">
+      <c r="B52" s="24" t="n">
         <v>1.05</v>
       </c>
-      <c r="C52" s="23" t="n">
+      <c r="C52" s="24" t="n">
         <v>1.03</v>
       </c>
-      <c r="D52" s="46" t="inlineStr">
+      <c r="D52" s="48" t="inlineStr">
         <is>
           <t>base (switch=0)</t>
         </is>
       </c>
-      <c r="E52" s="23" t="n">
+      <c r="E52" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="F52" s="46" t="inlineStr">
+      <c r="F52" s="48" t="inlineStr">
         <is>
           <t>-100bp</t>
         </is>
       </c>
-      <c r="G52" s="46" t="inlineStr">
+      <c r="G52" s="48" t="inlineStr">
         <is>
           <t>3.5%</t>
         </is>
       </c>
       <c r="H52" s="7" t="n">
-        <v>9.684244782121505</v>
+        <v>7.044222881257744</v>
       </c>
     </row>
     <row r="53">
@@ -3666,19 +3669,19 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>Assumptions!$C$55</f>
+        <f>Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>'Cash Flow'!B15/Assumptions!$C$54</f>
+        <f>'Cash Flow'!B15/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>'Cash Flow'!D15/Assumptions!$C$54</f>
+        <f>'Cash Flow'!D15/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>'Cash Flow'!F15/Assumptions!$C$54</f>
+        <f>'Cash Flow'!F15/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -3689,19 +3692,19 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>Assumptions!$C$84/Assumptions!$C$54</f>
+        <f>Assumptions!$C$87/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>'Balance Sheet'!E15/Assumptions!$C$54</f>
+        <f>'Balance Sheet'!E15/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>'Balance Sheet'!G15/Assumptions!$C$54</f>
+        <f>'Balance Sheet'!G15/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>'Balance Sheet'!I15/Assumptions!$C$54</f>
+        <f>'Balance Sheet'!I15/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -3712,15 +3715,15 @@
         </is>
       </c>
       <c r="C8" s="8">
-        <f>'Cash Flow'!B9/Assumptions!$C$54</f>
+        <f>'Cash Flow'!B9/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>'Cash Flow'!D9/Assumptions!$C$54</f>
+        <f>'Cash Flow'!D9/Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>'Cash Flow'!F9/Assumptions!$C$54</f>
+        <f>'Cash Flow'!F9/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -3731,7 +3734,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'SOTP Bridge'!C6/Assumptions!$C$54</f>
+        <f>'SOTP Bridge'!C6/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -3754,8 +3757,8 @@
           <t>Trailing price/earnings</t>
         </is>
       </c>
-      <c r="C12" s="40">
-        <f>Assumptions!$C$53/'Income Statement'!D21</f>
+      <c r="C12" s="41">
+        <f>Assumptions!$C$56/'Income Statement'!D21</f>
         <v/>
       </c>
     </row>
@@ -3765,8 +3768,8 @@
           <t>Forward price/earnings (FY2027E)</t>
         </is>
       </c>
-      <c r="C13" s="40">
-        <f>Assumptions!$C$53/'Income Statement'!F21</f>
+      <c r="C13" s="41">
+        <f>Assumptions!$C$56/'Income Statement'!F21</f>
         <v/>
       </c>
     </row>
@@ -3776,8 +3779,8 @@
           <t>Price / book (FY2025)</t>
         </is>
       </c>
-      <c r="C14" s="40">
-        <f>Assumptions!$C$53/((Assumptions!$C$84)/Assumptions!$C$54)</f>
+      <c r="C14" s="41">
+        <f>Assumptions!$C$56/((Assumptions!$C$87)/Assumptions!$C$57)</f>
         <v/>
       </c>
     </row>
@@ -3787,8 +3790,8 @@
           <t>EV / EBITDA (trailing, incl. fees)</t>
         </is>
       </c>
-      <c r="C15" s="40">
-        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/('Income Statement'!D9+'Income Statement'!D12)</f>
+      <c r="C15" s="41">
+        <f>(DCF!C14+Assumptions!$C$80-Assumptions!$C$81)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
     </row>
@@ -3798,8 +3801,8 @@
           <t>Dividend yield (FY2025 dividend at spot)</t>
         </is>
       </c>
-      <c r="C16" s="11">
-        <f>Assumptions!$C$55/Assumptions!$C$53</f>
+      <c r="C16" s="9">
+        <f>Assumptions!$C$58/Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -3876,10 +3879,10 @@
           <t>Ryanair</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="29" t="n">
         <v>12.6</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>7.81</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -3894,10 +3897,10 @@
           <t>easyJet</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="29" t="n">
         <v>12.39</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>3.48</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -3912,12 +3915,12 @@
           <t>IndiGo</t>
         </is>
       </c>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>11.09</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -3932,10 +3935,10 @@
           <t>Pegasus</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="29" t="n">
         <v>8.9</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>6.58</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -3950,12 +3953,12 @@
           <t>Wizz Air</t>
         </is>
       </c>
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
@@ -3972,10 +3975,10 @@
           <t>Jazeera Airways</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="29" t="n">
         <v>17.7</v>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
@@ -3992,10 +3995,10 @@
           <t>Air transport sector (Damodaran, Jan-2026)</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="29" t="n">
         <v>12.87</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>7.58</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -4005,27 +4008,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Air Arabia (live formulas)</t>
         </is>
       </c>
-      <c r="B12" s="47">
-        <f>Assumptions!$C$53/'Income Statement'!D21</f>
-        <v/>
-      </c>
-      <c r="C12" s="47">
-        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/('Income Statement'!D9+'Income Statement'!D12)</f>
-        <v/>
-      </c>
-      <c r="D12" s="48" t="inlineStr">
+      <c r="B12" s="49">
+        <f>Assumptions!$C$56/'Income Statement'!D21</f>
+        <v/>
+      </c>
+      <c r="C12" s="49">
+        <f>(DCF!C14+Assumptions!$C$80-Assumptions!$C$81)/('Income Statement'!D9+'Income Statement'!D12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>FY2025 audited, spot 07-Aug-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Justified multiples adopted: EV/EBITDA 7.5x (sector centre), P/E 13x (between the mature European carriers ~12.5x and Jazeera ~17.7x). Air Arabia trades above the peer set on both trailing multiples — the relative lens question is whether its net cash, franchise margin and growing JV network justify the premium.</t>
         </is>
@@ -4097,14 +4100,10 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
           <t>vs spot</t>
@@ -4114,28 +4113,25 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (primary)</t>
+          <t>Discounted cash flow (the central)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.61686433528253</v>
+        <v>1.121883543030733</v>
       </c>
       <c r="C5" s="8">
         <f>'Fundamental Valuation'!C5</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>9.684244782121505</v>
-      </c>
-      <c r="E5" s="9">
-        <f>Assumptions!$C$85</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
+        <v>7.044222881257744</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
         <f>C5/$C$16-1</f>
         <v/>
       </c>
@@ -4143,7 +4139,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
+          <t>Relative multiples (cross-check)</t>
         </is>
       </c>
       <c r="B6" s="8">
@@ -4158,15 +4154,12 @@
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
-      <c r="E6" s="9">
-        <f>Assumptions!$C$86</f>
-        <v/>
-      </c>
-      <c r="F6" s="10">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
         <f>C6/$C$16-1</f>
         <v/>
       </c>
@@ -4174,89 +4167,71 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Normalised earnings power</t>
+          <t>Book value and sustainable return (cross-check, a floor)</t>
         </is>
       </c>
       <c r="B7" s="8">
-        <f>'Relative &amp; Normalized'!C31</f>
+        <f>'Relative &amp; Normalized'!C39</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>'Relative &amp; Normalized'!C29</f>
+        <f>'Relative &amp; Normalized'!C37</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>'Relative &amp; Normalized'!C32</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>Assumptions!$C$87</f>
-        <v/>
-      </c>
-      <c r="F7" s="10">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
+        <f>'Relative &amp; Normalized'!C40</f>
+        <v/>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>cross-check (a floor)</t>
+        </is>
+      </c>
+      <c r="G7" s="9">
         <f>C7/$C$16-1</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Book value and sustainable return</t>
-        </is>
-      </c>
-      <c r="B8" s="8">
-        <f>'Relative &amp; Normalized'!C39</f>
-        <v/>
-      </c>
-      <c r="C8" s="8">
-        <f>'Relative &amp; Normalized'!C37</f>
-        <v/>
-      </c>
-      <c r="D8" s="8">
-        <f>'Relative &amp; Normalized'!C40</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>Assumptions!$C$88</f>
-        <v/>
-      </c>
-      <c r="F8" s="10">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Central — the cash-flow lens, and the envelope is its own bear and bull on one clock</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>the class primary, unweighted</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14">
         <f>C8/$C$16-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central (range weighted like the base)</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>B5*E5+B6*E6+B7*E7+B8*E8</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>D5*E5+D6*E6+D7*E7+D8*E8</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUM(E5:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="14">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>The same lens on the other framing of the contested joint-venture judgement (both stated, never averaged)</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>'SOTP Bridge'!C20</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
         <f>C9/$C$16-1</f>
         <v/>
       </c>
@@ -4264,30 +4239,22 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DCF — JV network capitalised (contested judgement, other framing)</t>
+          <t>Normalised earnings power — COMPUTED AND EXCLUDED: not a permitted lens for an airline, whose reported earnings in any year are an accident of the fuel curve and the delivery schedule</t>
         </is>
       </c>
       <c r="C10" s="8">
-        <f>'SOTP Bridge'!C20</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
-        <f>C10/$C$16-1</f>
+        <f>'Relative &amp; Normalized'!C29</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Weighted central on that framing</t>
-        </is>
-      </c>
-      <c r="C11" s="10">
-        <f>C9+Assumptions!$C$85*('SOTP Bridge'!C20-'Fundamental Valuation'!C5)</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>C11/$C$16-1</f>
+          <t>Memo: the retired 45/20/20/15 weighted blend this edition replaced, printed so the change is visible</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>0.45*C5+0.20*C6+0.20*C10+0.15*C7</f>
         <v/>
       </c>
     </row>
@@ -4297,8 +4264,8 @@
           <t>Terminal value share of DCF enterprise value</t>
         </is>
       </c>
-      <c r="C12" s="9">
-        <f>DCF!C57</f>
+      <c r="C12" s="16">
+        <f>DCF!C60</f>
         <v/>
       </c>
     </row>
@@ -4312,7 +4279,7 @@
         <f>'Fundamental Valuation'!C23</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <f>C13/$C$16-1</f>
         <v/>
       </c>
@@ -4324,43 +4291,28 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.299371516993448</v>
-      </c>
-      <c r="G14" s="11">
+        <v>2.750417615655593</v>
+      </c>
+      <c r="G14" s="9">
         <f>C14/$C$16-1</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Widest single-lens span (the DCF scenarios) — labelled, not the weighted range</t>
-        </is>
-      </c>
-      <c r="B15" s="10">
-        <f>MIN(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="D15" s="10">
-        <f>MAX(D5:D8)</f>
-        <v/>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Market price (7-Aug-2026 close)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="16">
-        <f>Assumptions!$C$53</f>
-        <v/>
-      </c>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="17">
+        <f>Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4381,8 +4333,8 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C19" s="17">
-        <f>Assumptions!$C$54</f>
+      <c r="C19" s="18">
+        <f>Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -4392,7 +4344,7 @@
           <t>Market capitalisation (AED mn)</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <f>DCF!C14</f>
         <v/>
       </c>
@@ -4403,7 +4355,7 @@
           <t>Net cash incl. fixed deposits, FY2025 (AED mn)</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <f>'SOTP Bridge'!C6</f>
         <v/>
       </c>
@@ -4414,7 +4366,7 @@
           <t>FY2025 revenue (AED mn)</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="18">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
@@ -4425,7 +4377,7 @@
           <t>FY2025 EBITDA (AED mn)</t>
         </is>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
@@ -4436,7 +4388,7 @@
           <t>FY2025 attributable profit (AED mn)</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="18">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
@@ -4447,7 +4399,7 @@
           <t>Cost of capital — explicit window</t>
         </is>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <f>DCF!C17</f>
         <v/>
       </c>
@@ -4458,7 +4410,7 @@
           <t>Cost of capital — terminal</t>
         </is>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="19">
         <f>DCF!C24</f>
         <v/>
       </c>
@@ -4466,11 +4418,11 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C27" s="9">
-        <f>Assumptions!$C$48</f>
+          <t>Terminal growth (derived from the house inflation and this study's real rate)</t>
+        </is>
+      </c>
+      <c r="C27" s="16">
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
     </row>
@@ -4499,7 +4451,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fundamental valuation — the four lenses and the alternatives</t>
+          <t>Fundamental valuation — the central and the cross-checks beside it</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4528,7 +4480,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (primary)</t>
+          <t>Discounted cash flow — THE CENTRAL</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -4536,7 +4488,7 @@
           <t>FCFF, glide-discounted, JV at carrying value</t>
         </is>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <f>'SOTP Bridge'!C15</f>
         <v/>
       </c>
@@ -4544,7 +4496,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
+          <t>Relative multiples — cross-check</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -4560,49 +4512,49 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Normalised earnings power</t>
+          <t>Book value and sustainable return — cross-check, a disclosed floor</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>13x mid-cycle EPS at current scale</t>
+          <t>Justified price-to-book on FY2025 equity</t>
         </is>
       </c>
       <c r="C7" s="8">
-        <f>'Relative &amp; Normalized'!C29</f>
+        <f>'Relative &amp; Normalized'!C37</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Book value and sustainable return</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Justified price-to-book on FY2025 equity</t>
+          <t>Normalised earnings power — COMPUTED AND EXCLUDED</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>13x mid-cycle EPS; not a permitted lens for an airline, whose reported earnings in any one year are an accident of the fuel curve, the delivery schedule and the load factor</t>
         </is>
       </c>
       <c r="C8" s="8">
-        <f>'Relative &amp; Normalized'!C37</f>
+        <f>'Relative &amp; Normalized'!C29</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="13">
-        <f>Summary!C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Central — one lens, not an average of four</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="11">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4635,7 +4587,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.299371516993448</v>
+        <v>2.750417615655593</v>
       </c>
     </row>
     <row r="15">
@@ -4645,7 +4597,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.61686433528253</v>
+        <v>1.121883543030733</v>
       </c>
     </row>
     <row r="16">
@@ -4655,7 +4607,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>9.684244782121505</v>
+        <v>7.044222881257744</v>
       </c>
     </row>
     <row r="18">
@@ -4677,16 +4629,16 @@
           <t>Expert 1 — earnings power at a justified multiple (live formula)</t>
         </is>
       </c>
-      <c r="C19" s="10">
-        <f>13*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54)*DCF!C61-Assumptions!$C$55</f>
-        <v/>
-      </c>
-      <c r="D19" s="10">
-        <f>10*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54)*DCF!C61-Assumptions!$C$55</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>16*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54)*DCF!C61-Assumptions!$C$55</f>
+      <c r="C19" s="15">
+        <f>13*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$86)/Assumptions!$C$57)*DCF!C66-Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="D19" s="15">
+        <f>10*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$86)/Assumptions!$C$57)*DCF!C66-Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
+        <f>16*(('Segments'!D30*'Segments'!D14+'Segments'!D28-Assumptions!D21+('Cash Flow'!D13-'Cash Flow'!D14)+'Income Statement'!G15)*(1-Assumptions!$C$36)*(1-Assumptions!$C$86)/Assumptions!$C$57)*DCF!C66-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -4696,16 +4648,16 @@
           <t>Expert 2 — owner cash earnings capitalised (live formula)</t>
         </is>
       </c>
-      <c r="C20" s="10">
-        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$83))*(1+Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48)+0.5*(Assumptions!$C$78-Assumptions!$C$77))/Assumptions!$C$54*DCF!C61-Assumptions!$C$55</f>
-        <v/>
-      </c>
-      <c r="D20" s="10">
-        <f>((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$83))*1.015/(0.5*(DCF!C10+DCF!C21)-0.015)/Assumptions!$C$54*DCF!C61-Assumptions!$C$55</f>
-        <v/>
-      </c>
-      <c r="E20" s="10">
-        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$83))*1.035/(DCF!C21-0.035)+2*0.5*(Assumptions!$C$78-Assumptions!$C$77))/Assumptions!$C$54*DCF!C61-Assumptions!$C$55</f>
+      <c r="C20" s="15">
+        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$86))*(1+Assumptions!$C$50)/(DCF!C21-Assumptions!$C$50)+0.5*(Assumptions!$C$81-Assumptions!$C$80))/Assumptions!$C$57*DCF!C66-Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$86))*1.015/(0.5*(DCF!C10+DCF!C21)-0.015)/Assumptions!$C$57*DCF!C66-Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>(((AVERAGE('Cash Flow'!D9:F9)+('Cash Flow'!E13-'Cash Flow'!E14)*(1-Assumptions!$C$36)+'Income Statement'!H15*(1-Assumptions!$C$36)*0.4)*(1-Assumptions!$C$86))*1.035/(DCF!C21-0.035)+2*0.5*(Assumptions!$C$81-Assumptions!$C$80))/Assumptions!$C$57*DCF!C66-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -4716,30 +4668,30 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>4.287753837561748</v>
+        <v>4.313709222231732</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3.125195737078831</v>
+        <v>3.14375015925815</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>4.833516008138254</v>
+        <v>4.861096003108747</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="23">
         <f>MEDIAN(C19,C20,C21)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Columns D and E carry each expert's own low and high. The spot price on the anchor date is AED 5.24.</t>
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Columns D and E carry each expert's own low and high. The spot price on the anchor date is AED 4.97.</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -4826,19 +4778,19 @@
           <t>Passengers (millions)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>12.85</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="24" t="n">
         <v>13.95</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="24" t="n">
         <v>15.15</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="24" t="n">
         <v>16.35</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="24" t="n">
         <v>17.55</v>
       </c>
     </row>
@@ -4848,19 +4800,19 @@
           <t>Passenger + baggage revenue per passenger (AED)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="25" t="n">
         <v>488</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <v>480</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="25" t="n">
         <v>484</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="25" t="n">
         <v>489</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="25" t="n">
         <v>494</v>
       </c>
     </row>
@@ -4870,19 +4822,19 @@
           <t>Ancillary revenue per passenger (AED)</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="25" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <v>75.8</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="25" t="n">
         <v>78.8</v>
       </c>
     </row>
@@ -4892,19 +4844,19 @@
           <t>Cargo revenue growth</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4914,19 +4866,19 @@
           <t>Service revenue growth</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -4936,19 +4888,19 @@
           <t>Hotel revenue growth</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <v>0.03</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <v>0.03</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <v>0.03</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>0.03</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -4958,19 +4910,19 @@
           <t>Aircraft-lease revenue growth</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4980,19 +4932,19 @@
           <t>Effective jet fuel price (USD/bbl) — base path</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>100.7</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <v>85.2</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="25" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <v>90.40000000000001</v>
       </c>
     </row>
@@ -5002,19 +4954,19 @@
           <t>Effective jet fuel price (USD/bbl) — high-fuel alternative</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>108.4</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>105.8</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>106.4</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <v>107.5</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>108.5</v>
       </c>
     </row>
@@ -5024,19 +4976,19 @@
           <t>Staff cost per passenger (AED)</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="25" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <v>89.5</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="25" t="n">
         <v>92.2</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="25" t="n">
         <v>94.90000000000001</v>
       </c>
     </row>
@@ -5046,19 +4998,19 @@
           <t>Maintenance cost per passenger (AED)</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="25" t="n">
         <v>63.8</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="25" t="n">
         <v>66.3</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="25" t="n">
         <v>71.7</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="25" t="n">
         <v>74.59999999999999</v>
       </c>
     </row>
@@ -5068,19 +5020,19 @@
           <t>Landing &amp; overflying charges per passenger (AED)</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="25" t="n">
         <v>36.7</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="25" t="n">
         <v>37.4</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="25" t="n">
         <v>38.2</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="25" t="n">
         <v>38.9</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="25" t="n">
         <v>39.7</v>
       </c>
     </row>
@@ -5090,19 +5042,19 @@
           <t>Handling charges per passenger (AED)</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="25" t="n">
         <v>30.6</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="25" t="n">
         <v>31.2</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="25" t="n">
         <v>31.8</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="25" t="n">
         <v>32.4</v>
       </c>
     </row>
@@ -5112,19 +5064,19 @@
           <t>Other direct cost per passenger (AED)</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="25" t="n">
         <v>41.5</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="25" t="n">
         <v>41.5</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="25" t="n">
         <v>41.5</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="25" t="n">
         <v>41.5</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="25" t="n">
         <v>41.5</v>
       </c>
     </row>
@@ -5134,19 +5086,19 @@
           <t>Administrative cost growth</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5156,19 +5108,19 @@
           <t>Other-income growth</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -5178,19 +5130,19 @@
           <t>Depreciation &amp; amortisation (AED mn)</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>720</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>810</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <v>900</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <v>980</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="27" t="n">
         <v>1060</v>
       </c>
     </row>
@@ -5200,19 +5152,19 @@
           <t>Fleet capital expenditure incl. pre-delivery payments (AED mn)</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>1900</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="27" t="n">
         <v>1900</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="27" t="n">
         <v>1950</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="27" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -5222,19 +5174,19 @@
           <t>Owned aircraft additions (units)</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="27" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5244,19 +5196,19 @@
           <t>Leased aircraft additions (units)</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="27" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5266,19 +5218,19 @@
           <t>Consolidated fleet, year-end (aircraft)</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>61</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="27" t="n">
         <v>64</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="27" t="n">
         <v>68</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="27" t="n">
         <v>72</v>
       </c>
     </row>
@@ -5288,19 +5240,19 @@
           <t>Booked finance-cost rate on the debt book</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="28" t="n">
         <v>0.031</v>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="28" t="n">
         <v>0.033</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="28" t="n">
         <v>0.035</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="28" t="n">
         <v>0.036</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="28" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -5310,19 +5262,19 @@
           <t>Debt amortisation (AED mn)</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>500</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>520</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="27" t="n">
         <v>540</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="27" t="n">
         <v>560</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="27" t="n">
         <v>580</v>
       </c>
     </row>
@@ -5332,19 +5284,19 @@
           <t>Marginal cost of debt path</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="28" t="n">
         <v>0.054</v>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="28" t="n">
         <v>0.052</v>
       </c>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="28" t="n">
         <v>0.051</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="28" t="n">
         <v>0.05</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="28" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5354,19 +5306,19 @@
           <t>Deposit yield path</t>
         </is>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="28" t="n">
         <v>0.041</v>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="28" t="n">
         <v>0.038</v>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="28" t="n">
         <v>0.037</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="28" t="n">
         <v>0.037</v>
       </c>
-      <c r="F29" s="27" t="n">
+      <c r="F29" s="28" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -5376,19 +5328,19 @@
           <t>Growth in the share of joint-venture and associate profit</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="D30" s="25" t="n">
+      <c r="D30" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="26" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5398,19 +5350,19 @@
           <t>Dividend payout ratio</t>
         </is>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <v>0.9</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="26" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -5432,7 +5384,7 @@
           <t>Selling &amp; marketing / revenue</t>
         </is>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="28" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -5442,7 +5394,7 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="26" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -5452,7 +5404,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="26" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5462,7 +5414,7 @@
           <t>AED government bond yield (January-2031 tranche)</t>
         </is>
       </c>
-      <c r="C37" s="27" t="n">
+      <c r="C37" s="28" t="n">
         <v>0.0448</v>
       </c>
     </row>
@@ -5472,7 +5424,7 @@
           <t>Observed sovereign spread at the auction (netted out)</t>
         </is>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="28" t="n">
         <v>0.0004</v>
       </c>
     </row>
@@ -5482,7 +5434,7 @@
           <t>Rating-table sovereign spread (alternative netting, disclosed)</t>
         </is>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="28" t="n">
         <v>0.0042</v>
       </c>
     </row>
@@ -5492,7 +5444,7 @@
           <t>Beta — adopted (own stock, five-year weekly vs the Abu Dhabi market index)</t>
         </is>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C40" s="24" t="n">
         <v>0.8120000000000001</v>
       </c>
     </row>
@@ -5502,7 +5454,7 @@
           <t>Beta — cross-check (same regression vs the Dubai market index)</t>
         </is>
       </c>
-      <c r="C41" s="23" t="n">
+      <c r="C41" s="24" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -5512,7 +5464,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C42" s="27" t="n">
+      <c r="C42" s="28" t="n">
         <v>0.0487</v>
       </c>
     </row>
@@ -5522,7 +5474,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C43" s="27" t="n">
+      <c r="C43" s="28" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -5532,7 +5484,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C44" s="27" t="n">
+      <c r="C44" s="28" t="n">
         <v>0.0475</v>
       </c>
     </row>
@@ -5542,7 +5494,7 @@
           <t>Marginal cost of debt</t>
         </is>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="28" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -5552,7 +5504,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C46" s="27" t="n">
+      <c r="C46" s="28" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5562,457 +5514,487 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C47" s="25" t="n">
+      <c r="C47" s="26" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="n">
-        <v>0.025</v>
+          <t>Terminal real growth (this study assumes only this)</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n">
+        <v>0.0049</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Joint-venture capitalisation multiple</t>
+          <t>Terminal inflation (house macro path, AE — this study may not carry its own)</t>
         </is>
       </c>
       <c r="C49" s="28" t="n">
-        <v>15</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="C50" s="28" t="n">
-        <v>6.5</v>
+        <v>0.02499799999999985</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C51" s="28" t="n">
-        <v>13</v>
+          <t>Weighted useful life of the depreciable asset base (years, from the FY2025 accounting-policy note weighted by the property note's own gross cost)</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="n">
+        <v>17.84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="n">
-        <v>0.18</v>
+          <t>Joint-venture capitalisation multiple</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Spot price (AED)</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>5.24</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="n">
-        <v>4666.7</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share (AED, approved 12 March 2026)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>0.3</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Days from 31-Dec-2025 to the 7-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C56" s="26" t="n">
-        <v>219</v>
+          <t>Spot price (AED)</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>4.97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Fuel intensity (AED per passenger per USD/bbl of effective jet price)</t>
-        </is>
-      </c>
-      <c r="C57" s="29" t="n">
-        <v>1.937</v>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="n">
+        <v>4666.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use value per leased aircraft (AED mn)</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="n">
-        <v>175</v>
+          <t>FY2025 dividend per share (AED, approved 12 March 2026)</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Loan drawn per owned aircraft (AED mn)</t>
-        </is>
-      </c>
-      <c r="C59" s="26" t="n">
-        <v>150</v>
+          <t>Days from 31-Dec-2025 to the 3-Sep-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="n">
+        <v>246</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Dividend floor (AED mn = 30 fils on the full share count)</t>
-        </is>
-      </c>
-      <c r="C60" s="26" t="n">
-        <v>1400</v>
+          <t>Fuel intensity (AED per passenger per USD/bbl of effective jet price)</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>1.937</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Minority interests at carrying value (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C61" s="23" t="n">
-        <v>1.287</v>
+          <t>Right-of-use value per leased aircraft (AED mn)</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Scenario: passenger multiplier</t>
-        </is>
-      </c>
-      <c r="C62" s="23" t="n">
-        <v>1</v>
+          <t>Loan drawn per owned aircraft (AED mn)</t>
+        </is>
+      </c>
+      <c r="C62" s="27" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Scenario: fare multiplier</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="n">
-        <v>1</v>
+          <t>Dividend floor (AED mn = 30 fils on the full share count)</t>
+        </is>
+      </c>
+      <c r="C63" s="27" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Scenario: fuel multiplier</t>
-        </is>
-      </c>
-      <c r="C64" s="23" t="n">
-        <v>1</v>
+          <t>Minority interests at carrying value (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="n">
+        <v>1.287</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Scenario: capital-expenditure multiplier</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="n">
+          <t>Scenario: passenger multiplier</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Scenario: cost-of-capital shift</t>
-        </is>
-      </c>
-      <c r="C66" s="27" t="n">
-        <v>0</v>
+          <t>Scenario: fare multiplier</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Scenario: high-fuel switch (0 = base path, 1 = alternative)</t>
-        </is>
-      </c>
-      <c r="C67" s="23" t="n">
-        <v>0</v>
+          <t>Scenario: fuel multiplier</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Scenario: beta benchmark switch (0 = adopted index, 1 = cross-check index)</t>
-        </is>
-      </c>
-      <c r="C68" s="23" t="n">
-        <v>0</v>
+          <t>Scenario: capital-expenditure multiplier</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Cash administrative costs, FY2025 (AED mn, audited less its depreciation)</t>
-        </is>
-      </c>
-      <c r="C69" s="24" t="n">
-        <v>276.183</v>
+          <t>Scenario: cost-of-capital shift</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>Cargo revenue, FY2025 (AED mn, disclosed)</t>
+          <t>Scenario: high-fuel switch (0 = base path, 1 = alternative)</t>
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>186.948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Service revenue, FY2025 (AED mn, disclosed)</t>
+          <t>Scenario: beta benchmark switch (0 = adopted index, 1 = cross-check index)</t>
         </is>
       </c>
       <c r="C71" s="24" t="n">
-        <v>223.323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Hotel revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="n">
-        <v>59.842</v>
+          <t>Cash administrative costs, FY2025 (AED mn, audited less its depreciation)</t>
+        </is>
+      </c>
+      <c r="C72" s="25" t="n">
+        <v>276.183</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Aircraft-lease revenue, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C73" s="24" t="n">
-        <v>219.755</v>
+          <t>Cargo revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="n">
+        <v>186.948</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Other income, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C74" s="24" t="n">
-        <v>197.132</v>
+          <t>Service revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C74" s="25" t="n">
+        <v>223.323</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Share of JV and associate profit, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C75" s="24" t="n">
-        <v>189.975</v>
+          <t>Hotel revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="n">
+        <v>59.842</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Working capital, FY2025 (AED mn, audited balance sheet)</t>
-        </is>
-      </c>
-      <c r="C76" s="24" t="n">
-        <v>-5186.834</v>
+          <t>Aircraft-lease revenue, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C76" s="25" t="n">
+        <v>219.755</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Gross debt, FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C77" s="24" t="n">
-        <v>2781.435</v>
+          <t>Other income, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C77" s="25" t="n">
+        <v>197.132</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Cash and fixed deposits, FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="n">
-        <v>5198.732</v>
+          <t>Share of JV and associate profit, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C78" s="25" t="n">
+        <v>189.975</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Fleet assets, FY2025 (PP&amp;E + right-of-use + aircraft advances, AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="n">
-        <v>8670.864</v>
+          <t>Working capital, FY2025 (AED mn, audited balance sheet)</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="n">
+        <v>-5186.834</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C80" s="24" t="n">
-        <v>1362.497</v>
+          <t>Gross debt, FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="n">
+        <v>2781.435</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>JV and associates at carrying value (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C81" s="24" t="n">
-        <v>363.386</v>
+          <t>Cash and fixed deposits, FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="n">
+        <v>5198.732</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Non-operating assets (investments + investment property + net investment in lease, AED mn)</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="n">
-        <v>1069.284</v>
+          <t>Fleet assets, FY2025 (PP&amp;E + right-of-use + aircraft advances, AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C82" s="25" t="n">
+        <v>8670.864</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Minority share of profit</t>
-        </is>
-      </c>
-      <c r="C83" s="30" t="n">
-        <v>0.0001596330894835507</v>
+          <t>Intangible assets (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="n">
+        <v>1362.497</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to owners, FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="n">
-        <v>8408.904</v>
+          <t>JV and associates at carrying value (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="n">
+        <v>363.386</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Non-operating assets (investments + investment property + net investment in lease, AED mn)</t>
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>0.45</v>
+        <v>1069.284</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C86" s="25" t="n">
-        <v>0.2</v>
+          <t>Minority share of profit</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="n">
+        <v>0.0001596330894835507</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Equity attributable to owners, FY2025 (AED mn, audited)</t>
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>0.2</v>
+        <v>8408.904</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C88" s="25" t="n">
-        <v>0.15</v>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Relative lens — bear multiple</t>
-        </is>
-      </c>
-      <c r="C89" s="28" t="n">
-        <v>5</v>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Relative lens — bull multiple</t>
-        </is>
-      </c>
-      <c r="C90" s="28" t="n">
-        <v>8</v>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C90" s="26" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Normalised lens — bear P/E</t>
-        </is>
-      </c>
-      <c r="C91" s="28" t="n">
-        <v>10</v>
+          <t>Weight — book</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
+          <t>Relative lens — bear multiple</t>
+        </is>
+      </c>
+      <c r="C92" s="29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Relative lens — bull multiple</t>
+        </is>
+      </c>
+      <c r="C93" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Normalised lens — bear P/E</t>
+        </is>
+      </c>
+      <c r="C94" s="29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
           <t>Normalised lens — bull P/E</t>
         </is>
       </c>
-      <c r="C92" s="28" t="n">
+      <c r="C95" s="29" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6078,8 +6060,8 @@
           <t>Enterprise value of the airline (DCF)</t>
         </is>
       </c>
-      <c r="C5" s="17">
-        <f>DCF!C56</f>
+      <c r="C5" s="18">
+        <f>DCF!C59</f>
         <v/>
       </c>
     </row>
@@ -6089,8 +6071,8 @@
           <t>plus net cash (cash + deposits - borrowings - leases)</t>
         </is>
       </c>
-      <c r="C6" s="31">
-        <f>Assumptions!$C$78-Assumptions!$C$77</f>
+      <c r="C6" s="32">
+        <f>Assumptions!$C$81-Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -6100,8 +6082,8 @@
           <t>plus non-operating assets</t>
         </is>
       </c>
-      <c r="C7" s="17">
-        <f>Assumptions!$C$82</f>
+      <c r="C7" s="18">
+        <f>Assumptions!$C$85</f>
         <v/>
       </c>
     </row>
@@ -6111,18 +6093,18 @@
           <t>plus JV network at audited carrying value</t>
         </is>
       </c>
-      <c r="C8" s="17">
-        <f>Assumptions!$C$81</f>
+      <c r="C8" s="18">
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Equity before minorities</t>
         </is>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
@@ -6133,18 +6115,18 @@
           <t>less minorities at audited carrying value</t>
         </is>
       </c>
-      <c r="C11" s="33">
-        <f>Assumptions!$C$61</f>
+      <c r="C11" s="34">
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>C9-C11</f>
         <v/>
       </c>
@@ -6155,19 +6137,19 @@
           <t>Per share at 31-Dec-2025</t>
         </is>
       </c>
-      <c r="C14" s="10">
-        <f>C13/Assumptions!$C$54</f>
+      <c r="C14" s="15">
+        <f>C13/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Per share at the anchor — operating equity rolled at the cost of equity, cash and near-cash legs at the deposit yield</t>
         </is>
       </c>
-      <c r="C15" s="21">
-        <f>(C5*DCF!C61+(C6+C7+C8)*DCF!C63-C11)/Assumptions!$C$54-Assumptions!$C$55</f>
+      <c r="C15" s="23">
+        <f>(C5*DCF!C66+(C6+C7+C8)*DCF!C68-C11)/Assumptions!$C$57-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -6190,8 +6172,8 @@
           <t>JV network capitalised (multiple x FY2025 profit share)</t>
         </is>
       </c>
-      <c r="C18" s="31">
-        <f>Assumptions!$C$49*Assumptions!$C$75</f>
+      <c r="C18" s="32">
+        <f>Assumptions!$C$52*Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -6201,19 +6183,19 @@
           <t>Equity attributable on this framing</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C5+C6+C7+C18-C11</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Per share at the anchor — JV capitalised</t>
         </is>
       </c>
-      <c r="C20" s="21">
-        <f>(C5*DCF!C61+(C6+C7+C18)*DCF!C63-C11)/Assumptions!$C$54-Assumptions!$C$55</f>
+      <c r="C20" s="23">
+        <f>(C5*DCF!C66+(C6+C7+C18)*DCF!C68-C11)/Assumptions!$C$57-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -6236,7 +6218,7 @@
           <t>Investments at fair value through OCI</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="25" t="n">
         <v>457.528</v>
       </c>
     </row>
@@ -6246,7 +6228,7 @@
           <t>Investment property (book; disclosed fair value AED 334mn)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n">
+      <c r="C24" s="25" t="n">
         <v>277.09</v>
       </c>
     </row>
@@ -6256,23 +6238,23 @@
           <t>Net investment in lease (aircraft subleased to the JV airlines)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <v>334.666</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Total non-operating assets</t>
         </is>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="35">
         <f>SUM(C23:C25)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>The JV network: Air Arabia Abu Dhabi (49%), Air Arabia Egypt (49%, raised from 40% in 2025), Fly Jinnah (45%), Air Arabia Maroc (44.13%), Air Arabia DMM — Saudi Arabia (49%, pre-operational). FY2025 profit share AED 190.0mn; audited carrying value AED 363.4mn.</t>
         </is>
@@ -6361,24 +6343,24 @@
           <t>Passengers (millions)</t>
         </is>
       </c>
-      <c r="B5" s="35">
-        <f>Assumptions!B5*Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="C5" s="35">
-        <f>Assumptions!C5*Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="D5" s="35">
-        <f>Assumptions!D5*Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="E5" s="35">
-        <f>Assumptions!E5*Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="F5" s="35">
-        <f>Assumptions!F5*Assumptions!$C$62</f>
+      <c r="B5" s="36">
+        <f>Assumptions!B5*Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="C5" s="36">
+        <f>Assumptions!C5*Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="D5" s="36">
+        <f>Assumptions!D5*Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="E5" s="36">
+        <f>Assumptions!E5*Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="F5" s="36">
+        <f>Assumptions!F5*Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -6388,24 +6370,24 @@
           <t>Revenue per passenger — fare + baggage (AED)</t>
         </is>
       </c>
-      <c r="B6" s="36">
-        <f>Assumptions!B6*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="C6" s="36">
-        <f>Assumptions!C6*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="D6" s="36">
-        <f>Assumptions!D6*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="E6" s="36">
-        <f>Assumptions!E6*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="F6" s="36">
-        <f>Assumptions!F6*Assumptions!$C$63</f>
+      <c r="B6" s="37">
+        <f>Assumptions!B6*Assumptions!$C$66</f>
+        <v/>
+      </c>
+      <c r="C6" s="37">
+        <f>Assumptions!C6*Assumptions!$C$66</f>
+        <v/>
+      </c>
+      <c r="D6" s="37">
+        <f>Assumptions!D6*Assumptions!$C$66</f>
+        <v/>
+      </c>
+      <c r="E6" s="37">
+        <f>Assumptions!E6*Assumptions!$C$66</f>
+        <v/>
+      </c>
+      <c r="F6" s="37">
+        <f>Assumptions!F6*Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -6415,23 +6397,23 @@
           <t>Passenger and baggage revenue</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="32">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>F5*F6</f>
         <v/>
       </c>
@@ -6442,23 +6424,23 @@
           <t>Ancillary rate (AED per passenger)</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="38">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="38">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="38">
         <f>Assumptions!D7</f>
         <v/>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="38">
         <f>Assumptions!E7</f>
         <v/>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="38">
         <f>Assumptions!F7</f>
         <v/>
       </c>
@@ -6469,23 +6451,23 @@
           <t>Ancillary revenue</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>B5*B8</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>C5*C8</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>D5*D8</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>E5*E8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>F5*F8</f>
         <v/>
       </c>
@@ -6496,23 +6478,23 @@
           <t>Cargo revenue</t>
         </is>
       </c>
-      <c r="B10" s="36">
-        <f>Assumptions!$C$70*(1+Assumptions!B8)</f>
-        <v/>
-      </c>
-      <c r="C10" s="36">
+      <c r="B10" s="37">
+        <f>Assumptions!$C$73*(1+Assumptions!B8)</f>
+        <v/>
+      </c>
+      <c r="C10" s="37">
         <f>B10*(1+Assumptions!C8)</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>C10*(1+Assumptions!D8)</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>D10*(1+Assumptions!E8)</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>E10*(1+Assumptions!F8)</f>
         <v/>
       </c>
@@ -6523,23 +6505,23 @@
           <t>Service revenue</t>
         </is>
       </c>
-      <c r="B11" s="36">
-        <f>Assumptions!$C$71*(1+Assumptions!B9)</f>
-        <v/>
-      </c>
-      <c r="C11" s="36">
+      <c r="B11" s="37">
+        <f>Assumptions!$C$74*(1+Assumptions!B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="37">
         <f>B11*(1+Assumptions!C9)</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="37">
         <f>C11*(1+Assumptions!D9)</f>
         <v/>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="37">
         <f>D11*(1+Assumptions!E9)</f>
         <v/>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="37">
         <f>E11*(1+Assumptions!F9)</f>
         <v/>
       </c>
@@ -6550,23 +6532,23 @@
           <t>Hotel revenue</t>
         </is>
       </c>
-      <c r="B12" s="36">
-        <f>Assumptions!$C$72*(1+Assumptions!B10)</f>
-        <v/>
-      </c>
-      <c r="C12" s="36">
+      <c r="B12" s="37">
+        <f>Assumptions!$C$75*(1+Assumptions!B10)</f>
+        <v/>
+      </c>
+      <c r="C12" s="37">
         <f>B12*(1+Assumptions!C10)</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="37">
         <f>C12*(1+Assumptions!D10)</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="37">
         <f>D12*(1+Assumptions!E10)</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="37">
         <f>E12*(1+Assumptions!F10)</f>
         <v/>
       </c>
@@ -6577,50 +6559,50 @@
           <t>Aircraft-lease revenue (JV network)</t>
         </is>
       </c>
-      <c r="B13" s="36">
-        <f>Assumptions!$C$73*(1+Assumptions!B11)</f>
-        <v/>
-      </c>
-      <c r="C13" s="36">
+      <c r="B13" s="37">
+        <f>Assumptions!$C$76*(1+Assumptions!B11)</f>
+        <v/>
+      </c>
+      <c r="C13" s="37">
         <f>B13*(1+Assumptions!C11)</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="37">
         <f>C13*(1+Assumptions!D11)</f>
         <v/>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="37">
         <f>D13*(1+Assumptions!E11)</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="37">
         <f>E13*(1+Assumptions!F11)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>B7+B9+B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>C7+C9+C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>D7+D9+D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>E7+E9+E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>F7+F9+F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -6663,24 +6645,24 @@
           <t>Fuel cost per passenger (intensity x effective jet price)</t>
         </is>
       </c>
-      <c r="B17" s="36">
-        <f>Assumptions!$C$57*(Assumptions!B12*(1-Assumptions!$C$67)+Assumptions!B13*Assumptions!$C$67)*Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="C17" s="36">
-        <f>Assumptions!$C$57*(Assumptions!C12*(1-Assumptions!$C$67)+Assumptions!C13*Assumptions!$C$67)*Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="D17" s="36">
-        <f>Assumptions!$C$57*(Assumptions!D12*(1-Assumptions!$C$67)+Assumptions!D13*Assumptions!$C$67)*Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="E17" s="36">
-        <f>Assumptions!$C$57*(Assumptions!E12*(1-Assumptions!$C$67)+Assumptions!E13*Assumptions!$C$67)*Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="F17" s="36">
-        <f>Assumptions!$C$57*(Assumptions!F12*(1-Assumptions!$C$67)+Assumptions!F13*Assumptions!$C$67)*Assumptions!$C$64</f>
+      <c r="B17" s="37">
+        <f>Assumptions!$C$60*(Assumptions!B12*(1-Assumptions!$C$70)+Assumptions!B13*Assumptions!$C$70)*Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="C17" s="37">
+        <f>Assumptions!$C$60*(Assumptions!C12*(1-Assumptions!$C$70)+Assumptions!C13*Assumptions!$C$70)*Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="D17" s="37">
+        <f>Assumptions!$C$60*(Assumptions!D12*(1-Assumptions!$C$70)+Assumptions!D13*Assumptions!$C$70)*Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="E17" s="37">
+        <f>Assumptions!$C$60*(Assumptions!E12*(1-Assumptions!$C$70)+Assumptions!E13*Assumptions!$C$70)*Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="F17" s="37">
+        <f>Assumptions!$C$60*(Assumptions!F12*(1-Assumptions!$C$70)+Assumptions!F13*Assumptions!$C$70)*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -6690,23 +6672,23 @@
           <t>Staff</t>
         </is>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>Assumptions!B14</f>
         <v/>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="38">
         <f>Assumptions!C14</f>
         <v/>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="38">
         <f>Assumptions!D14</f>
         <v/>
       </c>
-      <c r="E18" s="37">
+      <c r="E18" s="38">
         <f>Assumptions!E14</f>
         <v/>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="38">
         <f>Assumptions!F14</f>
         <v/>
       </c>
@@ -6717,23 +6699,23 @@
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="38">
         <f>Assumptions!B15</f>
         <v/>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="38">
         <f>Assumptions!C15</f>
         <v/>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="38">
         <f>Assumptions!D15</f>
         <v/>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="38">
         <f>Assumptions!E15</f>
         <v/>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="38">
         <f>Assumptions!F15</f>
         <v/>
       </c>
@@ -6744,23 +6726,23 @@
           <t>Landing &amp; overflying</t>
         </is>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="38">
         <f>Assumptions!B16</f>
         <v/>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="38">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="38">
         <f>Assumptions!D16</f>
         <v/>
       </c>
-      <c r="E20" s="37">
+      <c r="E20" s="38">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="38">
         <f>Assumptions!F16</f>
         <v/>
       </c>
@@ -6771,23 +6753,23 @@
           <t>Handling</t>
         </is>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="38">
         <f>Assumptions!B17</f>
         <v/>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="38">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="38">
         <f>Assumptions!D17</f>
         <v/>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="38">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="38">
         <f>Assumptions!F17</f>
         <v/>
       </c>
@@ -6798,50 +6780,50 @@
           <t>Other direct</t>
         </is>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="38">
         <f>Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="38">
         <f>Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="38">
         <f>Assumptions!D18</f>
         <v/>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="38">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="38">
         <f>Assumptions!F18</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Cash cost per passenger</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>SUM(B17:B22)</f>
         <v/>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>SUM(C17:C22)</f>
         <v/>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>SUM(D17:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="35">
         <f>SUM(E17:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="35">
         <f>SUM(F17:F22)</f>
         <v/>
       </c>
@@ -6852,23 +6834,23 @@
           <t>Direct cash operating costs (AED mn)</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>B5*B23</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>C5*C23</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>D5*D23</f>
         <v/>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <f>E5*E23</f>
         <v/>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>F5*F23</f>
         <v/>
       </c>
@@ -6879,23 +6861,23 @@
           <t>Administrative costs (cash)</t>
         </is>
       </c>
-      <c r="B25" s="36">
-        <f>Assumptions!$C$69*(1+Assumptions!B19)</f>
-        <v/>
-      </c>
-      <c r="C25" s="36">
+      <c r="B25" s="37">
+        <f>Assumptions!$C$72*(1+Assumptions!B19)</f>
+        <v/>
+      </c>
+      <c r="C25" s="37">
         <f>B25*(1+Assumptions!C19)</f>
         <v/>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="37">
         <f>C25*(1+Assumptions!D19)</f>
         <v/>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="37">
         <f>D25*(1+Assumptions!E19)</f>
         <v/>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="37">
         <f>E25*(1+Assumptions!F19)</f>
         <v/>
       </c>
@@ -6906,50 +6888,50 @@
           <t>Selling &amp; marketing</t>
         </is>
       </c>
-      <c r="B26" s="36">
+      <c r="B26" s="37">
         <f>Assumptions!$C$34*B14</f>
         <v/>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="37">
         <f>Assumptions!$C$34*C14</f>
         <v/>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="37">
         <f>Assumptions!$C$34*D14</f>
         <v/>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="37">
         <f>Assumptions!$C$34*E14</f>
         <v/>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="37">
         <f>Assumptions!$C$34*F14</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="33">
         <f>B14-B24-B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <f>C14-C24-C25-C26</f>
         <v/>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <f>D14-D24-D25-D26</f>
         <v/>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <f>E14-E24-E25-E26</f>
         <v/>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <f>F14-F24-F25-F26</f>
         <v/>
       </c>
@@ -6960,50 +6942,50 @@
           <t>Other income (management fees from the JV network and misc.)</t>
         </is>
       </c>
-      <c r="B28" s="36">
-        <f>Assumptions!$C$74*(1+Assumptions!B20)</f>
-        <v/>
-      </c>
-      <c r="C28" s="36">
+      <c r="B28" s="37">
+        <f>Assumptions!$C$77*(1+Assumptions!B20)</f>
+        <v/>
+      </c>
+      <c r="C28" s="37">
         <f>B28*(1+Assumptions!C20)</f>
         <v/>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="37">
         <f>C28*(1+Assumptions!D20)</f>
         <v/>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="37">
         <f>D28*(1+Assumptions!E20)</f>
         <v/>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="37">
         <f>E28*(1+Assumptions!F20)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>EBITDA including fees and other income</t>
         </is>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="33">
         <f>B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="33">
         <f>C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="33">
         <f>D27+D28</f>
         <v/>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="33">
         <f>E27+E28</f>
         <v/>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="33">
         <f>F27+F28</f>
         <v/>
       </c>
@@ -7014,23 +6996,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="9">
         <f>B27/B14</f>
         <v/>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="9">
         <f>C27/C14</f>
         <v/>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="9">
         <f>D27/D14</f>
         <v/>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="9">
         <f>E27/E14</f>
         <v/>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="9">
         <f>F27/F14</f>
         <v/>
       </c>
@@ -7063,13 +7045,13 @@
           <t>Passengers (millions)</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="24" t="n">
         <v>10.11</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="24" t="n">
         <v>11.22</v>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="24" t="n">
         <v>13.06</v>
       </c>
     </row>
@@ -7079,13 +7061,13 @@
           <t>Seat load factor</t>
         </is>
       </c>
-      <c r="B35" s="25" t="n">
+      <c r="B35" s="26" t="n">
         <v>0.804</v>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="26" t="n">
         <v>0.82</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="26" t="n">
         <v>0.853</v>
       </c>
     </row>
@@ -7100,10 +7082,10 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="C36" s="24" t="n">
+      <c r="C36" s="25" t="n">
         <v>5552.393</v>
       </c>
-      <c r="D36" s="24" t="n">
+      <c r="D36" s="25" t="n">
         <v>6251.713</v>
       </c>
     </row>
@@ -7118,10 +7100,10 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="C37" s="24" t="n">
+      <c r="C37" s="25" t="n">
         <v>677.506</v>
       </c>
-      <c r="D37" s="24" t="n">
+      <c r="D37" s="25" t="n">
         <v>846</v>
       </c>
     </row>
@@ -7131,13 +7113,13 @@
           <t>Fuel cost (AED mn)</t>
         </is>
       </c>
-      <c r="B38" s="24" t="n">
+      <c r="B38" s="25" t="n">
         <v>1690.639</v>
       </c>
-      <c r="C38" s="24" t="n">
+      <c r="C38" s="25" t="n">
         <v>1924.547</v>
       </c>
-      <c r="D38" s="24" t="n">
+      <c r="D38" s="25" t="n">
         <v>2251.363</v>
       </c>
     </row>
@@ -7147,13 +7129,13 @@
           <t>Staff cost, direct (AED mn)</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n">
+      <c r="B39" s="25" t="n">
         <v>774.751</v>
       </c>
-      <c r="C39" s="24" t="n">
+      <c r="C39" s="25" t="n">
         <v>885.104</v>
       </c>
-      <c r="D39" s="24" t="n">
+      <c r="D39" s="25" t="n">
         <v>1069.366</v>
       </c>
     </row>
@@ -7163,13 +7145,13 @@
           <t>Maintenance (AED mn)</t>
         </is>
       </c>
-      <c r="B40" s="24" t="n">
+      <c r="B40" s="25" t="n">
         <v>438.924</v>
       </c>
-      <c r="C40" s="24" t="n">
+      <c r="C40" s="25" t="n">
         <v>685.639</v>
       </c>
-      <c r="D40" s="24" t="n">
+      <c r="D40" s="25" t="n">
         <v>800.577</v>
       </c>
     </row>
@@ -7179,13 +7161,13 @@
           <t>Landing &amp; overflying (AED mn)</t>
         </is>
       </c>
-      <c r="B41" s="24" t="n">
+      <c r="B41" s="25" t="n">
         <v>361.209</v>
       </c>
-      <c r="C41" s="24" t="n">
+      <c r="C41" s="25" t="n">
         <v>405.084</v>
       </c>
-      <c r="D41" s="24" t="n">
+      <c r="D41" s="25" t="n">
         <v>470.049</v>
       </c>
     </row>
@@ -7195,18 +7177,18 @@
           <t>Handling (AED mn)</t>
         </is>
       </c>
-      <c r="B42" s="24" t="n">
+      <c r="B42" s="25" t="n">
         <v>312.891</v>
       </c>
-      <c r="C42" s="24" t="n">
+      <c r="C42" s="25" t="n">
         <v>344.585</v>
       </c>
-      <c r="D42" s="24" t="n">
+      <c r="D42" s="25" t="n">
         <v>384.125</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>FY2023 revenue lines are on the pre-restatement basis (commissions netted); seat/ASK data is not disclosed by the company — passengers x rate is the finest disclosed level.</t>
         </is>
@@ -7267,7 +7249,7 @@
           <t>FY2027E EBITDA EXCLUDING fees/other income (AED mn) — peer basis</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>Segments!C27</f>
         <v/>
       </c>
@@ -7278,8 +7260,8 @@
           <t>Justified EV/EBITDA (peer median, primary filings)</t>
         </is>
       </c>
-      <c r="C6" s="38">
-        <f>Assumptions!$C$50</f>
+      <c r="C6" s="39">
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -7289,8 +7271,8 @@
           <t>Fee/other-income stream valued separately (after-tax annuity)</t>
         </is>
       </c>
-      <c r="C7" s="31">
-        <f>Segments!C28*(1-Assumptions!$C$36)/(DCF!C24-Assumptions!$C$48)</f>
+      <c r="C7" s="32">
+        <f>Segments!C28*(1-Assumptions!$C$36)/(DCF!C24-Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -7300,7 +7282,7 @@
           <t>Enterprise value at end-FY2027</t>
         </is>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>C5*C6+C7</f>
         <v/>
       </c>
@@ -7311,7 +7293,7 @@
           <t>Year-2 discount factor</t>
         </is>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="40">
         <f>DCF!C30</f>
         <v/>
       </c>
@@ -7322,19 +7304,19 @@
           <t>PV of FY2026-27 free cash flow</t>
         </is>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>DCF!B44+DCF!C44</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (split roll)</t>
         </is>
       </c>
-      <c r="C11" s="21">
-        <f>((C5*C6+C7)*C9+C10)*DCF!C61/Assumptions!$C$54+((Assumptions!$C$78-Assumptions!$C$77+Assumptions!$C$82+Assumptions!$C$81)*DCF!C63-Assumptions!$C$61)/Assumptions!$C$54-Assumptions!$C$55</f>
+      <c r="C11" s="23">
+        <f>((C5*C6+C7)*C9+C10)*DCF!C66/Assumptions!$C$57+((Assumptions!$C$81-Assumptions!$C$80+Assumptions!$C$85+Assumptions!$C$84)*DCF!C68-Assumptions!$C$64)/Assumptions!$C$57-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7344,8 +7326,8 @@
           <t>Bear (5.0x)</t>
         </is>
       </c>
-      <c r="C12" s="10">
-        <f>((C5*Assumptions!$C$89+C7)*C9+C10)*DCF!C61/Assumptions!$C$54+((Assumptions!$C$78-Assumptions!$C$77+Assumptions!$C$82+Assumptions!$C$81)*DCF!C63-Assumptions!$C$61)/Assumptions!$C$54-Assumptions!$C$55</f>
+      <c r="C12" s="15">
+        <f>((C5*Assumptions!$C$92+C7)*C9+C10)*DCF!C66/Assumptions!$C$57+((Assumptions!$C$81-Assumptions!$C$80+Assumptions!$C$85+Assumptions!$C$84)*DCF!C68-Assumptions!$C$64)/Assumptions!$C$57-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7355,13 +7337,13 @@
           <t>Bull (8.0x)</t>
         </is>
       </c>
-      <c r="C13" s="10">
-        <f>((C5*Assumptions!$C$90+C7)*C9+C10)*DCF!C61/Assumptions!$C$54+((Assumptions!$C$78-Assumptions!$C$77+Assumptions!$C$82+Assumptions!$C$81)*DCF!C63-Assumptions!$C$61)/Assumptions!$C$54-Assumptions!$C$55</f>
+      <c r="C13" s="15">
+        <f>((C5*Assumptions!$C$93+C7)*C9+C10)*DCF!C66/Assumptions!$C$57+((Assumptions!$C$81-Assumptions!$C$80+Assumptions!$C$85+Assumptions!$C$84)*DCF!C68-Assumptions!$C$64)/Assumptions!$C$57-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Trailing context (formulas at spot)</t>
         </is>
@@ -7373,8 +7355,8 @@
           <t>EV / FY2025 EBITDA at spot — EX fees (peer basis)</t>
         </is>
       </c>
-      <c r="C16" s="40">
-        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/'Income Statement'!D9</f>
+      <c r="C16" s="41">
+        <f>(DCF!C14+Assumptions!$C$80-Assumptions!$C$81)/'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
@@ -7384,8 +7366,8 @@
           <t>Price / FY2025 earnings at spot</t>
         </is>
       </c>
-      <c r="C17" s="40">
-        <f>Assumptions!$C$53/'Income Statement'!D21</f>
+      <c r="C17" s="41">
+        <f>Assumptions!$C$56/'Income Statement'!D21</f>
         <v/>
       </c>
     </row>
@@ -7395,8 +7377,8 @@
           <t>EV / FY2025 EBITDA at spot — INCLUDING fees (both bases published)</t>
         </is>
       </c>
-      <c r="C18" s="40">
-        <f>(DCF!C14+Assumptions!$C$77-Assumptions!$C$78)/('Income Statement'!D9+'Income Statement'!D12)</f>
+      <c r="C18" s="41">
+        <f>(DCF!C14+Assumptions!$C$80-Assumptions!$C$81)/('Income Statement'!D9+'Income Statement'!D12)</f>
         <v/>
       </c>
     </row>
@@ -7419,7 +7401,7 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="16">
         <f>Segments!D30</f>
         <v/>
       </c>
@@ -7430,7 +7412,7 @@
           <t>FY2026E revenue (current scale)</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="18">
         <f>Segments!B14</f>
         <v/>
       </c>
@@ -7441,7 +7423,7 @@
           <t>Normalised EBITDA incl. fees and other income</t>
         </is>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="32">
         <f>C21*C22+Segments!B28</f>
         <v/>
       </c>
@@ -7452,7 +7434,7 @@
           <t>less depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="18">
         <f>Assumptions!B21</f>
         <v/>
       </c>
@@ -7463,7 +7445,7 @@
           <t>Normalised EBIT</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>C23-C24</f>
         <v/>
       </c>
@@ -7474,7 +7456,7 @@
           <t>Net finance income (FY2026E)</t>
         </is>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="38">
         <f>'Cash Flow'!B13-'Cash Flow'!B14</f>
         <v/>
       </c>
@@ -7492,19 +7474,19 @@
           <t>Normalised earnings per share (ex-JV)</t>
         </is>
       </c>
-      <c r="C28" s="41">
-        <f>(C25+C26)*(1-Assumptions!$C$36)*(1-Assumptions!$C$83)/Assumptions!$C$54</f>
+      <c r="C28" s="42">
+        <f>(C25+C26)*(1-Assumptions!$C$36)*(1-Assumptions!$C$86)/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Normalised value per share at the anchor</t>
-        </is>
-      </c>
-      <c r="C29" s="21">
-        <f>Assumptions!$C$51*C28*DCF!C61+Assumptions!$C$81/Assumptions!$C$54*DCF!C63-Assumptions!$C$55</f>
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Normalised value per share at the anchor — COMPUTED AND EXCLUDED. An airline's reported earnings in any one year are an accident of the fuel curve, the delivery schedule and the load factor, so a normalised figure normalises a cycle rather than a level. It is shown because it was calculated, and it does not enter the valuation.</t>
+        </is>
+      </c>
+      <c r="C29" s="23">
+        <f>Assumptions!$C$54*C28*DCF!C66+Assumptions!$C$84/Assumptions!$C$57*DCF!C68-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7514,8 +7496,8 @@
           <t>Bear (10x)</t>
         </is>
       </c>
-      <c r="C31" s="10">
-        <f>Assumptions!$C$91*C28*DCF!C61+Assumptions!$C$81/Assumptions!$C$54*DCF!C63-Assumptions!$C$55</f>
+      <c r="C31" s="15">
+        <f>Assumptions!$C$94*C28*DCF!C66+Assumptions!$C$84/Assumptions!$C$57*DCF!C68-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7525,8 +7507,8 @@
           <t>Bull (16x)</t>
         </is>
       </c>
-      <c r="C32" s="10">
-        <f>Assumptions!$C$92*C28*DCF!C61+Assumptions!$C$81/Assumptions!$C$54*DCF!C63-Assumptions!$C$55</f>
+      <c r="C32" s="15">
+        <f>Assumptions!$C$95*C28*DCF!C66+Assumptions!$C$84/Assumptions!$C$57*DCF!C68-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7549,19 +7531,19 @@
           <t>Book value per share (FY2025, audited)</t>
         </is>
       </c>
-      <c r="C36" s="10">
-        <f>Assumptions!$C$84/Assumptions!$C$54</f>
+      <c r="C36" s="15">
+        <f>Assumptions!$C$87/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Justified price-to-book value per share at the anchor</t>
         </is>
       </c>
-      <c r="C37" s="21">
-        <f>((Assumptions!$C$52-Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48))*C36*DCF!C61-Assumptions!$C$55</f>
+      <c r="C37" s="23">
+        <f>((Assumptions!$C$55-Assumptions!$C$50)/(DCF!C21-Assumptions!$C$50))*C36*DCF!C66-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7571,8 +7553,8 @@
           <t>Justified P/B multiple</t>
         </is>
       </c>
-      <c r="C38" s="40">
-        <f>(Assumptions!$C$52-Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48)</f>
+      <c r="C38" s="41">
+        <f>(Assumptions!$C$55-Assumptions!$C$50)/(DCF!C21-Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -7582,8 +7564,8 @@
           <t>Bear construction</t>
         </is>
       </c>
-      <c r="C39" s="10">
-        <f>((Assumptions!$C$52-0.02-0.015)/(0.5*(DCF!C10+DCF!C21)-0.015))*C36*DCF!C61-Assumptions!$C$55</f>
+      <c r="C39" s="15">
+        <f>((Assumptions!$C$55-0.02-0.015)/(0.5*(DCF!C10+DCF!C21)-0.015))*C36*DCF!C66-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7593,13 +7575,13 @@
           <t>Bull construction</t>
         </is>
       </c>
-      <c r="C40" s="10">
-        <f>((Assumptions!$C$52+0.02-Assumptions!$C$48)/(DCF!C21-Assumptions!$C$48))*C36*DCF!C61-Assumptions!$C$55</f>
+      <c r="C40" s="15">
+        <f>((Assumptions!$C$55+0.02-Assumptions!$C$50)/(DCF!C21-Assumptions!$C$50))*C36*DCF!C66-Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>The bear leg holds the same Gordon identity as base and bull: (ROE_bear - g_bear)/(k_bear - g_bear).</t>
         </is>
@@ -7616,7 +7598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7651,7 +7633,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Cost of capital — explicit window</t>
         </is>
@@ -7663,7 +7645,7 @@
           <t>AED government bond yield</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>Assumptions!$C$37</f>
         <v/>
       </c>
@@ -7674,7 +7656,7 @@
           <t>less the observed auction spread over US Treasuries</t>
         </is>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>Assumptions!$C$38</f>
         <v/>
       </c>
@@ -7685,7 +7667,7 @@
           <t>Net risk-free rate</t>
         </is>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="44">
         <f>C5-C6</f>
         <v/>
       </c>
@@ -7696,8 +7678,8 @@
           <t>Beta (switchable: adopted index / alternative benchmark)</t>
         </is>
       </c>
-      <c r="C8" s="35">
-        <f>Assumptions!$C$40*(1-Assumptions!$C$68)+Assumptions!$C$41*Assumptions!$C$68</f>
+      <c r="C8" s="36">
+        <f>Assumptions!$C$40*(1-Assumptions!$C$71)+Assumptions!$C$41*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -7707,18 +7689,18 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Cost of equity</t>
         </is>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="45">
         <f>C7+C8*C9</f>
         <v/>
       </c>
@@ -7729,7 +7711,7 @@
           <t>Marginal cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>Assumptions!$C$45</f>
         <v/>
       </c>
@@ -7740,7 +7722,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="16">
         <f>Assumptions!$C$36</f>
         <v/>
       </c>
@@ -7751,7 +7733,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="44">
         <f>C11*(1-C12)</f>
         <v/>
       </c>
@@ -7762,8 +7744,8 @@
           <t>Market capitalisation (AED mn)</t>
         </is>
       </c>
-      <c r="C14" s="31">
-        <f>Assumptions!$C$53*Assumptions!$C$54</f>
+      <c r="C14" s="32">
+        <f>Assumptions!$C$56*Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -7773,8 +7755,8 @@
           <t>Gross debt (audited)</t>
         </is>
       </c>
-      <c r="C15" s="37">
-        <f>Assumptions!$C$77</f>
+      <c r="C15" s="38">
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -7784,24 +7766,24 @@
           <t>Debt weight (gross)</t>
         </is>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="44">
         <f>C15/(C15+C14)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Cost of capital — explicit window</t>
         </is>
       </c>
-      <c r="C17" s="43">
-        <f>(1-C16)*C10+C16*C13+Assumptions!$C$66</f>
+      <c r="C17" s="45">
+        <f>(1-C16)*C10+C16*C13+Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Cost of capital — terminal</t>
         </is>
@@ -7813,7 +7795,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
@@ -7824,7 +7806,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="44">
         <f>C20+C8*Assumptions!$C$44</f>
         <v/>
       </c>
@@ -7835,7 +7817,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C22" s="42">
+      <c r="C22" s="44">
         <f>Assumptions!$C$46*(1-C12)</f>
         <v/>
       </c>
@@ -7846,19 +7828,19 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="16">
         <f>Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Cost of capital — terminal</t>
         </is>
       </c>
-      <c r="C24" s="43">
-        <f>(1-C23)*C21+C23*C22+Assumptions!$C$66</f>
+      <c r="C24" s="45">
+        <f>(1-C23)*C21+C23*C22+Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -7900,23 +7882,23 @@
           <t>Cost-of-debt path</t>
         </is>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <f>Assumptions!B28</f>
         <v/>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <f>Assumptions!C28</f>
         <v/>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="19">
         <f>Assumptions!D28</f>
         <v/>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <f>Assumptions!E28</f>
         <v/>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="19">
         <f>Assumptions!F28</f>
         <v/>
       </c>
@@ -7927,23 +7909,23 @@
           <t>Glide fraction (path progress)</t>
         </is>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="46">
         <f>(Assumptions!$B28-B27)/(Assumptions!B28-Assumptions!F28)</f>
         <v/>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="46">
         <f>(Assumptions!$B28-C27)/(Assumptions!B28-Assumptions!F28)</f>
         <v/>
       </c>
-      <c r="D28" s="44">
+      <c r="D28" s="46">
         <f>(Assumptions!$B28-D27)/(Assumptions!B28-Assumptions!F28)</f>
         <v/>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="46">
         <f>(Assumptions!$B28-E27)/(Assumptions!B28-Assumptions!F28)</f>
         <v/>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="46">
         <f>(Assumptions!$B28-F27)/(Assumptions!B28-Assumptions!F28)</f>
         <v/>
       </c>
@@ -7954,23 +7936,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="44">
         <f>$C$17-($C$17-$C$24)*B28</f>
         <v/>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="44">
         <f>$C$17-($C$17-$C$24)*C28</f>
         <v/>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="44">
         <f>$C$17-($C$17-$C$24)*D28</f>
         <v/>
       </c>
-      <c r="E29" s="42">
+      <c r="E29" s="44">
         <f>$C$17-($C$17-$C$24)*E28</f>
         <v/>
       </c>
-      <c r="F29" s="42">
+      <c r="F29" s="44">
         <f>$C$17-($C$17-$C$24)*F28</f>
         <v/>
       </c>
@@ -7981,23 +7963,23 @@
           <t>Cumulative discount factor</t>
         </is>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="46">
         <f>1/(1+B29)</f>
         <v/>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="46">
         <f>B30/(1+C29)</f>
         <v/>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="46">
         <f>C30/(1+D29)</f>
         <v/>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="46">
         <f>D30/(1+E29)</f>
         <v/>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="46">
         <f>E30/(1+F29)</f>
         <v/>
       </c>
@@ -8035,55 +8017,55 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="18">
         <f>Segments!B14</f>
         <v/>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="18">
         <f>Segments!C14</f>
         <v/>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="18">
         <f>Segments!D14</f>
         <v/>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="18">
         <f>Segments!E14</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="18">
         <f>Segments!F14</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>EBITDA incl. fees and other income</t>
         </is>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="18">
         <f>Segments!B29</f>
         <v/>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="18">
         <f>Segments!C29</f>
         <v/>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="18">
         <f>Segments!D29</f>
         <v/>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="18">
         <f>Segments!E29</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="18">
         <f>Segments!F29</f>
         <v/>
       </c>
@@ -8094,23 +8076,23 @@
           <t>less depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="18">
         <f>Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="18">
         <f>Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="18">
         <f>Assumptions!D21</f>
         <v/>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="18">
         <f>Assumptions!E21</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="18">
         <f>Assumptions!F21</f>
         <v/>
       </c>
@@ -8121,23 +8103,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="32">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="32">
         <f>C34-C35</f>
         <v/>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="32">
         <f>D34-D35</f>
         <v/>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="32">
         <f>E34-E35</f>
         <v/>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="32">
         <f>F34-F35</f>
         <v/>
       </c>
@@ -8148,23 +8130,23 @@
           <t>NOPAT (EBIT x (1 - tax))</t>
         </is>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="32">
         <f>B36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="32">
         <f>C36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="D37" s="31">
+      <c r="D37" s="32">
         <f>D36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="32">
         <f>E36*(1-$C$12)</f>
         <v/>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="32">
         <f>F36*(1-$C$12)</f>
         <v/>
       </c>
@@ -8175,23 +8157,23 @@
           <t>add back depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B38" s="31">
+      <c r="B38" s="32">
         <f>B35</f>
         <v/>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <f>C35</f>
         <v/>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <f>D35</f>
         <v/>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <f>E35</f>
         <v/>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <f>F35</f>
         <v/>
       </c>
@@ -8202,24 +8184,24 @@
           <t>less owned capex + pre-delivery payments</t>
         </is>
       </c>
-      <c r="B39" s="31">
-        <f>Assumptions!B22*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="C39" s="31">
-        <f>Assumptions!C22*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="D39" s="31">
-        <f>Assumptions!D22*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="E39" s="31">
-        <f>Assumptions!E22*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="F39" s="31">
-        <f>Assumptions!F22*Assumptions!$C$65</f>
+      <c r="B39" s="32">
+        <f>Assumptions!B22*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="C39" s="32">
+        <f>Assumptions!C22*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="D39" s="32">
+        <f>Assumptions!D22*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="E39" s="32">
+        <f>Assumptions!E22*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="F39" s="32">
+        <f>Assumptions!F22*Assumptions!$C$68</f>
         <v/>
       </c>
     </row>
@@ -8229,23 +8211,23 @@
           <t>Working capital balance</t>
         </is>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="32">
         <f>Assumptions!$C$35*B33</f>
         <v/>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="32">
         <f>Assumptions!$C$35*C33</f>
         <v/>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="32">
         <f>Assumptions!$C$35*D33</f>
         <v/>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="32">
         <f>Assumptions!$C$35*E33</f>
         <v/>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="32">
         <f>Assumptions!$C$35*F33</f>
         <v/>
       </c>
@@ -8256,50 +8238,50 @@
           <t>less change in working capital</t>
         </is>
       </c>
-      <c r="B41" s="31">
-        <f>B40-Assumptions!$C$76</f>
-        <v/>
-      </c>
-      <c r="C41" s="31">
+      <c r="B41" s="32">
+        <f>B40-Assumptions!$C$79</f>
+        <v/>
+      </c>
+      <c r="C41" s="32">
         <f>C40-B40</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <f>D40-C40</f>
         <v/>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <f>E40-D40</f>
         <v/>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <f>F40-E40</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="33">
         <f>B37+B38-B39-B41-B45</f>
         <v/>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <f>C37+C38-C39-C41-C45</f>
         <v/>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <f>D37+D38-D39-D41-D45</f>
         <v/>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <f>E37+E38-E39-E41-E45</f>
         <v/>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <f>F37+F38-F39-F41-F45</f>
         <v/>
       </c>
@@ -8310,50 +8292,50 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B43" s="44">
+      <c r="B43" s="46">
         <f>B30</f>
         <v/>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="46">
         <f>C30</f>
         <v/>
       </c>
-      <c r="D43" s="44">
+      <c r="D43" s="46">
         <f>D30</f>
         <v/>
       </c>
-      <c r="E43" s="44">
+      <c r="E43" s="46">
         <f>E30</f>
         <v/>
       </c>
-      <c r="F43" s="44">
+      <c r="F43" s="46">
         <f>F30</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="33">
         <f>B42*B43</f>
         <v/>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <f>C42*C43</f>
         <v/>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <f>D42*D43</f>
         <v/>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <f>E42*E43</f>
         <v/>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <f>F42*F43</f>
         <v/>
       </c>
@@ -8364,24 +8346,24 @@
           <t>less leased-fleet additions (gross right-of-use value)</t>
         </is>
       </c>
-      <c r="B45" s="31">
-        <f>Assumptions!B24*Assumptions!$C$58*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="C45" s="31">
-        <f>Assumptions!C24*Assumptions!$C$58*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="D45" s="31">
-        <f>Assumptions!D24*Assumptions!$C$58*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="E45" s="31">
-        <f>Assumptions!E24*Assumptions!$C$58*Assumptions!$C$65</f>
-        <v/>
-      </c>
-      <c r="F45" s="31">
-        <f>Assumptions!F24*Assumptions!$C$58*Assumptions!$C$65</f>
+      <c r="B45" s="32">
+        <f>Assumptions!B24*Assumptions!$C$61*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="C45" s="32">
+        <f>Assumptions!C24*Assumptions!$C$61*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="D45" s="32">
+        <f>Assumptions!D24*Assumptions!$C$61*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="E45" s="32">
+        <f>Assumptions!E24*Assumptions!$C$61*Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="F45" s="32">
+        <f>Assumptions!F24*Assumptions!$C$61*Assumptions!$C$68</f>
         <v/>
       </c>
     </row>
@@ -8391,23 +8373,23 @@
           <t>Fleet assets roll-forward</t>
         </is>
       </c>
-      <c r="B46" s="31">
-        <f>Assumptions!$C$79+B39+B45-B35</f>
-        <v/>
-      </c>
-      <c r="C46" s="31">
+      <c r="B46" s="32">
+        <f>Assumptions!$C$82+B39+B45-B35</f>
+        <v/>
+      </c>
+      <c r="C46" s="32">
         <f>B46+C39+C45-C35</f>
         <v/>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="32">
         <f>C46+D39+D45-D35</f>
         <v/>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="32">
         <f>D46+E39+E45-E35</f>
         <v/>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="32">
         <f>E46+F39+F45-F35</f>
         <v/>
       </c>
@@ -8418,29 +8400,29 @@
           <t>Invested capital (fleet + intangibles + working capital)</t>
         </is>
       </c>
-      <c r="B47" s="31">
-        <f>B46+Assumptions!$C$80+B40</f>
-        <v/>
-      </c>
-      <c r="C47" s="31">
-        <f>C46+Assumptions!$C$80+C40</f>
-        <v/>
-      </c>
-      <c r="D47" s="31">
-        <f>D46+Assumptions!$C$80+D40</f>
-        <v/>
-      </c>
-      <c r="E47" s="31">
-        <f>E46+Assumptions!$C$80+E40</f>
-        <v/>
-      </c>
-      <c r="F47" s="31">
-        <f>F46+Assumptions!$C$80+F40</f>
+      <c r="B47" s="32">
+        <f>B46+Assumptions!$C$83+B40</f>
+        <v/>
+      </c>
+      <c r="C47" s="32">
+        <f>C46+Assumptions!$C$83+C40</f>
+        <v/>
+      </c>
+      <c r="D47" s="32">
+        <f>D46+Assumptions!$C$83+D40</f>
+        <v/>
+      </c>
+      <c r="E47" s="32">
+        <f>E46+Assumptions!$C$83+E40</f>
+        <v/>
+      </c>
+      <c r="F47" s="32">
+        <f>F46+Assumptions!$C$83+F40</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>Terminal block</t>
         </is>
@@ -8452,150 +8434,205 @@
           <t>Terminal NOPAT (FY2031E)</t>
         </is>
       </c>
-      <c r="C50" s="36">
-        <f>F37*(1+Assumptions!$C$48)</f>
+      <c r="C50" s="37">
+        <f>F37*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C51" s="42">
-        <f>C50/F47</f>
+          <t>Plus book depreciation (NOPAT is already net of it)</t>
+        </is>
+      </c>
+      <c r="C51" s="37">
+        <f>F35*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Reinvestment rate = growth / return on capital</t>
-        </is>
-      </c>
-      <c r="C52" s="42">
-        <f>Assumptions!$C$48/C51</f>
+          <t>Less maintenance at current cost (book depreciation escalated over half the disclosed life)</t>
+        </is>
+      </c>
+      <c r="C52" s="37">
+        <f>-C51*(1+Assumptions!$C$49)^(Assumptions!$C$51/2)</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Terminal value</t>
-        </is>
-      </c>
-      <c r="C53" s="31">
-        <f>C50*(1-C52)/(C24-Assumptions!$C$48)</f>
+          <t>Less capital behind real growth</t>
+        </is>
+      </c>
+      <c r="C53" s="37">
+        <f>-Assumptions!$C$48*12172.687814</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>Less inflation on working capital — NEGATIVE here, because an airline is paid before it flies and its working capital is a source of cash</t>
+        </is>
+      </c>
+      <c r="C54" s="37">
+        <f>-Assumptions!$C$49*-7184.461799</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Terminal free cash flow to the firm</t>
+        </is>
+      </c>
+      <c r="C55" s="35">
+        <f>SUM(C50:C54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value — the free cash flow above, grown one year and capitalised</t>
+        </is>
+      </c>
+      <c r="C56" s="32">
+        <f>C55*(1+Assumptions!$C$50)/(C24-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C54" s="31">
-        <f>C53*F30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="C57" s="32">
+        <f>C56*F30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>PV of explicit years</t>
         </is>
       </c>
-      <c r="C55" s="31">
+      <c r="C58" s="32">
         <f>SUM(B44:F44)</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>Enterprise value of the airline</t>
         </is>
       </c>
-      <c r="C56" s="32">
-        <f>C54+C55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="C59" s="33">
+        <f>C57+C58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Terminal value share of enterprise value</t>
         </is>
       </c>
-      <c r="C57" s="45">
-        <f>C54/C56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Equity attributable (from the SOTP Bridge)</t>
-        </is>
-      </c>
-      <c r="C59" s="17">
-        <f>'SOTP Bridge'!C13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Per share at 31-Dec-2025</t>
-        </is>
-      </c>
-      <c r="C60" s="10">
-        <f>C59/Assumptions!$C$54</f>
+      <c r="C60" s="47">
+        <f>C57/C59</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Anchor accretion factor (at the cost of equity)</t>
-        </is>
-      </c>
-      <c r="C61" s="44">
-        <f>(1+C10)^(Assumptions!$C$56/365)</f>
+          <t>Memo: the no-growth perpetuity floor at book depreciation</t>
+        </is>
+      </c>
+      <c r="C61" s="32">
+        <f>C50/C24</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
+          <t>Memo: the retired reinvestment-identity terminal, printed so the change this edition made is visible rather than described</t>
+        </is>
+      </c>
+      <c r="C62" s="32">
+        <f>23300.718843</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Equity attributable (from the SOTP Bridge)</t>
+        </is>
+      </c>
+      <c r="C64" s="18">
+        <f>'SOTP Bridge'!C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Per share at 31-Dec-2025</t>
+        </is>
+      </c>
+      <c r="C65" s="15">
+        <f>C64/Assumptions!$C$57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Anchor accretion factor (at the cost of equity)</t>
+        </is>
+      </c>
+      <c r="C66" s="46">
+        <f>(1+C10)^(Assumptions!$C$59/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
           <t>Per share, whole equity rolled at Ke (single-rate view)</t>
         </is>
       </c>
-      <c r="C62" s="10">
-        <f>C60*C61-Assumptions!$C$55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="C67" s="15">
+        <f>C65*C66-Assumptions!$C$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Cash-leg accretion factor (deposit yield)</t>
         </is>
       </c>
-      <c r="C63" s="44">
-        <f>(1+Assumptions!B29)^(Assumptions!$C$56/365)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="C68" s="46">
+        <f>(1+Assumptions!B29)^(Assumptions!$C$59/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>Fair value per share at the anchor (split roll — the published figure)</t>
         </is>
       </c>
-      <c r="C64" s="19">
+      <c r="C69" s="20">
         <f>'SOTP Bridge'!C15</f>
         <v/>
       </c>
@@ -8698,32 +8735,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="27" t="n">
         <v>5999.75</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>6765.852</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="27" t="n">
         <v>7787.581</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>Segments!B14</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>Segments!C14</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>Segments!D14</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>Segments!E14</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>Segments!F14</f>
         <v/>
       </c>
@@ -8734,32 +8771,32 @@
           <t>Direct operating costs (cash)</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="27" t="n">
         <v>3725.597</v>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>4587.789000000001</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>5506.414999999999</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>Segments!B24</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>Segments!C24</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="18">
         <f>Segments!D24</f>
         <v/>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="18">
         <f>Segments!E24</f>
         <v/>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="18">
         <f>Segments!F24</f>
         <v/>
       </c>
@@ -8770,32 +8807,32 @@
           <t>Administrative expenses (cash)</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <v>299.466</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <v>241.532</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="25" t="n">
         <v>276.1830000000001</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="38">
         <f>Segments!B25</f>
         <v/>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="38">
         <f>Segments!C25</f>
         <v/>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="38">
         <f>Segments!D25</f>
         <v/>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="38">
         <f>Segments!E25</f>
         <v/>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="38">
         <f>Segments!F25</f>
         <v/>
       </c>
@@ -8806,71 +8843,71 @@
           <t>Selling &amp; marketing</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="25" t="n">
         <v>88.79300000000001</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <v>103.843</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="25" t="n">
         <v>113.605</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="38">
         <f>Segments!B26</f>
         <v/>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="38">
         <f>Segments!C26</f>
         <v/>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="38">
         <f>Segments!D26</f>
         <v/>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="38">
         <f>Segments!E26</f>
         <v/>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="38">
         <f>Segments!F26</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>B5-B6-B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>C5-C6-C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>D5-D6-D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>E5-E6-E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>F5-F6-F7-F8</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>G5-G6-G7-G8</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>H5-H6-H7-H8</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="33">
         <f>I5-I6-I7-I8</f>
         <v/>
       </c>
@@ -8881,71 +8918,71 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="27" t="n">
         <v>647.327</v>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="27" t="n">
         <v>648.588</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="27" t="n">
         <v>621.798</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="18">
         <f>Assumptions!B21</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>Assumptions!C21</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="18">
         <f>Assumptions!D21</f>
         <v/>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="18">
         <f>Assumptions!E21</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="18">
         <f>Assumptions!F21</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>B9-B10</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C9-C10</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D9-D10</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E9-E10</f>
         <v/>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F9-F10</f>
         <v/>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="33">
         <f>G9-G10</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="33">
         <f>H9-H10</f>
         <v/>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="33">
         <f>I9-I10</f>
         <v/>
       </c>
@@ -8956,32 +8993,32 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>113.471</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <v>131.68</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <v>197.132</v>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="38">
         <f>Segments!B28</f>
         <v/>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="38">
         <f>Segments!C28</f>
         <v/>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="38">
         <f>Segments!D28</f>
         <v/>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="38">
         <f>Segments!E28</f>
         <v/>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="38">
         <f>Segments!F28</f>
         <v/>
       </c>
@@ -8992,32 +9029,32 @@
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>209.994</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>250.698</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>240.774</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="38">
         <f>'Cash Flow'!B13</f>
         <v/>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="38">
         <f>'Cash Flow'!C13</f>
         <v/>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="38">
         <f>'Cash Flow'!D13</f>
         <v/>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="38">
         <f>'Cash Flow'!E13</f>
         <v/>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="38">
         <f>'Cash Flow'!F13</f>
         <v/>
       </c>
@@ -9028,32 +9065,32 @@
           <t>Finance costs</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="25" t="n">
         <v>102.457</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>82.092</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <v>66.672</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>'Cash Flow'!B14</f>
         <v/>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>'Cash Flow'!C14</f>
         <v/>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>'Cash Flow'!D14</f>
         <v/>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>'Cash Flow'!E14</f>
         <v/>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>'Cash Flow'!F14</f>
         <v/>
       </c>
@@ -9064,71 +9101,71 @@
           <t>Share of JV and associate profit</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="25" t="n">
         <v>88.121</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="25" t="n">
         <v>124.752</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="25" t="n">
         <v>189.975</v>
       </c>
-      <c r="E15" s="36">
-        <f>Assumptions!$C$75*(1+Assumptions!B30)</f>
-        <v/>
-      </c>
-      <c r="F15" s="36">
+      <c r="E15" s="37">
+        <f>Assumptions!$C$78*(1+Assumptions!B30)</f>
+        <v/>
+      </c>
+      <c r="F15" s="37">
         <f>E15*(1+Assumptions!C30)</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <f>F15*(1+Assumptions!D30)</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>G15*(1+Assumptions!E30)</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <f>H15*(1+Assumptions!F30)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Profit before tax (before the JV share, forecast)</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="33">
         <f>B11+B12+B13-B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>C11+C12+C13-C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="33">
         <f>D11+D12+D13-D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="33">
         <f>E11+E12+E13-E14</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="33">
         <f>F11+F12+F13-F14</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="33">
         <f>G11+G12+G13-G14</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="33">
         <f>H11+H12+H13-H14</f>
         <v/>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="33">
         <f>I11+I12+I13-I14</f>
         <v/>
       </c>
@@ -9139,71 +9176,71 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="25" t="n">
         <v>141.508</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="25" t="n">
         <v>202.054</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="37">
         <f>E16*Assumptions!$C$36</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="37">
         <f>F16*Assumptions!$C$36</f>
         <v/>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="37">
         <f>G16*Assumptions!$C$36</f>
         <v/>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="37">
         <f>H16*Assumptions!$C$36</f>
         <v/>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="37">
         <f>I16*Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="33">
         <f>B16-B17</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <f>C16-C17</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <f>D16-D17</f>
         <v/>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <f>E16-E17+E15</f>
         <v/>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>F16-F17+F15</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>G16-G17+G15</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="33">
         <f>H16-H17+H15</f>
         <v/>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="33">
         <f>I16-I17+I15</f>
         <v/>
       </c>
@@ -9214,36 +9251,36 @@
           <t>Minorities</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="36">
         <f>B18-B20</f>
         <v/>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="36">
         <f>C18-C20</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <f>D18-D20</f>
         <v/>
       </c>
-      <c r="E19" s="35">
-        <f>E18*Assumptions!$C$83</f>
-        <v/>
-      </c>
-      <c r="F19" s="35">
-        <f>F18*Assumptions!$C$83</f>
-        <v/>
-      </c>
-      <c r="G19" s="35">
-        <f>G18*Assumptions!$C$83</f>
-        <v/>
-      </c>
-      <c r="H19" s="35">
-        <f>H18*Assumptions!$C$83</f>
-        <v/>
-      </c>
-      <c r="I19" s="35">
-        <f>I18*Assumptions!$C$83</f>
+      <c r="E19" s="36">
+        <f>E18*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="F19" s="36">
+        <f>F18*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="G19" s="36">
+        <f>G18*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="H19" s="36">
+        <f>H18*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="I19" s="36">
+        <f>I18*Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -9253,32 +9290,32 @@
           <t>Attributable to owners</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>1547.132</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>1466.986</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="27" t="n">
         <v>1628.475</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="33">
         <f>E18-E19</f>
         <v/>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="33">
         <f>F18-F19</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>G18-G19</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="33">
         <f>H18-H19</f>
         <v/>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="33">
         <f>I18-I19</f>
         <v/>
       </c>
@@ -9289,36 +9326,36 @@
           <t>Earnings per share (AED)</t>
         </is>
       </c>
-      <c r="B21" s="10">
-        <f>B20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="C21" s="10">
-        <f>C20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="D21" s="10">
-        <f>D20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="E21" s="10">
-        <f>E20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>F20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="G21" s="10">
-        <f>G20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="H21" s="10">
-        <f>H20/Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="I21" s="10">
-        <f>I20/Assumptions!$C$54</f>
+      <c r="B21" s="15">
+        <f>B20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>C20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>D20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>E20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>F20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="G21" s="15">
+        <f>G20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="H21" s="15">
+        <f>H20/Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>I20/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -9328,41 +9365,41 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <f>B9/B5</f>
         <v/>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <f>C9/C5</f>
         <v/>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="9">
         <f>D9/D5</f>
         <v/>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="9">
         <f>E9/E5</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="9">
         <f>F9/F5</f>
         <v/>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="9">
         <f>G9/G5</f>
         <v/>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="9">
         <f>H9/H5</f>
         <v/>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <f>I9/I5</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>The forecast income statement carries EBIT excluding fees/other income on row 11; the DCF taxes EBIT including that recurring line (row 12), exactly as the study text describes.</t>
         </is>

--- a/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
+++ b/engine/airarabia_study/AIRARABIA_Valuation_Model_09082026_public.xlsx
@@ -2765,19 +2765,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6.613931971702153</v>
+        <v>6.530864632088698</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7.22938797416904</v>
+        <v>7.102168803376595</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>8.047303999567715</v>
+        <v>7.860833702331569</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>9.189336112633173</v>
+        <v>8.919442388482089</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>10.88022997212353</v>
+        <v>10.48530965071819</v>
       </c>
     </row>
     <row r="7">
@@ -2787,19 +2787,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5.290650036151688</v>
+        <v>5.22620977758266</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5.628038240398886</v>
+        <v>5.532093014962125</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6.047709804384486</v>
+        <v>5.912111496029038</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6.584966343990367</v>
+        <v>6.398071091427047</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7.298672947301888</v>
+        <v>7.043007769349051</v>
       </c>
     </row>
     <row r="8">
@@ -2809,19 +2809,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4.411265519707568</v>
+        <v>4.359176372904554</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4.611970399626963</v>
+        <v>4.535826864943507</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4.851184061604538</v>
+        <v>4.745966396016637</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5.14175332927026</v>
+        <v>5.000767165165692</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5.502954385226047</v>
+        <v>5.316992642879297</v>
       </c>
     </row>
     <row r="9">
@@ -2831,19 +2831,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.785338160707695</v>
+        <v>3.742017746254053</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.910801948149978</v>
+        <v>3.848289311017446</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>4.055845559017758</v>
+        <v>3.970774028444986</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>4.225812539903896</v>
+        <v>4.113896644092114</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4.428185438899458</v>
+        <v>4.283853112430982</v>
       </c>
     </row>
     <row r="10">
@@ -2853,19 +2853,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>3.317696432266285</v>
+        <v>3.280908427380842</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>3.398430090879895</v>
+        <v>3.345850013323994</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>3.489585452220582</v>
+        <v>3.418818015716527</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.593568894394453</v>
+        <v>3.501665739466495</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3.713589416492556</v>
+        <v>3.596864638976781</v>
       </c>
     </row>
     <row r="12">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>8.190595518800578</v>
+        <v>8.000623234748355</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6.152900095652542</v>
+        <v>6.014763569019446</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4.933557898331902</v>
+        <v>4.826377818105075</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.12305166807534</v>
+        <v>4.036399438767721</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3.545995708484645</v>
+        <v>3.473918397822978</v>
       </c>
     </row>
     <row r="15">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>8.118262350506111</v>
+        <v>7.930067114029304</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>6.099847501414335</v>
+        <v>5.962997828691612</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4.89203512682659</v>
+        <v>4.785849443207093</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>4.089186917413269</v>
+        <v>4.003335375343121</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>3.517578411938233</v>
+        <v>3.446164434809923</v>
       </c>
     </row>
     <row r="16">
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>8.046922852356397</v>
+        <v>7.860480281412786</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6.047521370368907</v>
+        <v>5.911940959735956</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4.055782974525162</v>
+        <v>3.970721252795083</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3.489546608836069</v>
+        <v>3.418786994571136</v>
       </c>
     </row>
     <row r="17">
@@ -2980,19 +2980,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7.976559329993601</v>
+        <v>7.791845476389811</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>5.995908808691096</v>
+        <v>5.861580380242414</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4.810679901554656</v>
+        <v>4.706442616760781</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>4.022831713053255</v>
+        <v>3.938549136097555</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>3.461893522369199</v>
+        <v>3.391779457697584</v>
       </c>
     </row>
     <row r="18">
@@ -3002,19 +3002,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>7.907154453209897</v>
+        <v>7.724145793683983</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>5.944997186851519</v>
+        <v>5.81190376621413</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>4.770827598168174</v>
+        <v>4.667544789338453</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3.990325171911993</v>
+        <v>3.906811251616137</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3.434612513025957</v>
+        <v>3.365135338899167</v>
       </c>
     </row>
     <row r="20">
@@ -3059,19 +3059,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>5.957451797954994</v>
+        <v>5.824215735162758</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>5.379702321466985</v>
+        <v>5.261113519562423</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>4.325720187878041</v>
+        <v>4.233794195992333</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>3.907604314511882</v>
+        <v>3.826225220792922</v>
       </c>
     </row>
     <row r="24">
@@ -3116,19 +3116,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>6.443342919647113</v>
+        <v>6.306723155809302</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>5.647211028302799</v>
+        <v>5.526298730594553</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4.054947245614179</v>
+        <v>3.965449880165061</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>3.258815354269865</v>
+        <v>3.18502545495031</v>
       </c>
     </row>
     <row r="28">
@@ -3173,19 +3173,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>4.024478047929036</v>
+        <v>3.933010729477441</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>4.437801581315985</v>
+        <v>4.339465506300848</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>5.264316942610993</v>
+        <v>5.152243354468767</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>5.677520149872032</v>
+        <v>5.558577805166262</v>
       </c>
     </row>
     <row r="32">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>2.991805901498502</v>
+        <v>2.922068051995918</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>3.921439448943881</v>
+        <v>3.833968108403248</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>5.780724545348389</v>
+        <v>5.657786222731658</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>6.710375291402692</v>
+        <v>6.569703477747911</v>
       </c>
     </row>
     <row r="36">
@@ -3287,19 +3287,19 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>5.363960992397897</v>
+        <v>5.258756160819213</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>5.107520064678192</v>
+        <v>5.002315233099507</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>4.466417745378932</v>
+        <v>4.361212913800246</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>4.081756353799374</v>
+        <v>3.97655152222069</v>
       </c>
     </row>
     <row r="40">
@@ -3344,19 +3344,19 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>5.105682872488786</v>
+        <v>5.0004780409101</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>5.272987469829767</v>
+        <v>5.167782638251081</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>5.398465917835503</v>
+        <v>5.293261086256817</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>5.607596664511728</v>
+        <v>5.502391832933043</v>
       </c>
     </row>
     <row r="44">
@@ -3401,19 +3401,19 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>4.666619172766612</v>
+        <v>4.562468056436314</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>4.758849154862552</v>
+        <v>4.654171180908059</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>4.851079136958488</v>
+        <v>4.745874305379804</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>4.943309119054425</v>
+        <v>4.837577429851549</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>5.035539101150361</v>
+        <v>4.929280554323295</v>
       </c>
     </row>
     <row r="48">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="H50" s="7" t="n">
-        <v>2.750417615655593</v>
+        <v>2.687145695130762</v>
       </c>
     </row>
     <row r="51">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="H51" s="7" t="n">
-        <v>1.121883543030733</v>
+        <v>1.081007637294689</v>
       </c>
     </row>
     <row r="52">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="H52" s="7" t="n">
-        <v>7.044222881257744</v>
+        <v>6.913529127525565</v>
       </c>
     </row>
     <row r="53">
@@ -4117,14 +4117,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1.121883543030733</v>
+        <v>1.081007637294689</v>
       </c>
       <c r="C5" s="8">
         <f>'Fundamental Valuation'!C5</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7.044222881257744</v>
+        <v>6.913529127525565</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.750417615655593</v>
+        <v>2.687145695130762</v>
       </c>
       <c r="G14" s="9">
         <f>C14/$C$16-1</f>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.750417615655593</v>
+        <v>2.687145695130762</v>
       </c>
     </row>
     <row r="15">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.121883543030733</v>
+        <v>1.081007637294689</v>
       </c>
     </row>
     <row r="16">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.044222881257744</v>
+        <v>6.913529127525565</v>
       </c>
     </row>
     <row r="18">
@@ -8431,11 +8431,11 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Terminal NOPAT (FY2031E)</t>
+          <t>FY2030E NOPAT — the perpetuity grows this once</t>
         </is>
       </c>
       <c r="C50" s="37">
-        <f>F37*(1+Assumptions!$C$50)</f>
+        <f>F37</f>
         <v/>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="C51" s="37">
-        <f>F35*(1+Assumptions!$C$50)</f>
+        <f>F35</f>
         <v/>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="C54" s="37">
-        <f>-Assumptions!$C$49*-7184.461799</f>
+        <f>-Assumptions!$C$49*-7009.244700</f>
         <v/>
       </c>
     </row>
